--- a/docs/excel_template.xlsx
+++ b/docs/excel_template.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="96">
   <si>
     <t>Date</t>
   </si>
@@ -263,6 +263,69 @@
   </si>
   <si>
     <t>sum</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PALE_MINT</t>
+  </si>
+  <si>
+    <t>PALE_PINK</t>
+  </si>
+  <si>
+    <t>LIGHT_BLUE</t>
+  </si>
+  <si>
+    <t>SKY_BLUE</t>
+  </si>
+  <si>
+    <t>PEACH</t>
+  </si>
+  <si>
+    <t>LACENDER</t>
+  </si>
+  <si>
+    <t>BEIGE</t>
+  </si>
+  <si>
+    <t>LIGHT_CORAL</t>
+  </si>
+  <si>
+    <t>YELLOW_GREEN</t>
+  </si>
+  <si>
+    <t>I</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coin-hold</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SATIN_GREEN</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Border. M</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>border. T</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Border . D</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coin hold</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -275,7 +338,7 @@
     <numFmt numFmtId="177" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
     <numFmt numFmtId="178" formatCode="0.00\ ;[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -309,8 +372,14 @@
       <family val="3"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF82AAFF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -401,8 +470,20 @@
         <bgColor rgb="FFF2DCDB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor rgb="FFFDE9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+        <bgColor rgb="FFFDE9D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="32">
+  <borders count="52">
     <border>
       <left/>
       <right/>
@@ -859,12 +940,296 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="252">
+  <cellXfs count="277">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1519,6 +1884,123 @@
     <xf numFmtId="49" fontId="2" fillId="11" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="15" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="15" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="16" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="16" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1543,6 +2025,12 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1566,54 +2054,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="15" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="15" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1689,6 +2129,9 @@
       <rgbColor rgb="00333399"/>
       <rgbColor rgb="00333333"/>
     </indexedColors>
+    <mruColors>
+      <color rgb="FFC6E0B4"/>
+    </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1964,18 +2407,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AMJ156"/>
+  <dimension ref="A1:AML156"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="18" width="9.75" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.75" style="1" customWidth="1"/>
-    <col min="20" max="20" width="9.75" style="1" customWidth="1"/>
-    <col min="21" max="1024" width="9" style="1"/>
+    <col min="3" max="20" width="9.75" style="1" customWidth="1"/>
+    <col min="21" max="21" width="10.75" style="1" customWidth="1"/>
+    <col min="22" max="22" width="9.75" style="1" customWidth="1"/>
+    <col min="23" max="1026" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1">
         <v>1</v>
       </c>
@@ -2036,49 +2479,59 @@
       <c r="T1" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U1" s="1">
+        <v>21</v>
+      </c>
+      <c r="V1" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="223" t="s">
+      <c r="C2" s="262" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="223"/>
-      <c r="E2" s="224" t="s">
+      <c r="D2" s="262"/>
+      <c r="E2" s="267" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" s="268"/>
+      <c r="G2" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="224"/>
-      <c r="G2" s="225" t="s">
+      <c r="H2" s="263"/>
+      <c r="I2" s="264" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="225"/>
-      <c r="I2" s="226" t="s">
+      <c r="J2" s="264"/>
+      <c r="K2" s="265" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="226"/>
-      <c r="K2" s="227" t="s">
+      <c r="L2" s="265"/>
+      <c r="M2" s="266" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="227"/>
-      <c r="M2" s="220" t="s">
+      <c r="N2" s="266"/>
+      <c r="O2" s="259" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="220"/>
-      <c r="O2" s="221" t="s">
+      <c r="P2" s="259"/>
+      <c r="Q2" s="260" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="221"/>
-      <c r="Q2" s="222" t="s">
+      <c r="R2" s="260"/>
+      <c r="S2" s="261" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="222"/>
-      <c r="S2" s="222"/>
-      <c r="T2" s="3" t="s">
+      <c r="T2" s="261"/>
+      <c r="U2" s="261"/>
+      <c r="V2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2088,54 +2541,60 @@
       <c r="D3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="241" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="242" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="L3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="M3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="N3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="14" t="s">
+      <c r="O3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="15" t="s">
+      <c r="P3" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="Q3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="P3" s="17" t="s">
+      <c r="R3" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="18" t="s">
+      <c r="S3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="R3" s="19" t="s">
+      <c r="T3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="S3" s="20" t="s">
+      <c r="U3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="3"/>
-    </row>
-    <row r="4" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V3" s="3"/>
+    </row>
+    <row r="4" spans="1:22" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="21" t="s">
         <v>14</v>
       </c>
@@ -2143,414 +2602,442 @@
         <v>70</v>
       </c>
       <c r="D4" s="5"/>
-      <c r="E4" s="6">
+      <c r="E4" s="241">
+        <v>0</v>
+      </c>
+      <c r="F4" s="242"/>
+      <c r="G4" s="6">
         <v>15266.02</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="8">
+      <c r="H4" s="7"/>
+      <c r="I4" s="8">
         <v>89.9</v>
       </c>
-      <c r="H4" s="9"/>
-      <c r="I4" s="10" t="s">
+      <c r="J4" s="9"/>
+      <c r="K4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="11"/>
-      <c r="K4" s="12" t="s">
+      <c r="L4" s="11"/>
+      <c r="M4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="13"/>
-      <c r="M4" s="14" t="s">
+      <c r="N4" s="13"/>
+      <c r="O4" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="15"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="24"/>
-      <c r="R4" s="25"/>
-      <c r="S4" s="26">
+      <c r="P4" s="15"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="25"/>
+      <c r="U4" s="26">
         <v>15425.92</v>
       </c>
-      <c r="T4" s="27"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V4" s="27"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B5" s="28">
         <v>46023</v>
       </c>
       <c r="C5" s="29"/>
       <c r="D5" s="30"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="33" t="s">
+      <c r="E5" s="243"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="34">
+      <c r="J5" s="34">
         <v>14.6</v>
       </c>
-      <c r="I5" s="35"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="40"/>
-      <c r="O5" s="41" t="s">
+      <c r="K5" s="35"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="38"/>
+      <c r="O5" s="39"/>
+      <c r="P5" s="40"/>
+      <c r="Q5" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="P5" s="42">
+      <c r="R5" s="42">
         <v>14.6</v>
       </c>
-      <c r="Q5" s="43" t="s">
+      <c r="S5" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="R5" s="44">
+      <c r="T5" s="44">
         <v>14.6</v>
       </c>
-      <c r="S5" s="45"/>
-      <c r="T5" s="46"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U5" s="45"/>
+      <c r="V5" s="46"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B6" s="47"/>
       <c r="C6" s="48"/>
       <c r="D6" s="49"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="52" t="s">
+      <c r="E6" s="245"/>
+      <c r="F6" s="246"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="53">
+      <c r="J6" s="53">
         <v>7.3</v>
       </c>
-      <c r="I6" s="54"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="58"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="60" t="s">
+      <c r="K6" s="54"/>
+      <c r="L6" s="55"/>
+      <c r="M6" s="56"/>
+      <c r="N6" s="57"/>
+      <c r="O6" s="58"/>
+      <c r="P6" s="59"/>
+      <c r="Q6" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="P6" s="61">
+      <c r="R6" s="61">
         <v>7.3</v>
       </c>
-      <c r="Q6" s="62" t="s">
+      <c r="S6" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="R6" s="63">
+      <c r="T6" s="63">
         <v>7.3</v>
       </c>
-      <c r="S6" s="64"/>
-      <c r="T6" s="65"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U6" s="64"/>
+      <c r="V6" s="65"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B7" s="47"/>
       <c r="C7" s="48"/>
       <c r="D7" s="49"/>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="245"/>
+      <c r="F7" s="246"/>
+      <c r="G7" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="51">
+      <c r="H7" s="51">
         <v>10</v>
       </c>
-      <c r="G7" s="52"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="54">
+      <c r="I7" s="52"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54">
         <v>10</v>
       </c>
-      <c r="J7" s="55" t="s">
+      <c r="L7" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="56"/>
-      <c r="L7" s="57"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="59"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="61"/>
-      <c r="Q7" s="62"/>
-      <c r="R7" s="63"/>
-      <c r="S7" s="64"/>
-      <c r="T7" s="65"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="58"/>
+      <c r="P7" s="59"/>
+      <c r="Q7" s="60"/>
+      <c r="R7" s="61"/>
+      <c r="S7" s="62"/>
+      <c r="T7" s="63"/>
+      <c r="U7" s="64"/>
+      <c r="V7" s="65"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B8" s="47"/>
       <c r="C8" s="48"/>
       <c r="D8" s="49"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="54" t="s">
+      <c r="E8" s="245"/>
+      <c r="F8" s="246"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="53"/>
+      <c r="K8" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="J8" s="55">
+      <c r="L8" s="55">
         <v>10</v>
       </c>
-      <c r="K8" s="56"/>
-      <c r="L8" s="57"/>
-      <c r="M8" s="58"/>
-      <c r="N8" s="59"/>
-      <c r="O8" s="60" t="s">
+      <c r="M8" s="56"/>
+      <c r="N8" s="57"/>
+      <c r="O8" s="58"/>
+      <c r="P8" s="59"/>
+      <c r="Q8" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="P8" s="61">
+      <c r="R8" s="61">
         <v>10</v>
       </c>
-      <c r="Q8" s="62" t="s">
+      <c r="S8" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="R8" s="63">
+      <c r="T8" s="63">
         <v>10</v>
       </c>
-      <c r="S8" s="64"/>
-      <c r="T8" s="65"/>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U8" s="64"/>
+      <c r="V8" s="65"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B9" s="47"/>
       <c r="C9" s="48"/>
       <c r="D9" s="49"/>
-      <c r="E9" s="50" t="s">
+      <c r="E9" s="245"/>
+      <c r="F9" s="246"/>
+      <c r="G9" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="51">
+      <c r="H9" s="51">
         <v>184</v>
       </c>
-      <c r="G9" s="52"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="54">
+      <c r="I9" s="52"/>
+      <c r="J9" s="53"/>
+      <c r="K9" s="54">
         <v>184</v>
       </c>
-      <c r="J9" s="55" t="s">
+      <c r="L9" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="K9" s="56"/>
-      <c r="L9" s="57"/>
-      <c r="M9" s="58"/>
-      <c r="N9" s="59"/>
-      <c r="O9" s="60"/>
-      <c r="P9" s="61"/>
-      <c r="Q9" s="62"/>
-      <c r="R9" s="63"/>
-      <c r="S9" s="64"/>
-      <c r="T9" s="65"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M9" s="56"/>
+      <c r="N9" s="57"/>
+      <c r="O9" s="58"/>
+      <c r="P9" s="59"/>
+      <c r="Q9" s="60"/>
+      <c r="R9" s="61"/>
+      <c r="S9" s="62"/>
+      <c r="T9" s="63"/>
+      <c r="U9" s="64"/>
+      <c r="V9" s="65"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B10" s="47"/>
       <c r="C10" s="48"/>
       <c r="D10" s="49"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="54" t="s">
+      <c r="E10" s="255"/>
+      <c r="F10" s="246"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="53"/>
+      <c r="K10" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="55">
+      <c r="L10" s="55">
         <v>184</v>
       </c>
-      <c r="K10" s="56"/>
-      <c r="L10" s="57"/>
-      <c r="M10" s="58"/>
-      <c r="N10" s="59"/>
-      <c r="O10" s="60" t="s">
+      <c r="M10" s="56"/>
+      <c r="N10" s="57"/>
+      <c r="O10" s="58"/>
+      <c r="P10" s="59"/>
+      <c r="Q10" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="P10" s="61">
+      <c r="R10" s="61">
         <v>184</v>
       </c>
-      <c r="Q10" s="62" t="s">
+      <c r="S10" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="R10" s="63">
+      <c r="T10" s="63">
         <v>184</v>
       </c>
-      <c r="S10" s="64"/>
-      <c r="T10" s="65"/>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U10" s="64"/>
+      <c r="V10" s="65"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B11" s="47"/>
       <c r="C11" s="48"/>
       <c r="D11" s="49"/>
-      <c r="E11" s="50" t="s">
+      <c r="E11" s="245"/>
+      <c r="F11" s="246"/>
+      <c r="G11" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="51">
+      <c r="H11" s="51">
         <v>100</v>
       </c>
-      <c r="G11" s="52"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="55"/>
-      <c r="K11" s="56"/>
-      <c r="L11" s="57"/>
-      <c r="M11" s="58">
+      <c r="I11" s="52"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="55"/>
+      <c r="M11" s="56"/>
+      <c r="N11" s="57"/>
+      <c r="O11" s="58">
         <v>100</v>
       </c>
-      <c r="N11" s="59" t="s">
+      <c r="P11" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="O11" s="60"/>
-      <c r="P11" s="61"/>
-      <c r="Q11" s="62"/>
-      <c r="R11" s="63"/>
-      <c r="S11" s="64"/>
-      <c r="T11" s="65"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q11" s="60"/>
+      <c r="R11" s="61"/>
+      <c r="S11" s="62"/>
+      <c r="T11" s="63"/>
+      <c r="U11" s="64"/>
+      <c r="V11" s="65"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B12" s="47"/>
       <c r="C12" s="48"/>
       <c r="D12" s="49"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="55"/>
-      <c r="K12" s="56"/>
-      <c r="L12" s="57"/>
-      <c r="M12" s="58" t="s">
+      <c r="E12" s="245"/>
+      <c r="F12" s="246"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="54"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="56"/>
+      <c r="N12" s="57"/>
+      <c r="O12" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="N12" s="59">
+      <c r="P12" s="59">
         <v>100</v>
       </c>
-      <c r="O12" s="60" t="s">
+      <c r="Q12" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="P12" s="61">
+      <c r="R12" s="61">
         <v>100</v>
       </c>
-      <c r="Q12" s="62" t="s">
+      <c r="S12" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="R12" s="63">
+      <c r="T12" s="63">
         <v>100</v>
       </c>
-      <c r="S12" s="64"/>
-      <c r="T12" s="65"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U12" s="64"/>
+      <c r="V12" s="65"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B13" s="47"/>
       <c r="C13" s="48"/>
       <c r="D13" s="49"/>
-      <c r="E13" s="50" t="s">
+      <c r="E13" s="245"/>
+      <c r="F13" s="246"/>
+      <c r="G13" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F13" s="51">
+      <c r="H13" s="51">
         <v>15.23</v>
       </c>
-      <c r="G13" s="52"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="54">
+      <c r="I13" s="52"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="54">
         <v>15.23</v>
       </c>
-      <c r="J13" s="55" t="s">
+      <c r="L13" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="56"/>
-      <c r="L13" s="57"/>
-      <c r="M13" s="58"/>
-      <c r="N13" s="59"/>
-      <c r="O13" s="60"/>
-      <c r="P13" s="61"/>
-      <c r="Q13" s="62"/>
-      <c r="R13" s="63"/>
-      <c r="S13" s="64"/>
-      <c r="T13" s="65"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M13" s="56"/>
+      <c r="N13" s="57"/>
+      <c r="O13" s="58"/>
+      <c r="P13" s="59"/>
+      <c r="Q13" s="60"/>
+      <c r="R13" s="61"/>
+      <c r="S13" s="62"/>
+      <c r="T13" s="63"/>
+      <c r="U13" s="64"/>
+      <c r="V13" s="65"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B14" s="47"/>
       <c r="C14" s="48"/>
       <c r="D14" s="49"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="54" t="s">
+      <c r="E14" s="245"/>
+      <c r="F14" s="246"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="J14" s="55">
+      <c r="L14" s="55">
         <v>15.23</v>
       </c>
-      <c r="K14" s="56"/>
-      <c r="L14" s="57"/>
-      <c r="M14" s="58"/>
-      <c r="N14" s="59"/>
-      <c r="O14" s="60" t="s">
+      <c r="M14" s="56"/>
+      <c r="N14" s="57"/>
+      <c r="O14" s="58"/>
+      <c r="P14" s="59"/>
+      <c r="Q14" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="P14" s="61">
+      <c r="R14" s="61">
         <v>15.23</v>
       </c>
-      <c r="Q14" s="62" t="s">
+      <c r="S14" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="R14" s="63">
+      <c r="T14" s="63">
         <v>15.23</v>
       </c>
-      <c r="S14" s="64"/>
-      <c r="T14" s="65"/>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U14" s="64"/>
+      <c r="V14" s="65"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B15" s="47"/>
       <c r="C15" s="48"/>
       <c r="D15" s="49"/>
-      <c r="E15" s="50" t="s">
+      <c r="E15" s="245"/>
+      <c r="F15" s="246"/>
+      <c r="G15" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F15" s="51">
+      <c r="H15" s="51">
         <v>12.57</v>
       </c>
-      <c r="G15" s="52"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="54">
+      <c r="I15" s="52"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="54">
         <v>12.57</v>
       </c>
-      <c r="J15" s="55" t="s">
+      <c r="L15" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="K15" s="56"/>
-      <c r="L15" s="57"/>
-      <c r="M15" s="58"/>
-      <c r="N15" s="59"/>
-      <c r="O15" s="60"/>
-      <c r="P15" s="61"/>
-      <c r="Q15" s="62"/>
-      <c r="R15" s="63"/>
-      <c r="S15" s="64"/>
-      <c r="T15" s="65"/>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M15" s="56"/>
+      <c r="N15" s="57"/>
+      <c r="O15" s="58"/>
+      <c r="P15" s="59"/>
+      <c r="Q15" s="60"/>
+      <c r="R15" s="61"/>
+      <c r="S15" s="62"/>
+      <c r="T15" s="63"/>
+      <c r="U15" s="64"/>
+      <c r="V15" s="65"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B16" s="47"/>
       <c r="C16" s="48"/>
       <c r="D16" s="49"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="53"/>
-      <c r="I16" s="54" t="s">
+      <c r="E16" s="245"/>
+      <c r="F16" s="246"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="53"/>
+      <c r="K16" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="J16" s="55">
+      <c r="L16" s="55">
         <v>12.57</v>
       </c>
-      <c r="K16" s="56"/>
-      <c r="L16" s="57"/>
-      <c r="M16" s="58"/>
-      <c r="N16" s="59"/>
-      <c r="O16" s="60" t="s">
+      <c r="M16" s="56"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="58"/>
+      <c r="P16" s="59"/>
+      <c r="Q16" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="P16" s="61">
+      <c r="R16" s="61">
         <v>12.57</v>
       </c>
-      <c r="Q16" s="62" t="s">
+      <c r="S16" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="R16" s="63">
+      <c r="T16" s="63">
         <v>12.57</v>
       </c>
-      <c r="S16" s="64"/>
-      <c r="T16" s="65"/>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U16" s="64"/>
+      <c r="V16" s="65"/>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B17" s="66" t="s">
         <v>77</v>
       </c>
@@ -2558,518 +3045,552 @@
         <v>70</v>
       </c>
       <c r="D17" s="68"/>
-      <c r="E17" s="69">
+      <c r="E17" s="247">
+        <v>0</v>
+      </c>
+      <c r="F17" s="248"/>
+      <c r="G17" s="69">
         <v>14944.22</v>
       </c>
-      <c r="F17" s="70"/>
-      <c r="G17" s="71">
+      <c r="H17" s="70"/>
+      <c r="I17" s="71">
         <v>68</v>
       </c>
-      <c r="H17" s="72"/>
-      <c r="I17" s="73">
+      <c r="J17" s="72"/>
+      <c r="K17" s="73">
         <v>0</v>
       </c>
-      <c r="J17" s="74"/>
-      <c r="K17" s="75">
+      <c r="L17" s="74"/>
+      <c r="M17" s="75">
         <v>0</v>
       </c>
-      <c r="L17" s="76"/>
-      <c r="M17" s="77">
+      <c r="N17" s="76"/>
+      <c r="O17" s="77">
         <v>0</v>
       </c>
-      <c r="N17" s="78"/>
-      <c r="O17" s="79">
+      <c r="P17" s="78"/>
+      <c r="Q17" s="79">
         <v>0</v>
       </c>
-      <c r="P17" s="80">
+      <c r="R17" s="80">
         <v>343.7</v>
       </c>
-      <c r="Q17" s="81">
+      <c r="S17" s="81">
         <v>0</v>
       </c>
-      <c r="R17" s="82">
+      <c r="T17" s="82">
         <v>343.7</v>
       </c>
-      <c r="S17" s="83">
+      <c r="U17" s="83">
         <v>15082.22</v>
       </c>
-      <c r="T17" s="84" t="b">
+      <c r="V17" s="84" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:22" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="85" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="86"/>
       <c r="D18" s="87"/>
-      <c r="E18" s="88"/>
-      <c r="F18" s="89"/>
-      <c r="G18" s="90"/>
-      <c r="H18" s="91"/>
-      <c r="I18" s="92"/>
-      <c r="J18" s="93"/>
-      <c r="K18" s="94"/>
-      <c r="L18" s="95"/>
-      <c r="M18" s="96"/>
-      <c r="N18" s="97"/>
-      <c r="O18" s="98">
+      <c r="E18" s="249"/>
+      <c r="F18" s="250"/>
+      <c r="G18" s="88"/>
+      <c r="H18" s="89"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="91"/>
+      <c r="K18" s="92"/>
+      <c r="L18" s="93"/>
+      <c r="M18" s="94"/>
+      <c r="N18" s="95"/>
+      <c r="O18" s="96"/>
+      <c r="P18" s="97"/>
+      <c r="Q18" s="98">
         <v>0</v>
       </c>
-      <c r="P18" s="99">
+      <c r="R18" s="99">
         <v>343.7</v>
       </c>
-      <c r="Q18" s="100">
+      <c r="S18" s="100">
         <v>0</v>
       </c>
-      <c r="R18" s="101">
+      <c r="T18" s="101">
         <v>343.7</v>
       </c>
-      <c r="S18" s="102"/>
-      <c r="T18" s="103"/>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U18" s="102"/>
+      <c r="V18" s="103"/>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B19" s="28">
         <v>46024</v>
       </c>
       <c r="C19" s="29"/>
       <c r="D19" s="30"/>
-      <c r="E19" s="31" t="s">
+      <c r="E19" s="243"/>
+      <c r="F19" s="244"/>
+      <c r="G19" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="32">
+      <c r="H19" s="32">
         <v>2993</v>
       </c>
-      <c r="G19" s="33"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="36"/>
-      <c r="K19" s="37"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="41"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="43" t="s">
+      <c r="I19" s="33"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="36"/>
+      <c r="M19" s="37"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="39"/>
+      <c r="P19" s="40"/>
+      <c r="Q19" s="41"/>
+      <c r="R19" s="42"/>
+      <c r="S19" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="R19" s="44">
+      <c r="T19" s="44">
         <v>2993</v>
       </c>
-      <c r="S19" s="104"/>
-      <c r="T19" s="46"/>
-    </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U19" s="104"/>
+      <c r="V19" s="46"/>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B20" s="105"/>
       <c r="C20" s="106"/>
       <c r="D20" s="107"/>
-      <c r="E20" s="108">
+      <c r="E20" s="251"/>
+      <c r="F20" s="252"/>
+      <c r="G20" s="108">
         <v>7000</v>
       </c>
-      <c r="F20" s="109" t="s">
+      <c r="H20" s="109" t="s">
         <v>25</v>
       </c>
-      <c r="G20" s="110"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="112"/>
-      <c r="J20" s="113"/>
-      <c r="K20" s="114"/>
-      <c r="L20" s="115"/>
-      <c r="M20" s="116"/>
-      <c r="N20" s="117"/>
-      <c r="O20" s="118"/>
-      <c r="P20" s="119"/>
-      <c r="Q20" s="120">
+      <c r="I20" s="110"/>
+      <c r="J20" s="111"/>
+      <c r="K20" s="112"/>
+      <c r="L20" s="113"/>
+      <c r="M20" s="114"/>
+      <c r="N20" s="115"/>
+      <c r="O20" s="116"/>
+      <c r="P20" s="117"/>
+      <c r="Q20" s="118"/>
+      <c r="R20" s="119"/>
+      <c r="S20" s="120">
         <v>7000</v>
       </c>
-      <c r="R20" s="121" t="s">
+      <c r="T20" s="121" t="s">
         <v>25</v>
       </c>
-      <c r="S20" s="45"/>
-      <c r="T20" s="122"/>
-    </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U20" s="45"/>
+      <c r="V20" s="122"/>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B21" s="105"/>
       <c r="C21" s="106"/>
       <c r="D21" s="107"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="109"/>
-      <c r="G21" s="110" t="s">
+      <c r="E21" s="251"/>
+      <c r="F21" s="252"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="110" t="s">
         <v>26</v>
       </c>
-      <c r="H21" s="111">
+      <c r="J21" s="111">
         <v>2.6</v>
       </c>
-      <c r="I21" s="112"/>
-      <c r="J21" s="113"/>
-      <c r="K21" s="114"/>
-      <c r="L21" s="115"/>
-      <c r="M21" s="116"/>
-      <c r="N21" s="117"/>
-      <c r="O21" s="118" t="s">
+      <c r="K21" s="112"/>
+      <c r="L21" s="113"/>
+      <c r="M21" s="114"/>
+      <c r="N21" s="115"/>
+      <c r="O21" s="116"/>
+      <c r="P21" s="117"/>
+      <c r="Q21" s="118" t="s">
         <v>26</v>
       </c>
-      <c r="P21" s="119">
+      <c r="R21" s="119">
         <v>2.6</v>
       </c>
-      <c r="Q21" s="120" t="s">
+      <c r="S21" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="R21" s="121">
+      <c r="T21" s="121">
         <v>2.6</v>
       </c>
-      <c r="S21" s="45"/>
-      <c r="T21" s="122"/>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U21" s="45"/>
+      <c r="V21" s="122"/>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B22" s="105"/>
       <c r="C22" s="106"/>
       <c r="D22" s="107"/>
-      <c r="E22" s="108"/>
-      <c r="F22" s="109"/>
-      <c r="G22" s="110" t="s">
+      <c r="E22" s="251"/>
+      <c r="F22" s="252"/>
+      <c r="G22" s="108"/>
+      <c r="H22" s="109"/>
+      <c r="I22" s="110" t="s">
         <v>16</v>
       </c>
-      <c r="H22" s="111">
+      <c r="J22" s="111">
         <v>10.8</v>
       </c>
-      <c r="I22" s="112"/>
-      <c r="J22" s="113"/>
-      <c r="K22" s="114"/>
-      <c r="L22" s="115"/>
-      <c r="M22" s="116"/>
-      <c r="N22" s="117"/>
-      <c r="O22" s="118" t="s">
+      <c r="K22" s="112"/>
+      <c r="L22" s="113"/>
+      <c r="M22" s="114"/>
+      <c r="N22" s="115"/>
+      <c r="O22" s="116"/>
+      <c r="P22" s="117"/>
+      <c r="Q22" s="118" t="s">
         <v>16</v>
       </c>
-      <c r="P22" s="119">
+      <c r="R22" s="119">
         <v>10.8</v>
       </c>
-      <c r="Q22" s="120" t="s">
+      <c r="S22" s="120" t="s">
         <v>16</v>
       </c>
-      <c r="R22" s="121">
+      <c r="T22" s="121">
         <v>10.8</v>
       </c>
-      <c r="S22" s="45"/>
-      <c r="T22" s="122"/>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U22" s="45"/>
+      <c r="V22" s="122"/>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B23" s="105"/>
       <c r="C23" s="106"/>
       <c r="D23" s="107"/>
-      <c r="E23" s="108"/>
-      <c r="F23" s="109"/>
-      <c r="G23" s="110" t="s">
+      <c r="E23" s="251"/>
+      <c r="F23" s="252"/>
+      <c r="G23" s="108"/>
+      <c r="H23" s="109"/>
+      <c r="I23" s="110" t="s">
         <v>27</v>
       </c>
-      <c r="H23" s="111">
+      <c r="J23" s="111">
         <v>3.2</v>
       </c>
-      <c r="I23" s="112"/>
-      <c r="J23" s="113"/>
-      <c r="K23" s="114"/>
-      <c r="L23" s="115"/>
-      <c r="M23" s="116"/>
-      <c r="N23" s="117"/>
-      <c r="O23" s="118" t="s">
+      <c r="K23" s="112"/>
+      <c r="L23" s="113"/>
+      <c r="M23" s="114"/>
+      <c r="N23" s="115"/>
+      <c r="O23" s="116"/>
+      <c r="P23" s="117"/>
+      <c r="Q23" s="118" t="s">
         <v>27</v>
       </c>
-      <c r="P23" s="119">
+      <c r="R23" s="119">
         <v>3.2</v>
       </c>
-      <c r="Q23" s="120" t="s">
+      <c r="S23" s="120" t="s">
         <v>27</v>
       </c>
-      <c r="R23" s="121">
+      <c r="T23" s="121">
         <v>3.2</v>
       </c>
-      <c r="S23" s="45"/>
-      <c r="T23" s="122"/>
-    </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U23" s="45"/>
+      <c r="V23" s="122"/>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B24" s="105"/>
       <c r="C24" s="106"/>
       <c r="D24" s="107"/>
-      <c r="E24" s="108"/>
-      <c r="F24" s="109"/>
-      <c r="G24" s="110" t="s">
+      <c r="E24" s="251"/>
+      <c r="F24" s="252"/>
+      <c r="G24" s="108"/>
+      <c r="H24" s="109"/>
+      <c r="I24" s="110" t="s">
         <v>16</v>
       </c>
-      <c r="H24" s="111">
+      <c r="J24" s="111">
         <v>10.4</v>
       </c>
-      <c r="I24" s="112"/>
-      <c r="J24" s="113"/>
-      <c r="K24" s="114"/>
-      <c r="L24" s="115"/>
-      <c r="M24" s="116"/>
-      <c r="N24" s="117"/>
-      <c r="O24" s="118" t="s">
+      <c r="K24" s="112"/>
+      <c r="L24" s="113"/>
+      <c r="M24" s="114"/>
+      <c r="N24" s="115"/>
+      <c r="O24" s="116"/>
+      <c r="P24" s="117"/>
+      <c r="Q24" s="118" t="s">
         <v>16</v>
       </c>
-      <c r="P24" s="119">
+      <c r="R24" s="119">
         <v>10.4</v>
       </c>
-      <c r="Q24" s="120" t="s">
+      <c r="S24" s="120" t="s">
         <v>16</v>
       </c>
-      <c r="R24" s="121">
+      <c r="T24" s="121">
         <v>10.4</v>
       </c>
-      <c r="S24" s="45"/>
-      <c r="T24" s="122"/>
-    </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U24" s="45"/>
+      <c r="V24" s="122"/>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B25" s="105"/>
       <c r="C25" s="106"/>
       <c r="D25" s="107"/>
-      <c r="E25" s="108" t="s">
+      <c r="E25" s="251"/>
+      <c r="F25" s="252"/>
+      <c r="G25" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="F25" s="109">
+      <c r="H25" s="109">
         <v>2520</v>
       </c>
-      <c r="G25" s="110"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="112">
+      <c r="I25" s="110"/>
+      <c r="J25" s="111"/>
+      <c r="K25" s="112">
         <v>2520</v>
       </c>
-      <c r="J25" s="113" t="s">
+      <c r="L25" s="113" t="s">
         <v>17</v>
       </c>
-      <c r="K25" s="114"/>
-      <c r="L25" s="115"/>
-      <c r="M25" s="116"/>
-      <c r="N25" s="117"/>
-      <c r="O25" s="118"/>
-      <c r="P25" s="119"/>
-      <c r="Q25" s="120"/>
-      <c r="R25" s="121"/>
-      <c r="S25" s="45"/>
-      <c r="T25" s="122"/>
-    </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="M25" s="114"/>
+      <c r="N25" s="115"/>
+      <c r="O25" s="116"/>
+      <c r="P25" s="117"/>
+      <c r="Q25" s="118"/>
+      <c r="R25" s="119"/>
+      <c r="S25" s="120"/>
+      <c r="T25" s="121"/>
+      <c r="U25" s="45"/>
+      <c r="V25" s="122"/>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B26" s="105"/>
       <c r="C26" s="106"/>
       <c r="D26" s="107"/>
-      <c r="E26" s="108"/>
-      <c r="F26" s="109"/>
-      <c r="G26" s="110"/>
-      <c r="H26" s="111"/>
-      <c r="I26" s="112" t="s">
+      <c r="E26" s="251"/>
+      <c r="F26" s="252"/>
+      <c r="G26" s="108"/>
+      <c r="H26" s="109"/>
+      <c r="I26" s="110"/>
+      <c r="J26" s="111"/>
+      <c r="K26" s="112" t="s">
         <v>28</v>
       </c>
-      <c r="J26" s="113">
+      <c r="L26" s="113">
         <v>2520</v>
       </c>
-      <c r="K26" s="114"/>
-      <c r="L26" s="115"/>
-      <c r="M26" s="116"/>
-      <c r="N26" s="117"/>
-      <c r="O26" s="118" t="s">
+      <c r="M26" s="114"/>
+      <c r="N26" s="115"/>
+      <c r="O26" s="116"/>
+      <c r="P26" s="117"/>
+      <c r="Q26" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="P26" s="119">
+      <c r="R26" s="119">
         <v>2520</v>
       </c>
-      <c r="Q26" s="120" t="s">
+      <c r="S26" s="120" t="s">
         <v>28</v>
       </c>
-      <c r="R26" s="121">
+      <c r="T26" s="121">
         <v>2520</v>
       </c>
-      <c r="S26" s="45"/>
-      <c r="T26" s="122"/>
-    </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U26" s="45"/>
+      <c r="V26" s="122"/>
+    </row>
+    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B27" s="105"/>
       <c r="C27" s="106"/>
       <c r="D27" s="107"/>
-      <c r="E27" s="108" t="s">
+      <c r="E27" s="251"/>
+      <c r="F27" s="252"/>
+      <c r="G27" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="F27" s="109">
+      <c r="H27" s="109">
         <v>100</v>
       </c>
-      <c r="G27" s="110"/>
-      <c r="H27" s="111"/>
-      <c r="I27" s="112">
+      <c r="I27" s="110"/>
+      <c r="J27" s="111"/>
+      <c r="K27" s="112">
         <v>100</v>
       </c>
-      <c r="J27" s="113" t="s">
+      <c r="L27" s="113" t="s">
         <v>17</v>
       </c>
-      <c r="K27" s="114"/>
-      <c r="L27" s="115"/>
-      <c r="M27" s="116"/>
-      <c r="N27" s="117"/>
-      <c r="O27" s="118"/>
-      <c r="P27" s="119"/>
-      <c r="Q27" s="120"/>
-      <c r="R27" s="121"/>
-      <c r="S27" s="45"/>
-      <c r="T27" s="122"/>
-    </row>
-    <row r="28" spans="2:20" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="M27" s="114"/>
+      <c r="N27" s="115"/>
+      <c r="O27" s="116"/>
+      <c r="P27" s="117"/>
+      <c r="Q27" s="118"/>
+      <c r="R27" s="119"/>
+      <c r="S27" s="120"/>
+      <c r="T27" s="121"/>
+      <c r="U27" s="45"/>
+      <c r="V27" s="122"/>
+    </row>
+    <row r="28" spans="2:22" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B28" s="105"/>
       <c r="C28" s="106"/>
       <c r="D28" s="107"/>
-      <c r="E28" s="108"/>
-      <c r="F28" s="109"/>
-      <c r="G28" s="110"/>
-      <c r="H28" s="111"/>
-      <c r="I28" s="112" t="s">
+      <c r="E28" s="251"/>
+      <c r="F28" s="252"/>
+      <c r="G28" s="108"/>
+      <c r="H28" s="109"/>
+      <c r="I28" s="110"/>
+      <c r="J28" s="111"/>
+      <c r="K28" s="112" t="s">
         <v>29</v>
       </c>
-      <c r="J28" s="113">
+      <c r="L28" s="113">
         <v>100</v>
       </c>
-      <c r="K28" s="114"/>
-      <c r="L28" s="115"/>
-      <c r="M28" s="116"/>
-      <c r="N28" s="117"/>
-      <c r="O28" s="118" t="s">
+      <c r="M28" s="114"/>
+      <c r="N28" s="115"/>
+      <c r="O28" s="116"/>
+      <c r="P28" s="117"/>
+      <c r="Q28" s="118" t="s">
         <v>29</v>
       </c>
-      <c r="P28" s="119">
+      <c r="R28" s="119">
         <v>100</v>
       </c>
-      <c r="Q28" s="120" t="s">
+      <c r="S28" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="R28" s="121">
+      <c r="T28" s="121">
         <v>100</v>
       </c>
-      <c r="S28" s="45"/>
-      <c r="T28" s="122"/>
-    </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U28" s="45"/>
+      <c r="V28" s="122"/>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B29" s="105"/>
       <c r="C29" s="106"/>
       <c r="D29" s="107"/>
-      <c r="E29" s="108" t="s">
+      <c r="E29" s="251"/>
+      <c r="F29" s="252"/>
+      <c r="G29" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="F29" s="109">
+      <c r="H29" s="109">
         <v>4.5</v>
       </c>
-      <c r="G29" s="110"/>
-      <c r="H29" s="111"/>
-      <c r="I29" s="112">
+      <c r="I29" s="110"/>
+      <c r="J29" s="111"/>
+      <c r="K29" s="112">
         <v>4.5</v>
       </c>
-      <c r="J29" s="113" t="s">
+      <c r="L29" s="113" t="s">
         <v>17</v>
       </c>
-      <c r="K29" s="114"/>
-      <c r="L29" s="115"/>
-      <c r="M29" s="116"/>
-      <c r="N29" s="117"/>
-      <c r="O29" s="118"/>
-      <c r="P29" s="119"/>
-      <c r="Q29" s="120"/>
-      <c r="R29" s="121"/>
-      <c r="S29" s="45"/>
-      <c r="T29" s="122"/>
-    </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="M29" s="114"/>
+      <c r="N29" s="115"/>
+      <c r="O29" s="116"/>
+      <c r="P29" s="117"/>
+      <c r="Q29" s="118"/>
+      <c r="R29" s="119"/>
+      <c r="S29" s="120"/>
+      <c r="T29" s="121"/>
+      <c r="U29" s="45"/>
+      <c r="V29" s="122"/>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B30" s="105"/>
       <c r="C30" s="106"/>
       <c r="D30" s="107"/>
-      <c r="E30" s="108"/>
-      <c r="F30" s="109"/>
-      <c r="G30" s="110"/>
-      <c r="H30" s="111"/>
-      <c r="I30" s="112" t="s">
+      <c r="E30" s="251"/>
+      <c r="F30" s="252"/>
+      <c r="G30" s="108"/>
+      <c r="H30" s="109"/>
+      <c r="I30" s="110"/>
+      <c r="J30" s="111"/>
+      <c r="K30" s="112" t="s">
         <v>18</v>
       </c>
-      <c r="J30" s="113">
+      <c r="L30" s="113">
         <v>4.5</v>
       </c>
-      <c r="K30" s="114"/>
-      <c r="L30" s="115"/>
-      <c r="M30" s="116"/>
-      <c r="N30" s="117"/>
-      <c r="O30" s="118" t="s">
+      <c r="M30" s="114"/>
+      <c r="N30" s="115"/>
+      <c r="O30" s="116"/>
+      <c r="P30" s="117"/>
+      <c r="Q30" s="118" t="s">
         <v>18</v>
       </c>
-      <c r="P30" s="119">
+      <c r="R30" s="119">
         <v>4.5</v>
       </c>
-      <c r="Q30" s="120" t="s">
+      <c r="S30" s="120" t="s">
         <v>18</v>
       </c>
-      <c r="R30" s="121">
+      <c r="T30" s="121">
         <v>4.5</v>
       </c>
-      <c r="S30" s="45"/>
-      <c r="T30" s="122"/>
-    </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U30" s="45"/>
+      <c r="V30" s="122"/>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B31" s="105"/>
       <c r="C31" s="106"/>
       <c r="D31" s="107"/>
-      <c r="E31" s="108" t="s">
+      <c r="E31" s="251"/>
+      <c r="F31" s="252"/>
+      <c r="G31" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="F31" s="109">
+      <c r="H31" s="109">
         <v>231.6</v>
       </c>
-      <c r="G31" s="110"/>
-      <c r="H31" s="111"/>
-      <c r="I31" s="112">
+      <c r="I31" s="110"/>
+      <c r="J31" s="111"/>
+      <c r="K31" s="112">
         <v>231.6</v>
       </c>
-      <c r="J31" s="113" t="s">
+      <c r="L31" s="113" t="s">
         <v>17</v>
       </c>
-      <c r="K31" s="114"/>
-      <c r="L31" s="115"/>
-      <c r="M31" s="116"/>
-      <c r="N31" s="117"/>
-      <c r="O31" s="118"/>
-      <c r="P31" s="119"/>
-      <c r="Q31" s="120"/>
-      <c r="R31" s="121"/>
-      <c r="S31" s="45"/>
-      <c r="T31" s="122"/>
-    </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="M31" s="114"/>
+      <c r="N31" s="115"/>
+      <c r="O31" s="116"/>
+      <c r="P31" s="117"/>
+      <c r="Q31" s="118"/>
+      <c r="R31" s="119"/>
+      <c r="S31" s="120"/>
+      <c r="T31" s="121"/>
+      <c r="U31" s="45"/>
+      <c r="V31" s="122"/>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B32" s="105"/>
       <c r="C32" s="106"/>
       <c r="D32" s="107"/>
-      <c r="E32" s="108"/>
-      <c r="F32" s="109"/>
-      <c r="G32" s="110"/>
-      <c r="H32" s="111"/>
-      <c r="I32" s="112" t="s">
+      <c r="E32" s="251"/>
+      <c r="F32" s="252"/>
+      <c r="G32" s="108"/>
+      <c r="H32" s="109"/>
+      <c r="I32" s="110"/>
+      <c r="J32" s="111"/>
+      <c r="K32" s="112" t="s">
         <v>30</v>
       </c>
-      <c r="J32" s="113">
+      <c r="L32" s="113">
         <v>231.6</v>
       </c>
-      <c r="K32" s="114"/>
-      <c r="L32" s="115"/>
-      <c r="M32" s="116"/>
-      <c r="N32" s="117"/>
-      <c r="O32" s="118" t="s">
+      <c r="M32" s="114"/>
+      <c r="N32" s="115"/>
+      <c r="O32" s="116"/>
+      <c r="P32" s="117"/>
+      <c r="Q32" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="P32" s="119">
+      <c r="R32" s="119">
         <v>231.6</v>
       </c>
-      <c r="Q32" s="120" t="s">
+      <c r="S32" s="120" t="s">
         <v>30</v>
       </c>
-      <c r="R32" s="121">
+      <c r="T32" s="121">
         <v>231.6</v>
       </c>
-      <c r="S32" s="45"/>
-      <c r="T32" s="122"/>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="U32" s="45"/>
+      <c r="V32" s="122"/>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B33" s="105"/>
       <c r="C33" s="106" t="s">
         <v>19</v>
@@ -3077,94 +3598,104 @@
       <c r="D33" s="107">
         <v>63</v>
       </c>
-      <c r="E33" s="108"/>
-      <c r="F33" s="109"/>
-      <c r="G33" s="110"/>
-      <c r="H33" s="111"/>
-      <c r="I33" s="112"/>
-      <c r="J33" s="113"/>
-      <c r="K33" s="114"/>
-      <c r="L33" s="115"/>
-      <c r="M33" s="116"/>
-      <c r="N33" s="117"/>
-      <c r="O33" s="118" t="s">
+      <c r="E33" s="251"/>
+      <c r="F33" s="252"/>
+      <c r="G33" s="108"/>
+      <c r="H33" s="109"/>
+      <c r="I33" s="110"/>
+      <c r="J33" s="111"/>
+      <c r="K33" s="112"/>
+      <c r="L33" s="113"/>
+      <c r="M33" s="114"/>
+      <c r="N33" s="115"/>
+      <c r="O33" s="116"/>
+      <c r="P33" s="117"/>
+      <c r="Q33" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="P33" s="119">
+      <c r="R33" s="119">
         <v>63</v>
       </c>
-      <c r="Q33" s="120" t="s">
+      <c r="S33" s="120" t="s">
         <v>19</v>
       </c>
-      <c r="R33" s="121">
+      <c r="T33" s="121">
         <v>63</v>
       </c>
-      <c r="S33" s="45"/>
-      <c r="T33" s="122"/>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="U33" s="45"/>
+      <c r="V33" s="122"/>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B34" s="105"/>
       <c r="C34" s="106" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="D34" s="107">
         <v>7</v>
       </c>
-      <c r="E34" s="108"/>
-      <c r="F34" s="109"/>
-      <c r="G34" s="110"/>
-      <c r="H34" s="111"/>
-      <c r="I34" s="112"/>
-      <c r="J34" s="113"/>
-      <c r="K34" s="114"/>
-      <c r="L34" s="115"/>
-      <c r="M34" s="116"/>
-      <c r="N34" s="117"/>
-      <c r="O34" s="118" t="s">
+      <c r="E34" s="251">
+        <v>7</v>
+      </c>
+      <c r="F34" s="252" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" s="108"/>
+      <c r="H34" s="109"/>
+      <c r="I34" s="110"/>
+      <c r="J34" s="111"/>
+      <c r="K34" s="112"/>
+      <c r="L34" s="113"/>
+      <c r="M34" s="114"/>
+      <c r="N34" s="115"/>
+      <c r="O34" s="116"/>
+      <c r="P34" s="117"/>
+      <c r="Q34" s="118" t="s">
         <v>31</v>
       </c>
-      <c r="P34" s="119">
+      <c r="R34" s="119">
         <v>7</v>
       </c>
-      <c r="Q34" s="120" t="s">
+      <c r="S34" s="120" t="s">
         <v>31</v>
       </c>
-      <c r="R34" s="121">
+      <c r="T34" s="121">
         <v>7</v>
       </c>
-      <c r="S34" s="45"/>
-      <c r="T34" s="122"/>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="U34" s="45"/>
+      <c r="V34" s="122"/>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B35" s="47"/>
       <c r="C35" s="106"/>
       <c r="D35" s="107"/>
-      <c r="E35" s="108" t="s">
+      <c r="E35" s="251"/>
+      <c r="F35" s="252"/>
+      <c r="G35" s="108" t="s">
         <v>12</v>
       </c>
-      <c r="F35" s="109">
+      <c r="H35" s="109">
         <v>500</v>
       </c>
-      <c r="G35" s="110">
+      <c r="I35" s="110">
         <v>500</v>
       </c>
-      <c r="H35" s="111" t="s">
+      <c r="J35" s="111" t="s">
         <v>17</v>
       </c>
-      <c r="I35" s="54"/>
-      <c r="J35" s="55"/>
-      <c r="K35" s="56"/>
-      <c r="L35" s="57"/>
-      <c r="M35" s="58"/>
-      <c r="N35" s="59"/>
-      <c r="O35" s="60"/>
-      <c r="P35" s="61"/>
-      <c r="Q35" s="62"/>
-      <c r="R35" s="63"/>
-      <c r="S35" s="64"/>
-      <c r="T35" s="65"/>
-    </row>
-    <row r="36" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K35" s="54"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="56"/>
+      <c r="N35" s="57"/>
+      <c r="O35" s="58"/>
+      <c r="P35" s="59"/>
+      <c r="Q35" s="60"/>
+      <c r="R35" s="61"/>
+      <c r="S35" s="62"/>
+      <c r="T35" s="63"/>
+      <c r="U35" s="64"/>
+      <c r="V35" s="65"/>
+    </row>
+    <row r="36" spans="2:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="66" t="s">
         <v>23</v>
       </c>
@@ -3172,77 +3703,83 @@
         <v>0</v>
       </c>
       <c r="D36" s="68"/>
-      <c r="E36" s="123">
+      <c r="E36" s="247">
+        <v>7</v>
+      </c>
+      <c r="F36" s="248"/>
+      <c r="G36" s="123">
         <v>15595.12</v>
       </c>
-      <c r="F36" s="70"/>
-      <c r="G36" s="124" t="s">
+      <c r="H36" s="70"/>
+      <c r="I36" s="124" t="s">
         <v>32</v>
       </c>
-      <c r="H36" s="72"/>
-      <c r="I36" s="73" t="s">
+      <c r="J36" s="72"/>
+      <c r="K36" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="J36" s="74"/>
-      <c r="K36" s="75">
+      <c r="L36" s="74"/>
+      <c r="M36" s="75">
         <v>0</v>
       </c>
-      <c r="L36" s="76"/>
-      <c r="M36" s="77">
+      <c r="N36" s="76"/>
+      <c r="O36" s="77">
         <v>0</v>
       </c>
-      <c r="N36" s="78"/>
-      <c r="O36" s="79">
+      <c r="P36" s="78"/>
+      <c r="Q36" s="79">
         <v>0</v>
       </c>
-      <c r="P36" s="125">
+      <c r="R36" s="125">
         <v>2953.1</v>
       </c>
-      <c r="Q36" s="81">
+      <c r="S36" s="81">
         <v>7000</v>
       </c>
-      <c r="R36" s="126">
+      <c r="T36" s="126">
         <v>5946.1</v>
       </c>
-      <c r="S36" s="127">
+      <c r="U36" s="127">
         <v>16136.12</v>
       </c>
-      <c r="T36" s="84" t="b">
+      <c r="V36" s="84" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="85" t="s">
         <v>24</v>
       </c>
       <c r="C37" s="86"/>
       <c r="D37" s="87"/>
-      <c r="E37" s="88"/>
-      <c r="F37" s="89"/>
-      <c r="G37" s="90"/>
-      <c r="H37" s="91"/>
-      <c r="I37" s="92"/>
-      <c r="J37" s="93"/>
-      <c r="K37" s="94"/>
-      <c r="L37" s="95"/>
-      <c r="M37" s="96"/>
-      <c r="N37" s="97"/>
-      <c r="O37" s="79">
+      <c r="E37" s="249"/>
+      <c r="F37" s="250"/>
+      <c r="G37" s="88"/>
+      <c r="H37" s="89"/>
+      <c r="I37" s="90"/>
+      <c r="J37" s="91"/>
+      <c r="K37" s="92"/>
+      <c r="L37" s="93"/>
+      <c r="M37" s="94"/>
+      <c r="N37" s="95"/>
+      <c r="O37" s="96"/>
+      <c r="P37" s="97"/>
+      <c r="Q37" s="79">
         <v>0</v>
       </c>
-      <c r="P37" s="128">
+      <c r="R37" s="128">
         <v>3296.8</v>
       </c>
-      <c r="Q37" s="81">
+      <c r="S37" s="81">
         <v>7000</v>
       </c>
-      <c r="R37" s="129">
+      <c r="T37" s="129">
         <v>6289.8</v>
       </c>
-      <c r="S37" s="130"/>
-      <c r="T37" s="103"/>
-    </row>
-    <row r="38" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U37" s="130"/>
+      <c r="V37" s="103"/>
+    </row>
+    <row r="38" spans="2:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="21" t="s">
         <v>33</v>
       </c>
@@ -3252,78 +3789,106 @@
       <c r="D38" s="131" t="b">
         <v>1</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="253">
+        <v>7</v>
+      </c>
+      <c r="F38" s="254" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="6">
         <v>15595.12</v>
       </c>
-      <c r="F38" s="132" t="b">
+      <c r="H38" s="132" t="b">
         <v>1</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="I38" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="H38" s="133" t="b">
+      <c r="J38" s="133" t="b">
         <v>1</v>
       </c>
-      <c r="I38" s="10" t="s">
+      <c r="K38" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J38" s="134" t="b">
+      <c r="L38" s="134" t="b">
         <v>1</v>
       </c>
-      <c r="K38" s="12" t="s">
+      <c r="M38" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="L38" s="135" t="b">
+      <c r="N38" s="135" t="b">
         <v>1</v>
       </c>
-      <c r="M38" s="14" t="s">
+      <c r="O38" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="N38" s="136" t="b">
+      <c r="P38" s="136" t="b">
         <v>1</v>
       </c>
-      <c r="O38" s="22"/>
-      <c r="P38" s="23"/>
-      <c r="Q38" s="24"/>
-      <c r="R38" s="25"/>
-      <c r="S38" s="137">
+      <c r="Q38" s="22"/>
+      <c r="R38" s="23"/>
+      <c r="S38" s="24"/>
+      <c r="T38" s="25"/>
+      <c r="U38" s="137">
         <v>16136.12</v>
       </c>
-      <c r="T38" s="27"/>
-    </row>
-    <row r="39" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V38" s="27"/>
+    </row>
+    <row r="39" spans="2:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="138"/>
-      <c r="C39" s="139"/>
+      <c r="C39" s="236" t="s">
+        <v>78</v>
+      </c>
       <c r="D39" s="139"/>
-      <c r="E39" s="138"/>
-      <c r="F39" s="138"/>
-      <c r="G39" s="139"/>
-      <c r="H39" s="139"/>
-      <c r="I39" s="139"/>
+      <c r="E39" s="236" t="s">
+        <v>91</v>
+      </c>
+      <c r="F39" s="139"/>
+      <c r="G39" s="236" t="s">
+        <v>79</v>
+      </c>
+      <c r="H39" s="138"/>
+      <c r="I39" s="236" t="s">
+        <v>80</v>
+      </c>
       <c r="J39" s="139"/>
-      <c r="K39" s="139"/>
+      <c r="K39" s="236" t="s">
+        <v>81</v>
+      </c>
       <c r="L39" s="139"/>
-      <c r="M39" s="139"/>
+      <c r="M39" s="236" t="s">
+        <v>82</v>
+      </c>
       <c r="N39" s="139"/>
-      <c r="O39" s="138"/>
-      <c r="P39" s="138"/>
-      <c r="Q39" s="138"/>
+      <c r="O39" s="236" t="s">
+        <v>83</v>
+      </c>
+      <c r="P39" s="139"/>
+      <c r="Q39" s="236" t="s">
+        <v>84</v>
+      </c>
       <c r="R39" s="138"/>
-      <c r="S39" s="139"/>
-      <c r="T39" s="139"/>
-    </row>
-    <row r="40" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S39" s="236" t="s">
+        <v>85</v>
+      </c>
+      <c r="T39" s="138"/>
+      <c r="U39" s="139"/>
+      <c r="V39" s="236" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="2:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="139"/>
       <c r="C40" s="139"/>
       <c r="D40" s="139"/>
-      <c r="E40" s="138"/>
-      <c r="F40" s="138"/>
-      <c r="G40" s="139"/>
-      <c r="H40" s="139"/>
-      <c r="I40" s="138"/>
-      <c r="J40" s="138"/>
-      <c r="K40" s="139"/>
-      <c r="L40" s="139"/>
+      <c r="E40" s="139"/>
+      <c r="F40" s="139"/>
+      <c r="G40" s="138"/>
+      <c r="H40" s="138"/>
+      <c r="I40" s="139"/>
+      <c r="J40" s="139"/>
+      <c r="K40" s="138"/>
+      <c r="L40" s="138"/>
       <c r="M40" s="139"/>
       <c r="N40" s="139"/>
       <c r="O40" s="139"/>
@@ -3332,66 +3897,92 @@
       <c r="R40" s="139"/>
       <c r="S40" s="139"/>
       <c r="T40" s="139"/>
-    </row>
-    <row r="41" spans="2:22" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="V41" s="143"/>
-    </row>
-    <row r="42" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="236"/>
-      <c r="C42" s="237"/>
-      <c r="D42" s="239"/>
-      <c r="E42" s="238"/>
-    </row>
-    <row r="43" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="240"/>
-      <c r="C43" s="242"/>
-      <c r="D43" s="243"/>
-      <c r="E43" s="241"/>
-    </row>
-    <row r="44" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="240"/>
-      <c r="C44" s="242"/>
-      <c r="D44" s="243"/>
-      <c r="E44" s="241"/>
-    </row>
-    <row r="45" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="244"/>
-      <c r="C45" s="245"/>
-      <c r="D45" s="246"/>
-      <c r="E45" s="247"/>
-    </row>
-    <row r="46" spans="2:22" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="248"/>
-      <c r="C46" s="249"/>
-      <c r="D46" s="250"/>
-      <c r="E46" s="251"/>
-    </row>
-    <row r="47" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U40" s="139"/>
+      <c r="V40" s="139"/>
+    </row>
+    <row r="41" spans="2:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="X41" s="143"/>
+    </row>
+    <row r="42" spans="2:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="2:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="220"/>
+      <c r="C43" s="221"/>
+      <c r="D43" s="223"/>
+      <c r="E43" s="237"/>
+      <c r="F43" s="237"/>
+      <c r="G43" s="222"/>
+    </row>
+    <row r="44" spans="2:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="224"/>
+      <c r="C44" s="226"/>
+      <c r="D44" s="227"/>
+      <c r="E44" s="238"/>
+      <c r="F44" s="238"/>
+      <c r="G44" s="225"/>
+    </row>
+    <row r="45" spans="2:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="224"/>
+      <c r="C45" s="226"/>
+      <c r="D45" s="227"/>
+      <c r="E45" s="238"/>
+      <c r="F45" s="238"/>
+      <c r="G45" s="225"/>
+    </row>
+    <row r="46" spans="2:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="228"/>
+      <c r="C46" s="229"/>
+      <c r="D46" s="230"/>
+      <c r="E46" s="239"/>
+      <c r="F46" s="239"/>
+      <c r="G46" s="231"/>
+    </row>
+    <row r="47" spans="2:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="232"/>
+      <c r="C47" s="233"/>
+      <c r="D47" s="234"/>
+      <c r="E47" s="240"/>
+      <c r="F47" s="240"/>
+      <c r="G47" s="235"/>
+    </row>
+    <row r="48" spans="2:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="49" spans="2:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="256" t="s">
+        <v>92</v>
+      </c>
+      <c r="C49" s="143"/>
+      <c r="E49" s="143"/>
+    </row>
+    <row r="50" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="257" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="258" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="138"/>
       <c r="C72" s="139"/>
       <c r="D72" s="139"/>
@@ -3405,67 +3996,73 @@
       <c r="L72" s="139"/>
       <c r="M72" s="139"/>
       <c r="N72" s="139"/>
-      <c r="O72" s="138"/>
-      <c r="P72" s="138"/>
+      <c r="O72" s="139"/>
+      <c r="P72" s="139"/>
       <c r="Q72" s="138"/>
       <c r="R72" s="138"/>
       <c r="S72" s="138"/>
-      <c r="T72" s="139"/>
-    </row>
-    <row r="73" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T72" s="138"/>
+      <c r="U72" s="138"/>
+      <c r="V72" s="139"/>
+    </row>
+    <row r="73" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="138"/>
       <c r="C73" s="139"/>
       <c r="D73" s="139"/>
       <c r="E73" s="139"/>
       <c r="F73" s="139"/>
-      <c r="G73" s="138"/>
-      <c r="H73" s="138"/>
-      <c r="I73" s="139"/>
-      <c r="J73" s="139"/>
+      <c r="G73" s="139"/>
+      <c r="H73" s="139"/>
+      <c r="I73" s="138"/>
+      <c r="J73" s="138"/>
       <c r="K73" s="139"/>
       <c r="L73" s="139"/>
       <c r="M73" s="139"/>
       <c r="N73" s="139"/>
-      <c r="O73" s="138"/>
-      <c r="P73" s="138"/>
+      <c r="O73" s="139"/>
+      <c r="P73" s="139"/>
       <c r="Q73" s="138"/>
       <c r="R73" s="138"/>
-      <c r="S73" s="139"/>
-      <c r="T73" s="139"/>
-    </row>
-    <row r="74" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S73" s="138"/>
+      <c r="T73" s="138"/>
+      <c r="U73" s="139"/>
+      <c r="V73" s="139"/>
+    </row>
+    <row r="74" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="139"/>
       <c r="C74" s="139"/>
       <c r="D74" s="139"/>
       <c r="E74" s="139"/>
       <c r="F74" s="139"/>
-      <c r="G74" s="138"/>
-      <c r="H74" s="138"/>
-      <c r="I74" s="139"/>
-      <c r="J74" s="139"/>
+      <c r="G74" s="139"/>
+      <c r="H74" s="139"/>
+      <c r="I74" s="138"/>
+      <c r="J74" s="138"/>
       <c r="K74" s="139"/>
       <c r="L74" s="139"/>
       <c r="M74" s="139"/>
       <c r="N74" s="139"/>
-      <c r="O74" s="138"/>
-      <c r="P74" s="138"/>
+      <c r="O74" s="139"/>
+      <c r="P74" s="139"/>
       <c r="Q74" s="138"/>
       <c r="R74" s="138"/>
-      <c r="S74" s="139"/>
-      <c r="T74" s="139"/>
-    </row>
-    <row r="75" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S74" s="138"/>
+      <c r="T74" s="138"/>
+      <c r="U74" s="139"/>
+      <c r="V74" s="139"/>
+    </row>
+    <row r="75" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="139"/>
       <c r="C75" s="139"/>
       <c r="D75" s="139"/>
-      <c r="E75" s="138"/>
-      <c r="F75" s="138"/>
-      <c r="G75" s="139"/>
-      <c r="H75" s="139"/>
-      <c r="I75" s="138"/>
-      <c r="J75" s="138"/>
-      <c r="K75" s="139"/>
-      <c r="L75" s="139"/>
+      <c r="E75" s="139"/>
+      <c r="F75" s="139"/>
+      <c r="G75" s="138"/>
+      <c r="H75" s="138"/>
+      <c r="I75" s="139"/>
+      <c r="J75" s="139"/>
+      <c r="K75" s="138"/>
+      <c r="L75" s="138"/>
       <c r="M75" s="139"/>
       <c r="N75" s="139"/>
       <c r="O75" s="139"/>
@@ -3474,8 +4071,10 @@
       <c r="R75" s="139"/>
       <c r="S75" s="139"/>
       <c r="T75" s="139"/>
-    </row>
-    <row r="76" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U75" s="139"/>
+      <c r="V75" s="139"/>
+    </row>
+    <row r="76" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="139"/>
       <c r="C76" s="139"/>
       <c r="D76" s="139"/>
@@ -3483,52 +4082,56 @@
       <c r="F76" s="139"/>
       <c r="G76" s="139"/>
       <c r="H76" s="139"/>
-      <c r="I76" s="138"/>
-      <c r="J76" s="138"/>
-      <c r="K76" s="139"/>
-      <c r="L76" s="139"/>
+      <c r="I76" s="139"/>
+      <c r="J76" s="139"/>
+      <c r="K76" s="138"/>
+      <c r="L76" s="138"/>
       <c r="M76" s="139"/>
       <c r="N76" s="139"/>
-      <c r="O76" s="138"/>
-      <c r="P76" s="138"/>
+      <c r="O76" s="139"/>
+      <c r="P76" s="139"/>
       <c r="Q76" s="138"/>
       <c r="R76" s="138"/>
-      <c r="S76" s="139"/>
-      <c r="T76" s="139"/>
-    </row>
-    <row r="77" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S76" s="138"/>
+      <c r="T76" s="138"/>
+      <c r="U76" s="139"/>
+      <c r="V76" s="139"/>
+    </row>
+    <row r="77" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="139"/>
       <c r="C77" s="139"/>
       <c r="D77" s="139"/>
       <c r="E77" s="139"/>
       <c r="F77" s="139"/>
-      <c r="G77" s="138"/>
-      <c r="H77" s="138"/>
-      <c r="I77" s="139"/>
-      <c r="J77" s="139"/>
+      <c r="G77" s="139"/>
+      <c r="H77" s="139"/>
+      <c r="I77" s="138"/>
+      <c r="J77" s="138"/>
       <c r="K77" s="139"/>
       <c r="L77" s="139"/>
       <c r="M77" s="139"/>
       <c r="N77" s="139"/>
-      <c r="O77" s="138"/>
-      <c r="P77" s="138"/>
+      <c r="O77" s="139"/>
+      <c r="P77" s="139"/>
       <c r="Q77" s="138"/>
       <c r="R77" s="138"/>
-      <c r="S77" s="139"/>
-      <c r="T77" s="139"/>
-    </row>
-    <row r="78" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S77" s="138"/>
+      <c r="T77" s="138"/>
+      <c r="U77" s="139"/>
+      <c r="V77" s="139"/>
+    </row>
+    <row r="78" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="139"/>
       <c r="C78" s="139"/>
       <c r="D78" s="139"/>
-      <c r="E78" s="138"/>
-      <c r="F78" s="138"/>
-      <c r="G78" s="139"/>
-      <c r="H78" s="139"/>
-      <c r="I78" s="138"/>
-      <c r="J78" s="138"/>
-      <c r="K78" s="139"/>
-      <c r="L78" s="139"/>
+      <c r="E78" s="139"/>
+      <c r="F78" s="139"/>
+      <c r="G78" s="138"/>
+      <c r="H78" s="138"/>
+      <c r="I78" s="139"/>
+      <c r="J78" s="139"/>
+      <c r="K78" s="138"/>
+      <c r="L78" s="138"/>
       <c r="M78" s="139"/>
       <c r="N78" s="139"/>
       <c r="O78" s="139"/>
@@ -3537,8 +4140,10 @@
       <c r="R78" s="139"/>
       <c r="S78" s="139"/>
       <c r="T78" s="139"/>
-    </row>
-    <row r="79" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U78" s="139"/>
+      <c r="V78" s="139"/>
+    </row>
+    <row r="79" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="139"/>
       <c r="C79" s="139"/>
       <c r="D79" s="139"/>
@@ -3546,24 +4151,26 @@
       <c r="F79" s="139"/>
       <c r="G79" s="139"/>
       <c r="H79" s="139"/>
-      <c r="I79" s="138"/>
-      <c r="J79" s="138"/>
-      <c r="K79" s="139"/>
-      <c r="L79" s="139"/>
+      <c r="I79" s="139"/>
+      <c r="J79" s="139"/>
+      <c r="K79" s="138"/>
+      <c r="L79" s="138"/>
       <c r="M79" s="139"/>
       <c r="N79" s="139"/>
-      <c r="O79" s="138"/>
-      <c r="P79" s="138"/>
+      <c r="O79" s="139"/>
+      <c r="P79" s="139"/>
       <c r="Q79" s="138"/>
       <c r="R79" s="138"/>
-      <c r="S79" s="139"/>
-      <c r="T79" s="139"/>
-    </row>
-    <row r="80" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S79" s="138"/>
+      <c r="T79" s="138"/>
+      <c r="U79" s="139"/>
+      <c r="V79" s="139"/>
+    </row>
+    <row r="80" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="138"/>
       <c r="C80" s="138"/>
       <c r="D80" s="139"/>
-      <c r="E80" s="138"/>
+      <c r="E80" s="139"/>
       <c r="F80" s="139"/>
       <c r="G80" s="138"/>
       <c r="H80" s="139"/>
@@ -3574,13 +4181,15 @@
       <c r="M80" s="138"/>
       <c r="N80" s="139"/>
       <c r="O80" s="138"/>
-      <c r="P80" s="138"/>
+      <c r="P80" s="139"/>
       <c r="Q80" s="138"/>
       <c r="R80" s="138"/>
       <c r="S80" s="138"/>
       <c r="T80" s="138"/>
-    </row>
-    <row r="81" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U80" s="138"/>
+      <c r="V80" s="138"/>
+    </row>
+    <row r="81" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="138"/>
       <c r="C81" s="139"/>
       <c r="D81" s="139"/>
@@ -3594,14 +4203,16 @@
       <c r="L81" s="139"/>
       <c r="M81" s="139"/>
       <c r="N81" s="139"/>
-      <c r="O81" s="138"/>
-      <c r="P81" s="138"/>
+      <c r="O81" s="139"/>
+      <c r="P81" s="139"/>
       <c r="Q81" s="138"/>
       <c r="R81" s="138"/>
       <c r="S81" s="138"/>
-      <c r="T81" s="139"/>
-    </row>
-    <row r="82" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T81" s="138"/>
+      <c r="U81" s="138"/>
+      <c r="V81" s="139"/>
+    </row>
+    <row r="82" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="138"/>
       <c r="C82" s="138"/>
       <c r="D82" s="138"/>
@@ -3615,67 +4226,73 @@
       <c r="L82" s="138"/>
       <c r="M82" s="138"/>
       <c r="N82" s="138"/>
-      <c r="O82" s="139"/>
-      <c r="P82" s="139"/>
+      <c r="O82" s="138"/>
+      <c r="P82" s="138"/>
       <c r="Q82" s="139"/>
       <c r="R82" s="139"/>
-      <c r="S82" s="138"/>
+      <c r="S82" s="139"/>
       <c r="T82" s="139"/>
-    </row>
-    <row r="83" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U82" s="138"/>
+      <c r="V82" s="139"/>
+    </row>
+    <row r="83" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="138"/>
       <c r="C83" s="139"/>
       <c r="D83" s="139"/>
-      <c r="E83" s="138"/>
-      <c r="F83" s="138"/>
-      <c r="G83" s="139"/>
-      <c r="H83" s="139"/>
+      <c r="E83" s="139"/>
+      <c r="F83" s="139"/>
+      <c r="G83" s="138"/>
+      <c r="H83" s="138"/>
       <c r="I83" s="139"/>
       <c r="J83" s="139"/>
       <c r="K83" s="139"/>
       <c r="L83" s="139"/>
       <c r="M83" s="139"/>
       <c r="N83" s="139"/>
-      <c r="O83" s="138"/>
-      <c r="P83" s="138"/>
+      <c r="O83" s="139"/>
+      <c r="P83" s="139"/>
       <c r="Q83" s="138"/>
       <c r="R83" s="138"/>
-      <c r="S83" s="139"/>
-      <c r="T83" s="139"/>
-    </row>
-    <row r="84" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S83" s="138"/>
+      <c r="T83" s="138"/>
+      <c r="U83" s="139"/>
+      <c r="V83" s="139"/>
+    </row>
+    <row r="84" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="139"/>
       <c r="C84" s="139"/>
       <c r="D84" s="139"/>
       <c r="E84" s="139"/>
       <c r="F84" s="139"/>
-      <c r="G84" s="138"/>
-      <c r="H84" s="138"/>
-      <c r="I84" s="139"/>
-      <c r="J84" s="139"/>
+      <c r="G84" s="139"/>
+      <c r="H84" s="139"/>
+      <c r="I84" s="138"/>
+      <c r="J84" s="138"/>
       <c r="K84" s="139"/>
       <c r="L84" s="139"/>
       <c r="M84" s="139"/>
       <c r="N84" s="139"/>
-      <c r="O84" s="138"/>
-      <c r="P84" s="138"/>
+      <c r="O84" s="139"/>
+      <c r="P84" s="139"/>
       <c r="Q84" s="138"/>
       <c r="R84" s="138"/>
-      <c r="S84" s="139"/>
-      <c r="T84" s="139"/>
-    </row>
-    <row r="85" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S84" s="138"/>
+      <c r="T84" s="138"/>
+      <c r="U84" s="139"/>
+      <c r="V84" s="139"/>
+    </row>
+    <row r="85" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="139"/>
       <c r="C85" s="139"/>
       <c r="D85" s="139"/>
-      <c r="E85" s="138"/>
-      <c r="F85" s="138"/>
-      <c r="G85" s="139"/>
-      <c r="H85" s="139"/>
-      <c r="I85" s="138"/>
-      <c r="J85" s="138"/>
-      <c r="K85" s="139"/>
-      <c r="L85" s="139"/>
+      <c r="E85" s="139"/>
+      <c r="F85" s="139"/>
+      <c r="G85" s="138"/>
+      <c r="H85" s="138"/>
+      <c r="I85" s="139"/>
+      <c r="J85" s="139"/>
+      <c r="K85" s="138"/>
+      <c r="L85" s="138"/>
       <c r="M85" s="139"/>
       <c r="N85" s="139"/>
       <c r="O85" s="139"/>
@@ -3684,8 +4301,10 @@
       <c r="R85" s="139"/>
       <c r="S85" s="139"/>
       <c r="T85" s="139"/>
-    </row>
-    <row r="86" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U85" s="139"/>
+      <c r="V85" s="139"/>
+    </row>
+    <row r="86" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="139"/>
       <c r="C86" s="139"/>
       <c r="D86" s="139"/>
@@ -3693,31 +4312,33 @@
       <c r="F86" s="139"/>
       <c r="G86" s="139"/>
       <c r="H86" s="139"/>
-      <c r="I86" s="138"/>
-      <c r="J86" s="138"/>
-      <c r="K86" s="139"/>
-      <c r="L86" s="139"/>
+      <c r="I86" s="139"/>
+      <c r="J86" s="139"/>
+      <c r="K86" s="138"/>
+      <c r="L86" s="138"/>
       <c r="M86" s="139"/>
       <c r="N86" s="139"/>
-      <c r="O86" s="138"/>
-      <c r="P86" s="138"/>
+      <c r="O86" s="139"/>
+      <c r="P86" s="139"/>
       <c r="Q86" s="138"/>
       <c r="R86" s="138"/>
-      <c r="S86" s="139"/>
-      <c r="T86" s="139"/>
-    </row>
-    <row r="87" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S86" s="138"/>
+      <c r="T86" s="138"/>
+      <c r="U86" s="139"/>
+      <c r="V86" s="139"/>
+    </row>
+    <row r="87" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="139"/>
       <c r="C87" s="139"/>
       <c r="D87" s="139"/>
-      <c r="E87" s="138"/>
-      <c r="F87" s="138"/>
-      <c r="G87" s="139"/>
-      <c r="H87" s="139"/>
-      <c r="I87" s="138"/>
-      <c r="J87" s="138"/>
-      <c r="K87" s="139"/>
-      <c r="L87" s="139"/>
+      <c r="E87" s="139"/>
+      <c r="F87" s="139"/>
+      <c r="G87" s="138"/>
+      <c r="H87" s="138"/>
+      <c r="I87" s="139"/>
+      <c r="J87" s="139"/>
+      <c r="K87" s="138"/>
+      <c r="L87" s="138"/>
       <c r="M87" s="139"/>
       <c r="N87" s="139"/>
       <c r="O87" s="139"/>
@@ -3726,8 +4347,10 @@
       <c r="R87" s="139"/>
       <c r="S87" s="139"/>
       <c r="T87" s="139"/>
-    </row>
-    <row r="88" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U87" s="139"/>
+      <c r="V87" s="139"/>
+    </row>
+    <row r="88" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="139"/>
       <c r="C88" s="139"/>
       <c r="D88" s="139"/>
@@ -3735,129 +4358,141 @@
       <c r="F88" s="139"/>
       <c r="G88" s="139"/>
       <c r="H88" s="139"/>
-      <c r="I88" s="138"/>
-      <c r="J88" s="138"/>
-      <c r="K88" s="139"/>
-      <c r="L88" s="139"/>
+      <c r="I88" s="139"/>
+      <c r="J88" s="139"/>
+      <c r="K88" s="138"/>
+      <c r="L88" s="138"/>
       <c r="M88" s="139"/>
       <c r="N88" s="139"/>
-      <c r="O88" s="138"/>
-      <c r="P88" s="138"/>
+      <c r="O88" s="139"/>
+      <c r="P88" s="139"/>
       <c r="Q88" s="138"/>
       <c r="R88" s="138"/>
-      <c r="S88" s="139"/>
-      <c r="T88" s="139"/>
-    </row>
-    <row r="89" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S88" s="138"/>
+      <c r="T88" s="138"/>
+      <c r="U88" s="139"/>
+      <c r="V88" s="139"/>
+    </row>
+    <row r="89" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="139"/>
       <c r="C89" s="139"/>
       <c r="D89" s="139"/>
       <c r="E89" s="139"/>
       <c r="F89" s="139"/>
-      <c r="G89" s="138"/>
-      <c r="H89" s="138"/>
-      <c r="I89" s="139"/>
-      <c r="J89" s="139"/>
+      <c r="G89" s="139"/>
+      <c r="H89" s="139"/>
+      <c r="I89" s="138"/>
+      <c r="J89" s="138"/>
       <c r="K89" s="139"/>
       <c r="L89" s="139"/>
       <c r="M89" s="139"/>
       <c r="N89" s="139"/>
-      <c r="O89" s="138"/>
-      <c r="P89" s="138"/>
+      <c r="O89" s="139"/>
+      <c r="P89" s="139"/>
       <c r="Q89" s="138"/>
       <c r="R89" s="138"/>
-      <c r="S89" s="139"/>
-      <c r="T89" s="139"/>
-    </row>
-    <row r="90" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S89" s="138"/>
+      <c r="T89" s="138"/>
+      <c r="U89" s="139"/>
+      <c r="V89" s="139"/>
+    </row>
+    <row r="90" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="139"/>
       <c r="C90" s="139"/>
       <c r="D90" s="139"/>
       <c r="E90" s="139"/>
       <c r="F90" s="139"/>
-      <c r="G90" s="138"/>
-      <c r="H90" s="138"/>
-      <c r="I90" s="139"/>
-      <c r="J90" s="139"/>
+      <c r="G90" s="139"/>
+      <c r="H90" s="139"/>
+      <c r="I90" s="138"/>
+      <c r="J90" s="138"/>
       <c r="K90" s="139"/>
       <c r="L90" s="139"/>
       <c r="M90" s="139"/>
       <c r="N90" s="139"/>
-      <c r="O90" s="138"/>
-      <c r="P90" s="138"/>
+      <c r="O90" s="139"/>
+      <c r="P90" s="139"/>
       <c r="Q90" s="138"/>
       <c r="R90" s="138"/>
-      <c r="S90" s="139"/>
-      <c r="T90" s="139"/>
-    </row>
-    <row r="91" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S90" s="138"/>
+      <c r="T90" s="138"/>
+      <c r="U90" s="139"/>
+      <c r="V90" s="139"/>
+    </row>
+    <row r="91" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="139"/>
       <c r="C91" s="139"/>
       <c r="D91" s="139"/>
       <c r="E91" s="139"/>
       <c r="F91" s="139"/>
-      <c r="G91" s="138"/>
-      <c r="H91" s="138"/>
-      <c r="I91" s="139"/>
-      <c r="J91" s="139"/>
+      <c r="G91" s="139"/>
+      <c r="H91" s="139"/>
+      <c r="I91" s="138"/>
+      <c r="J91" s="138"/>
       <c r="K91" s="139"/>
       <c r="L91" s="139"/>
       <c r="M91" s="139"/>
       <c r="N91" s="139"/>
-      <c r="O91" s="138"/>
-      <c r="P91" s="138"/>
+      <c r="O91" s="139"/>
+      <c r="P91" s="139"/>
       <c r="Q91" s="138"/>
       <c r="R91" s="138"/>
-      <c r="S91" s="139"/>
-      <c r="T91" s="139"/>
-    </row>
-    <row r="92" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S91" s="138"/>
+      <c r="T91" s="138"/>
+      <c r="U91" s="139"/>
+      <c r="V91" s="139"/>
+    </row>
+    <row r="92" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="139"/>
       <c r="C92" s="139"/>
       <c r="D92" s="139"/>
       <c r="E92" s="139"/>
       <c r="F92" s="139"/>
-      <c r="G92" s="138"/>
-      <c r="H92" s="138"/>
-      <c r="I92" s="139"/>
-      <c r="J92" s="139"/>
+      <c r="G92" s="139"/>
+      <c r="H92" s="139"/>
+      <c r="I92" s="138"/>
+      <c r="J92" s="138"/>
       <c r="K92" s="139"/>
       <c r="L92" s="139"/>
       <c r="M92" s="139"/>
       <c r="N92" s="139"/>
-      <c r="O92" s="138"/>
-      <c r="P92" s="138"/>
+      <c r="O92" s="139"/>
+      <c r="P92" s="139"/>
       <c r="Q92" s="138"/>
       <c r="R92" s="138"/>
-      <c r="S92" s="139"/>
-      <c r="T92" s="139"/>
-    </row>
-    <row r="93" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S92" s="138"/>
+      <c r="T92" s="138"/>
+      <c r="U92" s="139"/>
+      <c r="V92" s="139"/>
+    </row>
+    <row r="93" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="139"/>
       <c r="C93" s="139"/>
       <c r="D93" s="139"/>
-      <c r="E93" s="138"/>
-      <c r="F93" s="138"/>
-      <c r="G93" s="139"/>
-      <c r="H93" s="139"/>
+      <c r="E93" s="139"/>
+      <c r="F93" s="139"/>
+      <c r="G93" s="138"/>
+      <c r="H93" s="138"/>
       <c r="I93" s="139"/>
       <c r="J93" s="139"/>
       <c r="K93" s="139"/>
       <c r="L93" s="139"/>
       <c r="M93" s="139"/>
       <c r="N93" s="139"/>
-      <c r="O93" s="138"/>
-      <c r="P93" s="138"/>
+      <c r="O93" s="139"/>
+      <c r="P93" s="139"/>
       <c r="Q93" s="138"/>
       <c r="R93" s="138"/>
-      <c r="S93" s="139"/>
-      <c r="T93" s="139"/>
-    </row>
-    <row r="94" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S93" s="138"/>
+      <c r="T93" s="138"/>
+      <c r="U93" s="139"/>
+      <c r="V93" s="139"/>
+    </row>
+    <row r="94" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="138"/>
       <c r="C94" s="138"/>
       <c r="D94" s="139"/>
-      <c r="E94" s="138"/>
+      <c r="E94" s="139"/>
       <c r="F94" s="139"/>
       <c r="G94" s="138"/>
       <c r="H94" s="139"/>
@@ -3868,13 +4503,15 @@
       <c r="M94" s="138"/>
       <c r="N94" s="139"/>
       <c r="O94" s="138"/>
-      <c r="P94" s="138"/>
+      <c r="P94" s="139"/>
       <c r="Q94" s="138"/>
       <c r="R94" s="138"/>
       <c r="S94" s="138"/>
       <c r="T94" s="138"/>
-    </row>
-    <row r="95" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U94" s="138"/>
+      <c r="V94" s="138"/>
+    </row>
+    <row r="95" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="138"/>
       <c r="C95" s="139"/>
       <c r="D95" s="139"/>
@@ -3888,14 +4525,16 @@
       <c r="L95" s="139"/>
       <c r="M95" s="139"/>
       <c r="N95" s="139"/>
-      <c r="O95" s="138"/>
-      <c r="P95" s="138"/>
+      <c r="O95" s="139"/>
+      <c r="P95" s="139"/>
       <c r="Q95" s="138"/>
       <c r="R95" s="138"/>
       <c r="S95" s="138"/>
-      <c r="T95" s="139"/>
-    </row>
-    <row r="96" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T95" s="138"/>
+      <c r="U95" s="138"/>
+      <c r="V95" s="139"/>
+    </row>
+    <row r="96" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="138"/>
       <c r="C96" s="138"/>
       <c r="D96" s="138"/>
@@ -3909,25 +4548,27 @@
       <c r="L96" s="138"/>
       <c r="M96" s="138"/>
       <c r="N96" s="138"/>
-      <c r="O96" s="139"/>
-      <c r="P96" s="139"/>
+      <c r="O96" s="138"/>
+      <c r="P96" s="138"/>
       <c r="Q96" s="139"/>
       <c r="R96" s="139"/>
-      <c r="S96" s="138"/>
+      <c r="S96" s="139"/>
       <c r="T96" s="139"/>
-    </row>
-    <row r="97" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U96" s="138"/>
+      <c r="V96" s="139"/>
+    </row>
+    <row r="97" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="138"/>
       <c r="C97" s="139"/>
       <c r="D97" s="139"/>
-      <c r="E97" s="138"/>
-      <c r="F97" s="138"/>
-      <c r="G97" s="139"/>
-      <c r="H97" s="139"/>
-      <c r="I97" s="138"/>
-      <c r="J97" s="138"/>
-      <c r="K97" s="139"/>
-      <c r="L97" s="139"/>
+      <c r="E97" s="139"/>
+      <c r="F97" s="139"/>
+      <c r="G97" s="138"/>
+      <c r="H97" s="138"/>
+      <c r="I97" s="139"/>
+      <c r="J97" s="139"/>
+      <c r="K97" s="138"/>
+      <c r="L97" s="138"/>
       <c r="M97" s="139"/>
       <c r="N97" s="139"/>
       <c r="O97" s="139"/>
@@ -3936,8 +4577,10 @@
       <c r="R97" s="139"/>
       <c r="S97" s="139"/>
       <c r="T97" s="139"/>
-    </row>
-    <row r="98" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U97" s="139"/>
+      <c r="V97" s="139"/>
+    </row>
+    <row r="98" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="139"/>
       <c r="C98" s="139"/>
       <c r="D98" s="139"/>
@@ -3945,52 +4588,56 @@
       <c r="F98" s="139"/>
       <c r="G98" s="139"/>
       <c r="H98" s="139"/>
-      <c r="I98" s="138"/>
-      <c r="J98" s="138"/>
-      <c r="K98" s="139"/>
-      <c r="L98" s="139"/>
+      <c r="I98" s="139"/>
+      <c r="J98" s="139"/>
+      <c r="K98" s="138"/>
+      <c r="L98" s="138"/>
       <c r="M98" s="139"/>
       <c r="N98" s="139"/>
-      <c r="O98" s="138"/>
-      <c r="P98" s="138"/>
+      <c r="O98" s="139"/>
+      <c r="P98" s="139"/>
       <c r="Q98" s="138"/>
       <c r="R98" s="138"/>
-      <c r="S98" s="139"/>
-      <c r="T98" s="139"/>
-    </row>
-    <row r="99" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S98" s="138"/>
+      <c r="T98" s="138"/>
+      <c r="U98" s="139"/>
+      <c r="V98" s="139"/>
+    </row>
+    <row r="99" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="139"/>
       <c r="C99" s="139"/>
       <c r="D99" s="139"/>
-      <c r="E99" s="138"/>
-      <c r="F99" s="138"/>
-      <c r="G99" s="139"/>
-      <c r="H99" s="139"/>
+      <c r="E99" s="139"/>
+      <c r="F99" s="139"/>
+      <c r="G99" s="138"/>
+      <c r="H99" s="138"/>
       <c r="I99" s="139"/>
       <c r="J99" s="139"/>
       <c r="K99" s="139"/>
       <c r="L99" s="139"/>
       <c r="M99" s="139"/>
       <c r="N99" s="139"/>
-      <c r="O99" s="138"/>
-      <c r="P99" s="138"/>
+      <c r="O99" s="139"/>
+      <c r="P99" s="139"/>
       <c r="Q99" s="138"/>
       <c r="R99" s="138"/>
-      <c r="S99" s="139"/>
-      <c r="T99" s="139"/>
-    </row>
-    <row r="100" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S99" s="138"/>
+      <c r="T99" s="138"/>
+      <c r="U99" s="139"/>
+      <c r="V99" s="139"/>
+    </row>
+    <row r="100" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="139"/>
       <c r="C100" s="139"/>
       <c r="D100" s="139"/>
-      <c r="E100" s="138"/>
-      <c r="F100" s="138"/>
-      <c r="G100" s="139"/>
-      <c r="H100" s="139"/>
-      <c r="I100" s="138"/>
-      <c r="J100" s="138"/>
-      <c r="K100" s="139"/>
-      <c r="L100" s="139"/>
+      <c r="E100" s="139"/>
+      <c r="F100" s="139"/>
+      <c r="G100" s="138"/>
+      <c r="H100" s="138"/>
+      <c r="I100" s="139"/>
+      <c r="J100" s="139"/>
+      <c r="K100" s="138"/>
+      <c r="L100" s="138"/>
       <c r="M100" s="139"/>
       <c r="N100" s="139"/>
       <c r="O100" s="139"/>
@@ -3999,8 +4646,10 @@
       <c r="R100" s="139"/>
       <c r="S100" s="139"/>
       <c r="T100" s="139"/>
-    </row>
-    <row r="101" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U100" s="139"/>
+      <c r="V100" s="139"/>
+    </row>
+    <row r="101" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="139"/>
       <c r="C101" s="139"/>
       <c r="D101" s="139"/>
@@ -4008,24 +4657,26 @@
       <c r="F101" s="139"/>
       <c r="G101" s="139"/>
       <c r="H101" s="139"/>
-      <c r="I101" s="138"/>
-      <c r="J101" s="138"/>
-      <c r="K101" s="139"/>
-      <c r="L101" s="139"/>
+      <c r="I101" s="139"/>
+      <c r="J101" s="139"/>
+      <c r="K101" s="138"/>
+      <c r="L101" s="138"/>
       <c r="M101" s="139"/>
       <c r="N101" s="139"/>
-      <c r="O101" s="138"/>
-      <c r="P101" s="138"/>
+      <c r="O101" s="139"/>
+      <c r="P101" s="139"/>
       <c r="Q101" s="138"/>
       <c r="R101" s="138"/>
-      <c r="S101" s="139"/>
-      <c r="T101" s="139"/>
-    </row>
-    <row r="102" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S101" s="138"/>
+      <c r="T101" s="138"/>
+      <c r="U101" s="139"/>
+      <c r="V101" s="139"/>
+    </row>
+    <row r="102" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="138"/>
       <c r="C102" s="138"/>
       <c r="D102" s="139"/>
-      <c r="E102" s="138"/>
+      <c r="E102" s="139"/>
       <c r="F102" s="139"/>
       <c r="G102" s="138"/>
       <c r="H102" s="139"/>
@@ -4036,13 +4687,15 @@
       <c r="M102" s="138"/>
       <c r="N102" s="139"/>
       <c r="O102" s="138"/>
-      <c r="P102" s="138"/>
+      <c r="P102" s="139"/>
       <c r="Q102" s="138"/>
       <c r="R102" s="138"/>
       <c r="S102" s="138"/>
       <c r="T102" s="138"/>
-    </row>
-    <row r="103" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U102" s="138"/>
+      <c r="V102" s="138"/>
+    </row>
+    <row r="103" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="138"/>
       <c r="C103" s="139"/>
       <c r="D103" s="139"/>
@@ -4056,67 +4709,73 @@
       <c r="L103" s="139"/>
       <c r="M103" s="139"/>
       <c r="N103" s="139"/>
-      <c r="O103" s="138"/>
-      <c r="P103" s="138"/>
+      <c r="O103" s="139"/>
+      <c r="P103" s="139"/>
       <c r="Q103" s="138"/>
       <c r="R103" s="138"/>
       <c r="S103" s="138"/>
-      <c r="T103" s="139"/>
-    </row>
-    <row r="104" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T103" s="138"/>
+      <c r="U103" s="138"/>
+      <c r="V103" s="139"/>
+    </row>
+    <row r="104" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="138"/>
       <c r="C104" s="139"/>
       <c r="D104" s="139"/>
       <c r="E104" s="139"/>
       <c r="F104" s="139"/>
-      <c r="G104" s="138"/>
-      <c r="H104" s="138"/>
-      <c r="I104" s="139"/>
-      <c r="J104" s="139"/>
+      <c r="G104" s="139"/>
+      <c r="H104" s="139"/>
+      <c r="I104" s="138"/>
+      <c r="J104" s="138"/>
       <c r="K104" s="139"/>
       <c r="L104" s="139"/>
       <c r="M104" s="139"/>
       <c r="N104" s="139"/>
-      <c r="O104" s="138"/>
-      <c r="P104" s="138"/>
+      <c r="O104" s="139"/>
+      <c r="P104" s="139"/>
       <c r="Q104" s="138"/>
       <c r="R104" s="138"/>
-      <c r="S104" s="139"/>
-      <c r="T104" s="139"/>
-    </row>
-    <row r="105" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S104" s="138"/>
+      <c r="T104" s="138"/>
+      <c r="U104" s="139"/>
+      <c r="V104" s="139"/>
+    </row>
+    <row r="105" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="139"/>
       <c r="C105" s="139"/>
       <c r="D105" s="139"/>
       <c r="E105" s="139"/>
       <c r="F105" s="139"/>
-      <c r="G105" s="138"/>
-      <c r="H105" s="138"/>
-      <c r="I105" s="139"/>
-      <c r="J105" s="139"/>
+      <c r="G105" s="139"/>
+      <c r="H105" s="139"/>
+      <c r="I105" s="138"/>
+      <c r="J105" s="138"/>
       <c r="K105" s="139"/>
       <c r="L105" s="139"/>
       <c r="M105" s="139"/>
       <c r="N105" s="139"/>
-      <c r="O105" s="138"/>
-      <c r="P105" s="138"/>
+      <c r="O105" s="139"/>
+      <c r="P105" s="139"/>
       <c r="Q105" s="138"/>
       <c r="R105" s="138"/>
-      <c r="S105" s="139"/>
-      <c r="T105" s="139"/>
-    </row>
-    <row r="106" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S105" s="138"/>
+      <c r="T105" s="138"/>
+      <c r="U105" s="139"/>
+      <c r="V105" s="139"/>
+    </row>
+    <row r="106" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="139"/>
       <c r="C106" s="139"/>
       <c r="D106" s="139"/>
-      <c r="E106" s="138"/>
-      <c r="F106" s="138"/>
-      <c r="G106" s="139"/>
-      <c r="H106" s="139"/>
-      <c r="I106" s="138"/>
-      <c r="J106" s="138"/>
-      <c r="K106" s="139"/>
-      <c r="L106" s="139"/>
+      <c r="E106" s="139"/>
+      <c r="F106" s="139"/>
+      <c r="G106" s="138"/>
+      <c r="H106" s="138"/>
+      <c r="I106" s="139"/>
+      <c r="J106" s="139"/>
+      <c r="K106" s="138"/>
+      <c r="L106" s="138"/>
       <c r="M106" s="139"/>
       <c r="N106" s="139"/>
       <c r="O106" s="139"/>
@@ -4125,8 +4784,10 @@
       <c r="R106" s="139"/>
       <c r="S106" s="139"/>
       <c r="T106" s="139"/>
-    </row>
-    <row r="107" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U106" s="139"/>
+      <c r="V106" s="139"/>
+    </row>
+    <row r="107" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="139"/>
       <c r="C107" s="139"/>
       <c r="D107" s="139"/>
@@ -4134,52 +4795,56 @@
       <c r="F107" s="139"/>
       <c r="G107" s="139"/>
       <c r="H107" s="139"/>
-      <c r="I107" s="138"/>
-      <c r="J107" s="138"/>
-      <c r="K107" s="139"/>
-      <c r="L107" s="139"/>
+      <c r="I107" s="139"/>
+      <c r="J107" s="139"/>
+      <c r="K107" s="138"/>
+      <c r="L107" s="138"/>
       <c r="M107" s="139"/>
       <c r="N107" s="139"/>
-      <c r="O107" s="138"/>
-      <c r="P107" s="138"/>
+      <c r="O107" s="139"/>
+      <c r="P107" s="139"/>
       <c r="Q107" s="138"/>
       <c r="R107" s="138"/>
-      <c r="S107" s="139"/>
-      <c r="T107" s="139"/>
-    </row>
-    <row r="108" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S107" s="138"/>
+      <c r="T107" s="138"/>
+      <c r="U107" s="139"/>
+      <c r="V107" s="139"/>
+    </row>
+    <row r="108" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="139"/>
       <c r="C108" s="139"/>
       <c r="D108" s="139"/>
-      <c r="E108" s="138"/>
-      <c r="F108" s="138"/>
-      <c r="G108" s="139"/>
-      <c r="H108" s="139"/>
+      <c r="E108" s="139"/>
+      <c r="F108" s="139"/>
+      <c r="G108" s="138"/>
+      <c r="H108" s="138"/>
       <c r="I108" s="139"/>
       <c r="J108" s="139"/>
-      <c r="K108" s="138"/>
-      <c r="L108" s="138"/>
-      <c r="M108" s="139"/>
-      <c r="N108" s="139"/>
+      <c r="K108" s="139"/>
+      <c r="L108" s="139"/>
+      <c r="M108" s="138"/>
+      <c r="N108" s="138"/>
       <c r="O108" s="139"/>
       <c r="P108" s="139"/>
       <c r="Q108" s="139"/>
       <c r="R108" s="139"/>
       <c r="S108" s="139"/>
       <c r="T108" s="139"/>
-    </row>
-    <row r="109" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U108" s="139"/>
+      <c r="V108" s="139"/>
+    </row>
+    <row r="109" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="139"/>
       <c r="C109" s="139"/>
       <c r="D109" s="139"/>
-      <c r="E109" s="138"/>
-      <c r="F109" s="138"/>
-      <c r="G109" s="139"/>
-      <c r="H109" s="139"/>
-      <c r="I109" s="138"/>
-      <c r="J109" s="138"/>
-      <c r="K109" s="139"/>
-      <c r="L109" s="139"/>
+      <c r="E109" s="139"/>
+      <c r="F109" s="139"/>
+      <c r="G109" s="138"/>
+      <c r="H109" s="138"/>
+      <c r="I109" s="139"/>
+      <c r="J109" s="139"/>
+      <c r="K109" s="138"/>
+      <c r="L109" s="138"/>
       <c r="M109" s="139"/>
       <c r="N109" s="139"/>
       <c r="O109" s="139"/>
@@ -4188,8 +4853,10 @@
       <c r="R109" s="139"/>
       <c r="S109" s="139"/>
       <c r="T109" s="139"/>
-    </row>
-    <row r="110" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U109" s="139"/>
+      <c r="V109" s="139"/>
+    </row>
+    <row r="110" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="139"/>
       <c r="C110" s="139"/>
       <c r="D110" s="139"/>
@@ -4197,45 +4864,49 @@
       <c r="F110" s="139"/>
       <c r="G110" s="139"/>
       <c r="H110" s="139"/>
-      <c r="I110" s="138"/>
-      <c r="J110" s="138"/>
-      <c r="K110" s="139"/>
-      <c r="L110" s="139"/>
+      <c r="I110" s="139"/>
+      <c r="J110" s="139"/>
+      <c r="K110" s="138"/>
+      <c r="L110" s="138"/>
       <c r="M110" s="139"/>
       <c r="N110" s="139"/>
-      <c r="O110" s="138"/>
-      <c r="P110" s="138"/>
+      <c r="O110" s="139"/>
+      <c r="P110" s="139"/>
       <c r="Q110" s="138"/>
       <c r="R110" s="138"/>
-      <c r="S110" s="139"/>
-      <c r="T110" s="139"/>
-    </row>
-    <row r="111" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S110" s="138"/>
+      <c r="T110" s="138"/>
+      <c r="U110" s="139"/>
+      <c r="V110" s="139"/>
+    </row>
+    <row r="111" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="139"/>
       <c r="C111" s="139"/>
       <c r="D111" s="139"/>
       <c r="E111" s="139"/>
       <c r="F111" s="139"/>
-      <c r="G111" s="138"/>
-      <c r="H111" s="138"/>
-      <c r="I111" s="139"/>
-      <c r="J111" s="139"/>
+      <c r="G111" s="139"/>
+      <c r="H111" s="139"/>
+      <c r="I111" s="138"/>
+      <c r="J111" s="138"/>
       <c r="K111" s="139"/>
       <c r="L111" s="139"/>
       <c r="M111" s="139"/>
       <c r="N111" s="139"/>
-      <c r="O111" s="138"/>
-      <c r="P111" s="138"/>
+      <c r="O111" s="139"/>
+      <c r="P111" s="139"/>
       <c r="Q111" s="138"/>
       <c r="R111" s="138"/>
-      <c r="S111" s="139"/>
-      <c r="T111" s="139"/>
-    </row>
-    <row r="112" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S111" s="138"/>
+      <c r="T111" s="138"/>
+      <c r="U111" s="139"/>
+      <c r="V111" s="139"/>
+    </row>
+    <row r="112" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" s="138"/>
       <c r="C112" s="138"/>
       <c r="D112" s="139"/>
-      <c r="E112" s="138"/>
+      <c r="E112" s="139"/>
       <c r="F112" s="139"/>
       <c r="G112" s="138"/>
       <c r="H112" s="139"/>
@@ -4246,13 +4917,15 @@
       <c r="M112" s="138"/>
       <c r="N112" s="139"/>
       <c r="O112" s="138"/>
-      <c r="P112" s="138"/>
+      <c r="P112" s="139"/>
       <c r="Q112" s="138"/>
       <c r="R112" s="138"/>
       <c r="S112" s="138"/>
       <c r="T112" s="138"/>
-    </row>
-    <row r="113" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U112" s="138"/>
+      <c r="V112" s="138"/>
+    </row>
+    <row r="113" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B113" s="138"/>
       <c r="C113" s="139"/>
       <c r="D113" s="139"/>
@@ -4266,14 +4939,16 @@
       <c r="L113" s="139"/>
       <c r="M113" s="139"/>
       <c r="N113" s="139"/>
-      <c r="O113" s="138"/>
-      <c r="P113" s="138"/>
+      <c r="O113" s="139"/>
+      <c r="P113" s="139"/>
       <c r="Q113" s="138"/>
       <c r="R113" s="138"/>
       <c r="S113" s="138"/>
-      <c r="T113" s="139"/>
-    </row>
-    <row r="114" spans="2:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T113" s="138"/>
+      <c r="U113" s="138"/>
+      <c r="V113" s="139"/>
+    </row>
+    <row r="114" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B114" s="138"/>
       <c r="C114" s="138"/>
       <c r="D114" s="138"/>
@@ -4287,14 +4962,16 @@
       <c r="L114" s="138"/>
       <c r="M114" s="138"/>
       <c r="N114" s="138"/>
-      <c r="O114" s="139"/>
-      <c r="P114" s="139"/>
+      <c r="O114" s="138"/>
+      <c r="P114" s="138"/>
       <c r="Q114" s="139"/>
       <c r="R114" s="139"/>
-      <c r="S114" s="138"/>
+      <c r="S114" s="139"/>
       <c r="T114" s="139"/>
-    </row>
-    <row r="115" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U114" s="138"/>
+      <c r="V114" s="139"/>
+    </row>
+    <row r="115" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B115" s="138"/>
       <c r="C115" s="139"/>
       <c r="D115" s="139"/>
@@ -4304,71 +4981,77 @@
       <c r="H115" s="139"/>
       <c r="I115" s="139"/>
       <c r="J115" s="139"/>
-      <c r="K115" s="138"/>
-      <c r="L115" s="138"/>
-      <c r="M115" s="139"/>
-      <c r="N115" s="139"/>
-      <c r="O115" s="138"/>
-      <c r="P115" s="138"/>
+      <c r="K115" s="139"/>
+      <c r="L115" s="139"/>
+      <c r="M115" s="138"/>
+      <c r="N115" s="138"/>
+      <c r="O115" s="139"/>
+      <c r="P115" s="139"/>
       <c r="Q115" s="138"/>
       <c r="R115" s="138"/>
-      <c r="S115" s="139"/>
-      <c r="T115" s="139"/>
-    </row>
-    <row r="116" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S115" s="138"/>
+      <c r="T115" s="138"/>
+      <c r="U115" s="139"/>
+      <c r="V115" s="139"/>
+    </row>
+    <row r="116" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B116" s="139"/>
       <c r="C116" s="139"/>
       <c r="D116" s="139"/>
       <c r="E116" s="139"/>
       <c r="F116" s="139"/>
-      <c r="G116" s="138"/>
-      <c r="H116" s="138"/>
-      <c r="I116" s="139"/>
-      <c r="J116" s="139"/>
+      <c r="G116" s="139"/>
+      <c r="H116" s="139"/>
+      <c r="I116" s="138"/>
+      <c r="J116" s="138"/>
       <c r="K116" s="139"/>
       <c r="L116" s="139"/>
       <c r="M116" s="139"/>
       <c r="N116" s="139"/>
-      <c r="O116" s="138"/>
-      <c r="P116" s="138"/>
+      <c r="O116" s="139"/>
+      <c r="P116" s="139"/>
       <c r="Q116" s="138"/>
       <c r="R116" s="138"/>
-      <c r="S116" s="139"/>
-      <c r="T116" s="139"/>
-    </row>
-    <row r="117" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S116" s="138"/>
+      <c r="T116" s="138"/>
+      <c r="U116" s="139"/>
+      <c r="V116" s="139"/>
+    </row>
+    <row r="117" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B117" s="139"/>
       <c r="C117" s="139"/>
       <c r="D117" s="139"/>
       <c r="E117" s="139"/>
       <c r="F117" s="139"/>
-      <c r="G117" s="138"/>
-      <c r="H117" s="138"/>
-      <c r="I117" s="139"/>
-      <c r="J117" s="139"/>
+      <c r="G117" s="139"/>
+      <c r="H117" s="139"/>
+      <c r="I117" s="138"/>
+      <c r="J117" s="138"/>
       <c r="K117" s="139"/>
       <c r="L117" s="139"/>
       <c r="M117" s="139"/>
       <c r="N117" s="139"/>
-      <c r="O117" s="138"/>
-      <c r="P117" s="138"/>
+      <c r="O117" s="139"/>
+      <c r="P117" s="139"/>
       <c r="Q117" s="138"/>
       <c r="R117" s="138"/>
-      <c r="S117" s="139"/>
-      <c r="T117" s="139"/>
-    </row>
-    <row r="118" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S117" s="138"/>
+      <c r="T117" s="138"/>
+      <c r="U117" s="139"/>
+      <c r="V117" s="139"/>
+    </row>
+    <row r="118" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B118" s="139"/>
       <c r="C118" s="139"/>
       <c r="D118" s="139"/>
-      <c r="E118" s="138"/>
-      <c r="F118" s="138"/>
-      <c r="G118" s="139"/>
-      <c r="H118" s="139"/>
-      <c r="I118" s="138"/>
-      <c r="J118" s="138"/>
-      <c r="K118" s="139"/>
-      <c r="L118" s="139"/>
+      <c r="E118" s="139"/>
+      <c r="F118" s="139"/>
+      <c r="G118" s="138"/>
+      <c r="H118" s="138"/>
+      <c r="I118" s="139"/>
+      <c r="J118" s="139"/>
+      <c r="K118" s="138"/>
+      <c r="L118" s="138"/>
       <c r="M118" s="139"/>
       <c r="N118" s="139"/>
       <c r="O118" s="139"/>
@@ -4377,8 +5060,10 @@
       <c r="R118" s="139"/>
       <c r="S118" s="139"/>
       <c r="T118" s="139"/>
-    </row>
-    <row r="119" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U118" s="139"/>
+      <c r="V118" s="139"/>
+    </row>
+    <row r="119" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B119" s="139"/>
       <c r="C119" s="139"/>
       <c r="D119" s="139"/>
@@ -4386,31 +5071,33 @@
       <c r="F119" s="139"/>
       <c r="G119" s="139"/>
       <c r="H119" s="139"/>
-      <c r="I119" s="138"/>
-      <c r="J119" s="138"/>
-      <c r="K119" s="139"/>
-      <c r="L119" s="139"/>
+      <c r="I119" s="139"/>
+      <c r="J119" s="139"/>
+      <c r="K119" s="138"/>
+      <c r="L119" s="138"/>
       <c r="M119" s="139"/>
       <c r="N119" s="139"/>
-      <c r="O119" s="138"/>
-      <c r="P119" s="138"/>
+      <c r="O119" s="139"/>
+      <c r="P119" s="139"/>
       <c r="Q119" s="138"/>
       <c r="R119" s="138"/>
-      <c r="S119" s="139"/>
-      <c r="T119" s="139"/>
-    </row>
-    <row r="120" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S119" s="138"/>
+      <c r="T119" s="138"/>
+      <c r="U119" s="139"/>
+      <c r="V119" s="139"/>
+    </row>
+    <row r="120" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B120" s="139"/>
       <c r="C120" s="139"/>
       <c r="D120" s="139"/>
-      <c r="E120" s="138"/>
-      <c r="F120" s="138"/>
-      <c r="G120" s="139"/>
-      <c r="H120" s="139"/>
-      <c r="I120" s="138"/>
-      <c r="J120" s="138"/>
-      <c r="K120" s="139"/>
-      <c r="L120" s="139"/>
+      <c r="E120" s="139"/>
+      <c r="F120" s="139"/>
+      <c r="G120" s="138"/>
+      <c r="H120" s="138"/>
+      <c r="I120" s="139"/>
+      <c r="J120" s="139"/>
+      <c r="K120" s="138"/>
+      <c r="L120" s="138"/>
       <c r="M120" s="139"/>
       <c r="N120" s="139"/>
       <c r="O120" s="139"/>
@@ -4419,8 +5106,10 @@
       <c r="R120" s="139"/>
       <c r="S120" s="139"/>
       <c r="T120" s="139"/>
-    </row>
-    <row r="121" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U120" s="139"/>
+      <c r="V120" s="139"/>
+    </row>
+    <row r="121" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B121" s="139"/>
       <c r="C121" s="139"/>
       <c r="D121" s="139"/>
@@ -4428,94 +5117,102 @@
       <c r="F121" s="139"/>
       <c r="G121" s="139"/>
       <c r="H121" s="139"/>
-      <c r="I121" s="138"/>
-      <c r="J121" s="138"/>
-      <c r="K121" s="139"/>
-      <c r="L121" s="139"/>
+      <c r="I121" s="139"/>
+      <c r="J121" s="139"/>
+      <c r="K121" s="138"/>
+      <c r="L121" s="138"/>
       <c r="M121" s="139"/>
       <c r="N121" s="139"/>
-      <c r="O121" s="138"/>
-      <c r="P121" s="138"/>
+      <c r="O121" s="139"/>
+      <c r="P121" s="139"/>
       <c r="Q121" s="138"/>
       <c r="R121" s="138"/>
-      <c r="S121" s="139"/>
-      <c r="T121" s="139"/>
-    </row>
-    <row r="122" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S121" s="138"/>
+      <c r="T121" s="138"/>
+      <c r="U121" s="139"/>
+      <c r="V121" s="139"/>
+    </row>
+    <row r="122" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B122" s="139"/>
       <c r="C122" s="139"/>
       <c r="D122" s="139"/>
       <c r="E122" s="139"/>
       <c r="F122" s="139"/>
-      <c r="G122" s="138"/>
-      <c r="H122" s="138"/>
-      <c r="I122" s="139"/>
-      <c r="J122" s="139"/>
+      <c r="G122" s="139"/>
+      <c r="H122" s="139"/>
+      <c r="I122" s="138"/>
+      <c r="J122" s="138"/>
       <c r="K122" s="139"/>
       <c r="L122" s="139"/>
       <c r="M122" s="139"/>
       <c r="N122" s="139"/>
-      <c r="O122" s="138"/>
-      <c r="P122" s="138"/>
+      <c r="O122" s="139"/>
+      <c r="P122" s="139"/>
       <c r="Q122" s="138"/>
       <c r="R122" s="138"/>
-      <c r="S122" s="139"/>
-      <c r="T122" s="139"/>
-    </row>
-    <row r="123" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S122" s="138"/>
+      <c r="T122" s="138"/>
+      <c r="U122" s="139"/>
+      <c r="V122" s="139"/>
+    </row>
+    <row r="123" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B123" s="139"/>
       <c r="C123" s="139"/>
       <c r="D123" s="139"/>
       <c r="E123" s="139"/>
       <c r="F123" s="139"/>
-      <c r="G123" s="138"/>
-      <c r="H123" s="138"/>
-      <c r="I123" s="139"/>
-      <c r="J123" s="139"/>
+      <c r="G123" s="139"/>
+      <c r="H123" s="139"/>
+      <c r="I123" s="138"/>
+      <c r="J123" s="138"/>
       <c r="K123" s="139"/>
       <c r="L123" s="139"/>
       <c r="M123" s="139"/>
       <c r="N123" s="139"/>
-      <c r="O123" s="138"/>
-      <c r="P123" s="138"/>
+      <c r="O123" s="139"/>
+      <c r="P123" s="139"/>
       <c r="Q123" s="138"/>
       <c r="R123" s="138"/>
-      <c r="S123" s="139"/>
-      <c r="T123" s="139"/>
-    </row>
-    <row r="124" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S123" s="138"/>
+      <c r="T123" s="138"/>
+      <c r="U123" s="139"/>
+      <c r="V123" s="139"/>
+    </row>
+    <row r="124" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B124" s="139"/>
       <c r="C124" s="139"/>
       <c r="D124" s="139"/>
-      <c r="E124" s="138"/>
-      <c r="F124" s="138"/>
-      <c r="G124" s="139"/>
-      <c r="H124" s="139"/>
+      <c r="E124" s="139"/>
+      <c r="F124" s="139"/>
+      <c r="G124" s="138"/>
+      <c r="H124" s="138"/>
       <c r="I124" s="139"/>
       <c r="J124" s="139"/>
       <c r="K124" s="139"/>
       <c r="L124" s="139"/>
       <c r="M124" s="139"/>
       <c r="N124" s="139"/>
-      <c r="O124" s="138"/>
-      <c r="P124" s="138"/>
+      <c r="O124" s="139"/>
+      <c r="P124" s="139"/>
       <c r="Q124" s="138"/>
       <c r="R124" s="138"/>
-      <c r="S124" s="139"/>
-      <c r="T124" s="139"/>
-    </row>
-    <row r="125" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S124" s="138"/>
+      <c r="T124" s="138"/>
+      <c r="U124" s="139"/>
+      <c r="V124" s="139"/>
+    </row>
+    <row r="125" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B125" s="139"/>
       <c r="C125" s="139"/>
       <c r="D125" s="139"/>
-      <c r="E125" s="138"/>
-      <c r="F125" s="138"/>
-      <c r="G125" s="139"/>
-      <c r="H125" s="139"/>
-      <c r="I125" s="138"/>
-      <c r="J125" s="138"/>
-      <c r="K125" s="139"/>
-      <c r="L125" s="139"/>
+      <c r="E125" s="139"/>
+      <c r="F125" s="139"/>
+      <c r="G125" s="138"/>
+      <c r="H125" s="138"/>
+      <c r="I125" s="139"/>
+      <c r="J125" s="139"/>
+      <c r="K125" s="138"/>
+      <c r="L125" s="138"/>
       <c r="M125" s="139"/>
       <c r="N125" s="139"/>
       <c r="O125" s="139"/>
@@ -4524,8 +5221,10 @@
       <c r="R125" s="139"/>
       <c r="S125" s="139"/>
       <c r="T125" s="139"/>
-    </row>
-    <row r="126" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U125" s="139"/>
+      <c r="V125" s="139"/>
+    </row>
+    <row r="126" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B126" s="139"/>
       <c r="C126" s="139"/>
       <c r="D126" s="139"/>
@@ -4533,24 +5232,26 @@
       <c r="F126" s="139"/>
       <c r="G126" s="139"/>
       <c r="H126" s="139"/>
-      <c r="I126" s="138"/>
-      <c r="J126" s="138"/>
-      <c r="K126" s="139"/>
-      <c r="L126" s="139"/>
+      <c r="I126" s="139"/>
+      <c r="J126" s="139"/>
+      <c r="K126" s="138"/>
+      <c r="L126" s="138"/>
       <c r="M126" s="139"/>
       <c r="N126" s="139"/>
-      <c r="O126" s="138"/>
-      <c r="P126" s="138"/>
+      <c r="O126" s="139"/>
+      <c r="P126" s="139"/>
       <c r="Q126" s="138"/>
       <c r="R126" s="138"/>
-      <c r="S126" s="139"/>
-      <c r="T126" s="139"/>
-    </row>
-    <row r="127" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S126" s="138"/>
+      <c r="T126" s="138"/>
+      <c r="U126" s="139"/>
+      <c r="V126" s="139"/>
+    </row>
+    <row r="127" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B127" s="138"/>
       <c r="C127" s="138"/>
       <c r="D127" s="139"/>
-      <c r="E127" s="138"/>
+      <c r="E127" s="139"/>
       <c r="F127" s="139"/>
       <c r="G127" s="138"/>
       <c r="H127" s="139"/>
@@ -4561,13 +5262,15 @@
       <c r="M127" s="138"/>
       <c r="N127" s="139"/>
       <c r="O127" s="138"/>
-      <c r="P127" s="138"/>
+      <c r="P127" s="139"/>
       <c r="Q127" s="138"/>
       <c r="R127" s="138"/>
       <c r="S127" s="138"/>
       <c r="T127" s="138"/>
-    </row>
-    <row r="128" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U127" s="138"/>
+      <c r="V127" s="138"/>
+    </row>
+    <row r="128" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B128" s="138"/>
       <c r="C128" s="139"/>
       <c r="D128" s="139"/>
@@ -4581,46 +5284,50 @@
       <c r="L128" s="139"/>
       <c r="M128" s="139"/>
       <c r="N128" s="139"/>
-      <c r="O128" s="138"/>
-      <c r="P128" s="138"/>
+      <c r="O128" s="139"/>
+      <c r="P128" s="139"/>
       <c r="Q128" s="138"/>
       <c r="R128" s="138"/>
       <c r="S128" s="138"/>
-      <c r="T128" s="139"/>
-    </row>
-    <row r="129" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="T128" s="138"/>
+      <c r="U128" s="138"/>
+      <c r="V128" s="139"/>
+    </row>
+    <row r="129" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B129" s="138"/>
       <c r="C129" s="139"/>
       <c r="D129" s="139"/>
       <c r="E129" s="139"/>
       <c r="F129" s="139"/>
-      <c r="G129" s="138"/>
-      <c r="H129" s="138"/>
-      <c r="I129" s="139"/>
-      <c r="J129" s="139"/>
+      <c r="G129" s="139"/>
+      <c r="H129" s="139"/>
+      <c r="I129" s="138"/>
+      <c r="J129" s="138"/>
       <c r="K129" s="139"/>
       <c r="L129" s="139"/>
       <c r="M129" s="139"/>
       <c r="N129" s="139"/>
-      <c r="O129" s="138"/>
-      <c r="P129" s="138"/>
+      <c r="O129" s="139"/>
+      <c r="P129" s="139"/>
       <c r="Q129" s="138"/>
       <c r="R129" s="138"/>
-      <c r="S129" s="139"/>
-      <c r="T129" s="139"/>
-    </row>
-    <row r="130" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S129" s="138"/>
+      <c r="T129" s="138"/>
+      <c r="U129" s="139"/>
+      <c r="V129" s="139"/>
+    </row>
+    <row r="130" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B130" s="139"/>
       <c r="C130" s="139"/>
       <c r="D130" s="139"/>
-      <c r="E130" s="138"/>
-      <c r="F130" s="138"/>
-      <c r="G130" s="139"/>
-      <c r="H130" s="139"/>
-      <c r="I130" s="138"/>
-      <c r="J130" s="138"/>
-      <c r="K130" s="139"/>
-      <c r="L130" s="139"/>
+      <c r="E130" s="139"/>
+      <c r="F130" s="139"/>
+      <c r="G130" s="138"/>
+      <c r="H130" s="138"/>
+      <c r="I130" s="139"/>
+      <c r="J130" s="139"/>
+      <c r="K130" s="138"/>
+      <c r="L130" s="138"/>
       <c r="M130" s="139"/>
       <c r="N130" s="139"/>
       <c r="O130" s="139"/>
@@ -4629,8 +5336,10 @@
       <c r="R130" s="139"/>
       <c r="S130" s="139"/>
       <c r="T130" s="139"/>
-    </row>
-    <row r="131" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U130" s="139"/>
+      <c r="V130" s="139"/>
+    </row>
+    <row r="131" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B131" s="139"/>
       <c r="C131" s="139"/>
       <c r="D131" s="139"/>
@@ -4638,129 +5347,141 @@
       <c r="F131" s="139"/>
       <c r="G131" s="139"/>
       <c r="H131" s="139"/>
-      <c r="I131" s="138"/>
-      <c r="J131" s="138"/>
-      <c r="K131" s="139"/>
-      <c r="L131" s="139"/>
+      <c r="I131" s="139"/>
+      <c r="J131" s="139"/>
+      <c r="K131" s="138"/>
+      <c r="L131" s="138"/>
       <c r="M131" s="139"/>
       <c r="N131" s="139"/>
-      <c r="O131" s="138"/>
-      <c r="P131" s="138"/>
+      <c r="O131" s="139"/>
+      <c r="P131" s="139"/>
       <c r="Q131" s="138"/>
       <c r="R131" s="138"/>
-      <c r="S131" s="139"/>
-      <c r="T131" s="139"/>
-    </row>
-    <row r="132" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S131" s="138"/>
+      <c r="T131" s="138"/>
+      <c r="U131" s="139"/>
+      <c r="V131" s="139"/>
+    </row>
+    <row r="132" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B132" s="139"/>
       <c r="C132" s="139"/>
       <c r="D132" s="139"/>
       <c r="E132" s="139"/>
       <c r="F132" s="139"/>
-      <c r="G132" s="138"/>
-      <c r="H132" s="138"/>
-      <c r="I132" s="139"/>
-      <c r="J132" s="139"/>
+      <c r="G132" s="139"/>
+      <c r="H132" s="139"/>
+      <c r="I132" s="138"/>
+      <c r="J132" s="138"/>
       <c r="K132" s="139"/>
       <c r="L132" s="139"/>
       <c r="M132" s="139"/>
       <c r="N132" s="139"/>
-      <c r="O132" s="138"/>
-      <c r="P132" s="138"/>
+      <c r="O132" s="139"/>
+      <c r="P132" s="139"/>
       <c r="Q132" s="138"/>
       <c r="R132" s="138"/>
-      <c r="S132" s="139"/>
-      <c r="T132" s="139"/>
-    </row>
-    <row r="133" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S132" s="138"/>
+      <c r="T132" s="138"/>
+      <c r="U132" s="139"/>
+      <c r="V132" s="139"/>
+    </row>
+    <row r="133" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B133" s="139"/>
       <c r="C133" s="139"/>
       <c r="D133" s="139"/>
       <c r="E133" s="139"/>
       <c r="F133" s="139"/>
-      <c r="G133" s="138"/>
-      <c r="H133" s="138"/>
-      <c r="I133" s="139"/>
-      <c r="J133" s="139"/>
+      <c r="G133" s="139"/>
+      <c r="H133" s="139"/>
+      <c r="I133" s="138"/>
+      <c r="J133" s="138"/>
       <c r="K133" s="139"/>
       <c r="L133" s="139"/>
       <c r="M133" s="139"/>
       <c r="N133" s="139"/>
-      <c r="O133" s="138"/>
-      <c r="P133" s="138"/>
+      <c r="O133" s="139"/>
+      <c r="P133" s="139"/>
       <c r="Q133" s="138"/>
       <c r="R133" s="138"/>
-      <c r="S133" s="139"/>
-      <c r="T133" s="139"/>
-    </row>
-    <row r="134" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S133" s="138"/>
+      <c r="T133" s="138"/>
+      <c r="U133" s="139"/>
+      <c r="V133" s="139"/>
+    </row>
+    <row r="134" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B134" s="139"/>
       <c r="C134" s="139"/>
       <c r="D134" s="139"/>
       <c r="E134" s="139"/>
       <c r="F134" s="139"/>
-      <c r="G134" s="138"/>
-      <c r="H134" s="138"/>
-      <c r="I134" s="139"/>
-      <c r="J134" s="139"/>
+      <c r="G134" s="139"/>
+      <c r="H134" s="139"/>
+      <c r="I134" s="138"/>
+      <c r="J134" s="138"/>
       <c r="K134" s="139"/>
       <c r="L134" s="139"/>
       <c r="M134" s="139"/>
       <c r="N134" s="139"/>
-      <c r="O134" s="138"/>
-      <c r="P134" s="138"/>
+      <c r="O134" s="139"/>
+      <c r="P134" s="139"/>
       <c r="Q134" s="138"/>
       <c r="R134" s="138"/>
-      <c r="S134" s="139"/>
-      <c r="T134" s="139"/>
-    </row>
-    <row r="135" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S134" s="138"/>
+      <c r="T134" s="138"/>
+      <c r="U134" s="139"/>
+      <c r="V134" s="139"/>
+    </row>
+    <row r="135" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B135" s="139"/>
       <c r="C135" s="139"/>
       <c r="D135" s="139"/>
       <c r="E135" s="139"/>
       <c r="F135" s="139"/>
-      <c r="G135" s="138"/>
-      <c r="H135" s="138"/>
-      <c r="I135" s="139"/>
-      <c r="J135" s="139"/>
+      <c r="G135" s="139"/>
+      <c r="H135" s="139"/>
+      <c r="I135" s="138"/>
+      <c r="J135" s="138"/>
       <c r="K135" s="139"/>
       <c r="L135" s="139"/>
       <c r="M135" s="139"/>
       <c r="N135" s="139"/>
-      <c r="O135" s="138"/>
-      <c r="P135" s="138"/>
+      <c r="O135" s="139"/>
+      <c r="P135" s="139"/>
       <c r="Q135" s="138"/>
       <c r="R135" s="138"/>
-      <c r="S135" s="139"/>
-      <c r="T135" s="139"/>
-    </row>
-    <row r="136" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S135" s="138"/>
+      <c r="T135" s="138"/>
+      <c r="U135" s="139"/>
+      <c r="V135" s="139"/>
+    </row>
+    <row r="136" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B136" s="139"/>
       <c r="C136" s="139"/>
       <c r="D136" s="139"/>
       <c r="E136" s="139"/>
       <c r="F136" s="139"/>
-      <c r="G136" s="138"/>
-      <c r="H136" s="138"/>
-      <c r="I136" s="139"/>
-      <c r="J136" s="139"/>
+      <c r="G136" s="139"/>
+      <c r="H136" s="139"/>
+      <c r="I136" s="138"/>
+      <c r="J136" s="138"/>
       <c r="K136" s="139"/>
       <c r="L136" s="139"/>
       <c r="M136" s="139"/>
       <c r="N136" s="139"/>
-      <c r="O136" s="138"/>
-      <c r="P136" s="138"/>
+      <c r="O136" s="139"/>
+      <c r="P136" s="139"/>
       <c r="Q136" s="138"/>
       <c r="R136" s="138"/>
-      <c r="S136" s="139"/>
-      <c r="T136" s="139"/>
-    </row>
-    <row r="137" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S136" s="138"/>
+      <c r="T136" s="138"/>
+      <c r="U136" s="139"/>
+      <c r="V136" s="139"/>
+    </row>
+    <row r="137" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B137" s="138"/>
       <c r="C137" s="138"/>
       <c r="D137" s="139"/>
-      <c r="E137" s="138"/>
+      <c r="E137" s="139"/>
       <c r="F137" s="139"/>
       <c r="G137" s="138"/>
       <c r="H137" s="139"/>
@@ -4771,13 +5492,15 @@
       <c r="M137" s="138"/>
       <c r="N137" s="139"/>
       <c r="O137" s="138"/>
-      <c r="P137" s="138"/>
+      <c r="P137" s="139"/>
       <c r="Q137" s="138"/>
       <c r="R137" s="138"/>
       <c r="S137" s="138"/>
       <c r="T137" s="138"/>
-    </row>
-    <row r="138" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U137" s="138"/>
+      <c r="V137" s="138"/>
+    </row>
+    <row r="138" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B138" s="138"/>
       <c r="C138" s="139"/>
       <c r="D138" s="139"/>
@@ -4791,46 +5514,50 @@
       <c r="L138" s="139"/>
       <c r="M138" s="139"/>
       <c r="N138" s="139"/>
-      <c r="O138" s="138"/>
-      <c r="P138" s="138"/>
+      <c r="O138" s="139"/>
+      <c r="P138" s="139"/>
       <c r="Q138" s="138"/>
       <c r="R138" s="138"/>
       <c r="S138" s="138"/>
-      <c r="T138" s="139"/>
-    </row>
-    <row r="139" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="T138" s="138"/>
+      <c r="U138" s="138"/>
+      <c r="V138" s="139"/>
+    </row>
+    <row r="139" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B139" s="138"/>
       <c r="C139" s="139"/>
       <c r="D139" s="139"/>
       <c r="E139" s="139"/>
       <c r="F139" s="139"/>
-      <c r="G139" s="138"/>
-      <c r="H139" s="138"/>
-      <c r="I139" s="139"/>
-      <c r="J139" s="139"/>
+      <c r="G139" s="139"/>
+      <c r="H139" s="139"/>
+      <c r="I139" s="138"/>
+      <c r="J139" s="138"/>
       <c r="K139" s="139"/>
       <c r="L139" s="139"/>
       <c r="M139" s="139"/>
       <c r="N139" s="139"/>
-      <c r="O139" s="138"/>
-      <c r="P139" s="138"/>
+      <c r="O139" s="139"/>
+      <c r="P139" s="139"/>
       <c r="Q139" s="138"/>
       <c r="R139" s="138"/>
-      <c r="S139" s="139"/>
-      <c r="T139" s="139"/>
-    </row>
-    <row r="140" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S139" s="138"/>
+      <c r="T139" s="138"/>
+      <c r="U139" s="139"/>
+      <c r="V139" s="139"/>
+    </row>
+    <row r="140" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B140" s="139"/>
       <c r="C140" s="139"/>
       <c r="D140" s="139"/>
-      <c r="E140" s="138"/>
-      <c r="F140" s="138"/>
-      <c r="G140" s="139"/>
-      <c r="H140" s="139"/>
-      <c r="I140" s="138"/>
-      <c r="J140" s="138"/>
-      <c r="K140" s="139"/>
-      <c r="L140" s="139"/>
+      <c r="E140" s="139"/>
+      <c r="F140" s="139"/>
+      <c r="G140" s="138"/>
+      <c r="H140" s="138"/>
+      <c r="I140" s="139"/>
+      <c r="J140" s="139"/>
+      <c r="K140" s="138"/>
+      <c r="L140" s="138"/>
       <c r="M140" s="139"/>
       <c r="N140" s="139"/>
       <c r="O140" s="139"/>
@@ -4839,8 +5566,10 @@
       <c r="R140" s="139"/>
       <c r="S140" s="139"/>
       <c r="T140" s="139"/>
-    </row>
-    <row r="141" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U140" s="139"/>
+      <c r="V140" s="139"/>
+    </row>
+    <row r="141" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B141" s="139"/>
       <c r="C141" s="139"/>
       <c r="D141" s="139"/>
@@ -4848,52 +5577,56 @@
       <c r="F141" s="139"/>
       <c r="G141" s="139"/>
       <c r="H141" s="139"/>
-      <c r="I141" s="138"/>
-      <c r="J141" s="138"/>
-      <c r="K141" s="139"/>
-      <c r="L141" s="139"/>
+      <c r="I141" s="139"/>
+      <c r="J141" s="139"/>
+      <c r="K141" s="138"/>
+      <c r="L141" s="138"/>
       <c r="M141" s="139"/>
       <c r="N141" s="139"/>
-      <c r="O141" s="138"/>
-      <c r="P141" s="138"/>
+      <c r="O141" s="139"/>
+      <c r="P141" s="139"/>
       <c r="Q141" s="138"/>
       <c r="R141" s="138"/>
-      <c r="S141" s="139"/>
-      <c r="T141" s="139"/>
-    </row>
-    <row r="142" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S141" s="138"/>
+      <c r="T141" s="138"/>
+      <c r="U141" s="139"/>
+      <c r="V141" s="139"/>
+    </row>
+    <row r="142" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B142" s="139"/>
       <c r="C142" s="139"/>
       <c r="D142" s="139"/>
-      <c r="E142" s="138"/>
-      <c r="F142" s="138"/>
-      <c r="G142" s="139"/>
-      <c r="H142" s="139"/>
+      <c r="E142" s="139"/>
+      <c r="F142" s="139"/>
+      <c r="G142" s="138"/>
+      <c r="H142" s="138"/>
       <c r="I142" s="139"/>
       <c r="J142" s="139"/>
       <c r="K142" s="139"/>
       <c r="L142" s="139"/>
       <c r="M142" s="139"/>
       <c r="N142" s="139"/>
-      <c r="O142" s="138"/>
-      <c r="P142" s="138"/>
+      <c r="O142" s="139"/>
+      <c r="P142" s="139"/>
       <c r="Q142" s="138"/>
       <c r="R142" s="138"/>
-      <c r="S142" s="139"/>
-      <c r="T142" s="139"/>
-    </row>
-    <row r="143" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S142" s="138"/>
+      <c r="T142" s="138"/>
+      <c r="U142" s="139"/>
+      <c r="V142" s="139"/>
+    </row>
+    <row r="143" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B143" s="139"/>
       <c r="C143" s="139"/>
       <c r="D143" s="139"/>
-      <c r="E143" s="138"/>
-      <c r="F143" s="138"/>
-      <c r="G143" s="139"/>
-      <c r="H143" s="139"/>
-      <c r="I143" s="138"/>
-      <c r="J143" s="138"/>
-      <c r="K143" s="139"/>
-      <c r="L143" s="139"/>
+      <c r="E143" s="139"/>
+      <c r="F143" s="139"/>
+      <c r="G143" s="138"/>
+      <c r="H143" s="138"/>
+      <c r="I143" s="139"/>
+      <c r="J143" s="139"/>
+      <c r="K143" s="138"/>
+      <c r="L143" s="138"/>
       <c r="M143" s="139"/>
       <c r="N143" s="139"/>
       <c r="O143" s="139"/>
@@ -4902,8 +5635,10 @@
       <c r="R143" s="139"/>
       <c r="S143" s="139"/>
       <c r="T143" s="139"/>
-    </row>
-    <row r="144" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U143" s="139"/>
+      <c r="V143" s="139"/>
+    </row>
+    <row r="144" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B144" s="139"/>
       <c r="C144" s="139"/>
       <c r="D144" s="139"/>
@@ -4911,73 +5646,79 @@
       <c r="F144" s="139"/>
       <c r="G144" s="139"/>
       <c r="H144" s="139"/>
-      <c r="I144" s="138"/>
-      <c r="J144" s="138"/>
-      <c r="K144" s="139"/>
-      <c r="L144" s="139"/>
+      <c r="I144" s="139"/>
+      <c r="J144" s="139"/>
+      <c r="K144" s="138"/>
+      <c r="L144" s="138"/>
       <c r="M144" s="139"/>
       <c r="N144" s="139"/>
-      <c r="O144" s="138"/>
-      <c r="P144" s="138"/>
+      <c r="O144" s="139"/>
+      <c r="P144" s="139"/>
       <c r="Q144" s="138"/>
       <c r="R144" s="138"/>
-      <c r="S144" s="139"/>
-      <c r="T144" s="139"/>
-    </row>
-    <row r="145" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S144" s="138"/>
+      <c r="T144" s="138"/>
+      <c r="U144" s="139"/>
+      <c r="V144" s="139"/>
+    </row>
+    <row r="145" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B145" s="139"/>
       <c r="C145" s="139"/>
       <c r="D145" s="139"/>
       <c r="E145" s="139"/>
       <c r="F145" s="139"/>
-      <c r="G145" s="138"/>
-      <c r="H145" s="138"/>
-      <c r="I145" s="139"/>
-      <c r="J145" s="139"/>
+      <c r="G145" s="139"/>
+      <c r="H145" s="139"/>
+      <c r="I145" s="138"/>
+      <c r="J145" s="138"/>
       <c r="K145" s="139"/>
       <c r="L145" s="139"/>
       <c r="M145" s="139"/>
       <c r="N145" s="139"/>
-      <c r="O145" s="138"/>
-      <c r="P145" s="138"/>
+      <c r="O145" s="139"/>
+      <c r="P145" s="139"/>
       <c r="Q145" s="138"/>
       <c r="R145" s="138"/>
-      <c r="S145" s="139"/>
-      <c r="T145" s="139"/>
-    </row>
-    <row r="146" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S145" s="138"/>
+      <c r="T145" s="138"/>
+      <c r="U145" s="139"/>
+      <c r="V145" s="139"/>
+    </row>
+    <row r="146" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B146" s="139"/>
       <c r="C146" s="139"/>
       <c r="D146" s="139"/>
-      <c r="E146" s="138"/>
-      <c r="F146" s="138"/>
-      <c r="G146" s="139"/>
-      <c r="H146" s="139"/>
+      <c r="E146" s="139"/>
+      <c r="F146" s="139"/>
+      <c r="G146" s="138"/>
+      <c r="H146" s="138"/>
       <c r="I146" s="139"/>
       <c r="J146" s="139"/>
       <c r="K146" s="139"/>
       <c r="L146" s="139"/>
       <c r="M146" s="139"/>
       <c r="N146" s="139"/>
-      <c r="O146" s="138"/>
-      <c r="P146" s="138"/>
+      <c r="O146" s="139"/>
+      <c r="P146" s="139"/>
       <c r="Q146" s="138"/>
       <c r="R146" s="138"/>
-      <c r="S146" s="139"/>
-      <c r="T146" s="139"/>
-    </row>
-    <row r="147" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S146" s="138"/>
+      <c r="T146" s="138"/>
+      <c r="U146" s="139"/>
+      <c r="V146" s="139"/>
+    </row>
+    <row r="147" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B147" s="139"/>
       <c r="C147" s="139"/>
       <c r="D147" s="139"/>
-      <c r="E147" s="138"/>
-      <c r="F147" s="138"/>
-      <c r="G147" s="139"/>
-      <c r="H147" s="139"/>
-      <c r="I147" s="138"/>
-      <c r="J147" s="138"/>
-      <c r="K147" s="139"/>
-      <c r="L147" s="139"/>
+      <c r="E147" s="139"/>
+      <c r="F147" s="139"/>
+      <c r="G147" s="138"/>
+      <c r="H147" s="138"/>
+      <c r="I147" s="139"/>
+      <c r="J147" s="139"/>
+      <c r="K147" s="138"/>
+      <c r="L147" s="138"/>
       <c r="M147" s="139"/>
       <c r="N147" s="139"/>
       <c r="O147" s="139"/>
@@ -4986,8 +5727,10 @@
       <c r="R147" s="139"/>
       <c r="S147" s="139"/>
       <c r="T147" s="139"/>
-    </row>
-    <row r="148" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U147" s="139"/>
+      <c r="V147" s="139"/>
+    </row>
+    <row r="148" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B148" s="139"/>
       <c r="C148" s="139"/>
       <c r="D148" s="139"/>
@@ -4995,87 +5738,95 @@
       <c r="F148" s="139"/>
       <c r="G148" s="139"/>
       <c r="H148" s="139"/>
-      <c r="I148" s="138"/>
-      <c r="J148" s="138"/>
-      <c r="K148" s="139"/>
-      <c r="L148" s="139"/>
+      <c r="I148" s="139"/>
+      <c r="J148" s="139"/>
+      <c r="K148" s="138"/>
+      <c r="L148" s="138"/>
       <c r="M148" s="139"/>
       <c r="N148" s="139"/>
-      <c r="O148" s="138"/>
-      <c r="P148" s="138"/>
+      <c r="O148" s="139"/>
+      <c r="P148" s="139"/>
       <c r="Q148" s="138"/>
       <c r="R148" s="138"/>
-      <c r="S148" s="139"/>
-      <c r="T148" s="139"/>
-    </row>
-    <row r="149" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S148" s="138"/>
+      <c r="T148" s="138"/>
+      <c r="U148" s="139"/>
+      <c r="V148" s="139"/>
+    </row>
+    <row r="149" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B149" s="139"/>
       <c r="C149" s="139"/>
       <c r="D149" s="139"/>
-      <c r="E149" s="138"/>
-      <c r="F149" s="138"/>
-      <c r="G149" s="139"/>
-      <c r="H149" s="139"/>
+      <c r="E149" s="139"/>
+      <c r="F149" s="139"/>
+      <c r="G149" s="138"/>
+      <c r="H149" s="138"/>
       <c r="I149" s="139"/>
       <c r="J149" s="139"/>
       <c r="K149" s="139"/>
       <c r="L149" s="139"/>
       <c r="M149" s="139"/>
       <c r="N149" s="139"/>
-      <c r="O149" s="138"/>
-      <c r="P149" s="138"/>
+      <c r="O149" s="139"/>
+      <c r="P149" s="139"/>
       <c r="Q149" s="138"/>
       <c r="R149" s="138"/>
-      <c r="S149" s="139"/>
-      <c r="T149" s="139"/>
-    </row>
-    <row r="150" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S149" s="138"/>
+      <c r="T149" s="138"/>
+      <c r="U149" s="139"/>
+      <c r="V149" s="139"/>
+    </row>
+    <row r="150" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B150" s="139"/>
       <c r="C150" s="139"/>
       <c r="D150" s="139"/>
-      <c r="E150" s="138"/>
-      <c r="F150" s="138"/>
-      <c r="G150" s="139"/>
-      <c r="H150" s="139"/>
+      <c r="E150" s="139"/>
+      <c r="F150" s="139"/>
+      <c r="G150" s="138"/>
+      <c r="H150" s="138"/>
       <c r="I150" s="139"/>
       <c r="J150" s="139"/>
       <c r="K150" s="139"/>
       <c r="L150" s="139"/>
       <c r="M150" s="139"/>
       <c r="N150" s="139"/>
-      <c r="O150" s="138"/>
-      <c r="P150" s="138"/>
+      <c r="O150" s="139"/>
+      <c r="P150" s="139"/>
       <c r="Q150" s="138"/>
       <c r="R150" s="138"/>
-      <c r="S150" s="139"/>
-      <c r="T150" s="139"/>
-    </row>
-    <row r="151" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S150" s="138"/>
+      <c r="T150" s="138"/>
+      <c r="U150" s="139"/>
+      <c r="V150" s="139"/>
+    </row>
+    <row r="151" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B151" s="139"/>
       <c r="C151" s="139"/>
       <c r="D151" s="139"/>
-      <c r="E151" s="138"/>
-      <c r="F151" s="138"/>
-      <c r="G151" s="139"/>
-      <c r="H151" s="139"/>
+      <c r="E151" s="139"/>
+      <c r="F151" s="139"/>
+      <c r="G151" s="138"/>
+      <c r="H151" s="138"/>
       <c r="I151" s="139"/>
       <c r="J151" s="139"/>
       <c r="K151" s="139"/>
       <c r="L151" s="139"/>
       <c r="M151" s="139"/>
       <c r="N151" s="139"/>
-      <c r="O151" s="138"/>
-      <c r="P151" s="138"/>
+      <c r="O151" s="139"/>
+      <c r="P151" s="139"/>
       <c r="Q151" s="138"/>
       <c r="R151" s="138"/>
-      <c r="S151" s="139"/>
-      <c r="T151" s="139"/>
-    </row>
-    <row r="152" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="S151" s="138"/>
+      <c r="T151" s="138"/>
+      <c r="U151" s="139"/>
+      <c r="V151" s="139"/>
+    </row>
+    <row r="152" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B152" s="138"/>
       <c r="C152" s="138"/>
       <c r="D152" s="139"/>
-      <c r="E152" s="138"/>
+      <c r="E152" s="139"/>
       <c r="F152" s="139"/>
       <c r="G152" s="138"/>
       <c r="H152" s="139"/>
@@ -5086,13 +5837,15 @@
       <c r="M152" s="138"/>
       <c r="N152" s="139"/>
       <c r="O152" s="138"/>
-      <c r="P152" s="138"/>
+      <c r="P152" s="139"/>
       <c r="Q152" s="138"/>
       <c r="R152" s="138"/>
       <c r="S152" s="138"/>
       <c r="T152" s="138"/>
-    </row>
-    <row r="153" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U152" s="138"/>
+      <c r="V152" s="138"/>
+    </row>
+    <row r="153" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B153" s="138"/>
       <c r="C153" s="139"/>
       <c r="D153" s="139"/>
@@ -5106,14 +5859,16 @@
       <c r="L153" s="139"/>
       <c r="M153" s="139"/>
       <c r="N153" s="139"/>
-      <c r="O153" s="138"/>
-      <c r="P153" s="138"/>
+      <c r="O153" s="139"/>
+      <c r="P153" s="139"/>
       <c r="Q153" s="138"/>
       <c r="R153" s="138"/>
       <c r="S153" s="138"/>
-      <c r="T153" s="139"/>
-    </row>
-    <row r="154" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="T153" s="138"/>
+      <c r="U153" s="138"/>
+      <c r="V153" s="139"/>
+    </row>
+    <row r="154" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B154" s="138"/>
       <c r="C154" s="138"/>
       <c r="D154" s="138"/>
@@ -5127,14 +5882,16 @@
       <c r="L154" s="138"/>
       <c r="M154" s="138"/>
       <c r="N154" s="138"/>
-      <c r="O154" s="139"/>
-      <c r="P154" s="139"/>
+      <c r="O154" s="138"/>
+      <c r="P154" s="138"/>
       <c r="Q154" s="139"/>
       <c r="R154" s="139"/>
-      <c r="S154" s="138"/>
+      <c r="S154" s="139"/>
       <c r="T154" s="139"/>
-    </row>
-    <row r="155" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U154" s="138"/>
+      <c r="V154" s="139"/>
+    </row>
+    <row r="155" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B155" s="144"/>
       <c r="C155" s="144"/>
       <c r="D155" s="144"/>
@@ -5154,8 +5911,10 @@
       <c r="R155" s="144"/>
       <c r="S155" s="144"/>
       <c r="T155" s="144"/>
-    </row>
-    <row r="156" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U155" s="144"/>
+      <c r="V155" s="144"/>
+    </row>
+    <row r="156" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B156" s="144"/>
       <c r="C156" s="144"/>
       <c r="D156" s="144"/>
@@ -5175,17 +5934,20 @@
       <c r="R156" s="144"/>
       <c r="S156" s="144"/>
       <c r="T156" s="144"/>
+      <c r="U156" s="144"/>
+      <c r="V156" s="144"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="M2:N2"/>
+  <mergeCells count="9">
     <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:U2"/>
     <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="E2:F2"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5657,39 +6419,39 @@
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="231" t="s">
+      <c r="C2" s="272" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="231"/>
-      <c r="E2" s="232" t="s">
+      <c r="D2" s="272"/>
+      <c r="E2" s="273" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="232"/>
-      <c r="G2" s="233" t="s">
+      <c r="F2" s="273"/>
+      <c r="G2" s="274" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="233"/>
-      <c r="I2" s="234" t="s">
+      <c r="H2" s="274"/>
+      <c r="I2" s="275" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="234"/>
-      <c r="K2" s="235" t="s">
+      <c r="J2" s="275"/>
+      <c r="K2" s="276" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="235"/>
-      <c r="M2" s="228" t="s">
+      <c r="L2" s="276"/>
+      <c r="M2" s="269" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="228"/>
-      <c r="O2" s="229" t="s">
+      <c r="N2" s="269"/>
+      <c r="O2" s="270" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="229"/>
-      <c r="Q2" s="230" t="s">
+      <c r="P2" s="270"/>
+      <c r="Q2" s="271" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="230"/>
-      <c r="S2" s="230"/>
+      <c r="R2" s="271"/>
+      <c r="S2" s="271"/>
       <c r="T2" s="3" t="s">
         <v>9</v>
       </c>

--- a/docs/excel_template.xlsx
+++ b/docs/excel_template.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="96">
   <si>
     <t>Date</t>
   </si>
@@ -122,9 +122,6 @@
   </si>
   <si>
     <t>Dinner</t>
-  </si>
-  <si>
-    <t>Coin-hold</t>
   </si>
   <si>
     <t>541</t>
@@ -327,6 +324,9 @@
   <si>
     <t>Coin hold</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>True</t>
   </si>
 </sst>
 </file>
@@ -338,7 +338,7 @@
     <numFmt numFmtId="177" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
     <numFmt numFmtId="178" formatCode="0.00\ ;[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -378,8 +378,13 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Book Antiqua"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -482,6 +487,16 @@
         <bgColor rgb="FFFDE9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFBDBD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="52">
     <border>
@@ -1229,7 +1244,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="277">
+  <cellXfs count="281">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1606,21 +1621,9 @@
     <xf numFmtId="4" fontId="2" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="2" fillId="8" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="177" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1637,9 +1640,6 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2054,6 +2054,27 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2490,43 +2511,43 @@
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="262" t="s">
+      <c r="C2" s="257" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="262"/>
-      <c r="E2" s="267" t="s">
-        <v>90</v>
-      </c>
-      <c r="F2" s="268"/>
-      <c r="G2" s="263" t="s">
+      <c r="D2" s="257"/>
+      <c r="E2" s="262" t="s">
+        <v>89</v>
+      </c>
+      <c r="F2" s="263"/>
+      <c r="G2" s="258" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="263"/>
-      <c r="I2" s="264" t="s">
+      <c r="H2" s="258"/>
+      <c r="I2" s="259" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="264"/>
-      <c r="K2" s="265" t="s">
+      <c r="J2" s="259"/>
+      <c r="K2" s="260" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="265"/>
-      <c r="M2" s="266" t="s">
+      <c r="L2" s="260"/>
+      <c r="M2" s="261" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="266"/>
-      <c r="O2" s="259" t="s">
+      <c r="N2" s="261"/>
+      <c r="O2" s="254" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="259"/>
-      <c r="Q2" s="260" t="s">
+      <c r="P2" s="254"/>
+      <c r="Q2" s="255" t="s">
         <v>7</v>
       </c>
-      <c r="R2" s="260"/>
-      <c r="S2" s="261" t="s">
+      <c r="R2" s="255"/>
+      <c r="S2" s="256" t="s">
         <v>8</v>
       </c>
-      <c r="T2" s="261"/>
-      <c r="U2" s="261"/>
+      <c r="T2" s="256"/>
+      <c r="U2" s="256"/>
       <c r="V2" s="3" t="s">
         <v>9</v>
       </c>
@@ -2541,11 +2562,11 @@
       <c r="D3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="241" t="s">
+      <c r="E3" s="236" t="s">
+        <v>86</v>
+      </c>
+      <c r="F3" s="237" t="s">
         <v>87</v>
-      </c>
-      <c r="F3" s="242" t="s">
-        <v>88</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>11</v>
@@ -2602,10 +2623,10 @@
         <v>70</v>
       </c>
       <c r="D4" s="5"/>
-      <c r="E4" s="241">
+      <c r="E4" s="236">
         <v>0</v>
       </c>
-      <c r="F4" s="242"/>
+      <c r="F4" s="237"/>
       <c r="G4" s="6">
         <v>15266.02</v>
       </c>
@@ -2641,8 +2662,8 @@
       </c>
       <c r="C5" s="29"/>
       <c r="D5" s="30"/>
-      <c r="E5" s="243"/>
-      <c r="F5" s="244"/>
+      <c r="E5" s="238"/>
+      <c r="F5" s="239"/>
       <c r="G5" s="31"/>
       <c r="H5" s="32"/>
       <c r="I5" s="33" t="s">
@@ -2676,8 +2697,8 @@
       <c r="B6" s="47"/>
       <c r="C6" s="48"/>
       <c r="D6" s="49"/>
-      <c r="E6" s="245"/>
-      <c r="F6" s="246"/>
+      <c r="E6" s="240"/>
+      <c r="F6" s="241"/>
       <c r="G6" s="50"/>
       <c r="H6" s="51"/>
       <c r="I6" s="52" t="s">
@@ -2711,8 +2732,8 @@
       <c r="B7" s="47"/>
       <c r="C7" s="48"/>
       <c r="D7" s="49"/>
-      <c r="E7" s="245"/>
-      <c r="F7" s="246"/>
+      <c r="E7" s="240"/>
+      <c r="F7" s="241"/>
       <c r="G7" s="50" t="s">
         <v>4</v>
       </c>
@@ -2742,8 +2763,8 @@
       <c r="B8" s="47"/>
       <c r="C8" s="48"/>
       <c r="D8" s="49"/>
-      <c r="E8" s="245"/>
-      <c r="F8" s="246"/>
+      <c r="E8" s="240"/>
+      <c r="F8" s="241"/>
       <c r="G8" s="50"/>
       <c r="H8" s="51"/>
       <c r="I8" s="52"/>
@@ -2777,8 +2798,8 @@
       <c r="B9" s="47"/>
       <c r="C9" s="48"/>
       <c r="D9" s="49"/>
-      <c r="E9" s="245"/>
-      <c r="F9" s="246"/>
+      <c r="E9" s="240"/>
+      <c r="F9" s="241"/>
       <c r="G9" s="50" t="s">
         <v>4</v>
       </c>
@@ -2808,8 +2829,8 @@
       <c r="B10" s="47"/>
       <c r="C10" s="48"/>
       <c r="D10" s="49"/>
-      <c r="E10" s="255"/>
-      <c r="F10" s="246"/>
+      <c r="E10" s="250"/>
+      <c r="F10" s="241"/>
       <c r="G10" s="50"/>
       <c r="H10" s="51"/>
       <c r="I10" s="52"/>
@@ -2843,8 +2864,8 @@
       <c r="B11" s="47"/>
       <c r="C11" s="48"/>
       <c r="D11" s="49"/>
-      <c r="E11" s="245"/>
-      <c r="F11" s="246"/>
+      <c r="E11" s="240"/>
+      <c r="F11" s="241"/>
       <c r="G11" s="50" t="s">
         <v>20</v>
       </c>
@@ -2874,8 +2895,8 @@
       <c r="B12" s="47"/>
       <c r="C12" s="48"/>
       <c r="D12" s="49"/>
-      <c r="E12" s="245"/>
-      <c r="F12" s="246"/>
+      <c r="E12" s="240"/>
+      <c r="F12" s="241"/>
       <c r="G12" s="50"/>
       <c r="H12" s="51"/>
       <c r="I12" s="52"/>
@@ -2909,8 +2930,8 @@
       <c r="B13" s="47"/>
       <c r="C13" s="48"/>
       <c r="D13" s="49"/>
-      <c r="E13" s="245"/>
-      <c r="F13" s="246"/>
+      <c r="E13" s="240"/>
+      <c r="F13" s="241"/>
       <c r="G13" s="50" t="s">
         <v>4</v>
       </c>
@@ -2940,8 +2961,8 @@
       <c r="B14" s="47"/>
       <c r="C14" s="48"/>
       <c r="D14" s="49"/>
-      <c r="E14" s="245"/>
-      <c r="F14" s="246"/>
+      <c r="E14" s="240"/>
+      <c r="F14" s="241"/>
       <c r="G14" s="50"/>
       <c r="H14" s="51"/>
       <c r="I14" s="52"/>
@@ -2975,8 +2996,8 @@
       <c r="B15" s="47"/>
       <c r="C15" s="48"/>
       <c r="D15" s="49"/>
-      <c r="E15" s="245"/>
-      <c r="F15" s="246"/>
+      <c r="E15" s="240"/>
+      <c r="F15" s="241"/>
       <c r="G15" s="50" t="s">
         <v>4</v>
       </c>
@@ -3006,8 +3027,8 @@
       <c r="B16" s="47"/>
       <c r="C16" s="48"/>
       <c r="D16" s="49"/>
-      <c r="E16" s="245"/>
-      <c r="F16" s="246"/>
+      <c r="E16" s="240"/>
+      <c r="F16" s="241"/>
       <c r="G16" s="50"/>
       <c r="H16" s="51"/>
       <c r="I16" s="52"/>
@@ -3039,16 +3060,16 @@
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B17" s="66" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C17" s="67">
         <v>70</v>
       </c>
       <c r="D17" s="68"/>
-      <c r="E17" s="247">
+      <c r="E17" s="242">
         <v>0</v>
       </c>
-      <c r="F17" s="248"/>
+      <c r="F17" s="243"/>
       <c r="G17" s="69">
         <v>14944.22</v>
       </c>
@@ -3095,8 +3116,8 @@
       </c>
       <c r="C18" s="86"/>
       <c r="D18" s="87"/>
-      <c r="E18" s="249"/>
-      <c r="F18" s="250"/>
+      <c r="E18" s="244"/>
+      <c r="F18" s="245"/>
       <c r="G18" s="88"/>
       <c r="H18" s="89"/>
       <c r="I18" s="90"/>
@@ -3128,8 +3149,8 @@
       </c>
       <c r="C19" s="29"/>
       <c r="D19" s="30"/>
-      <c r="E19" s="243"/>
-      <c r="F19" s="244"/>
+      <c r="E19" s="238"/>
+      <c r="F19" s="239"/>
       <c r="G19" s="31" t="s">
         <v>25</v>
       </c>
@@ -3159,8 +3180,8 @@
       <c r="B20" s="105"/>
       <c r="C20" s="106"/>
       <c r="D20" s="107"/>
-      <c r="E20" s="251"/>
-      <c r="F20" s="252"/>
+      <c r="E20" s="246"/>
+      <c r="F20" s="247"/>
       <c r="G20" s="108">
         <v>7000</v>
       </c>
@@ -3190,8 +3211,8 @@
       <c r="B21" s="105"/>
       <c r="C21" s="106"/>
       <c r="D21" s="107"/>
-      <c r="E21" s="251"/>
-      <c r="F21" s="252"/>
+      <c r="E21" s="246"/>
+      <c r="F21" s="247"/>
       <c r="G21" s="108"/>
       <c r="H21" s="109"/>
       <c r="I21" s="110" t="s">
@@ -3225,8 +3246,8 @@
       <c r="B22" s="105"/>
       <c r="C22" s="106"/>
       <c r="D22" s="107"/>
-      <c r="E22" s="251"/>
-      <c r="F22" s="252"/>
+      <c r="E22" s="246"/>
+      <c r="F22" s="247"/>
       <c r="G22" s="108"/>
       <c r="H22" s="109"/>
       <c r="I22" s="110" t="s">
@@ -3260,8 +3281,8 @@
       <c r="B23" s="105"/>
       <c r="C23" s="106"/>
       <c r="D23" s="107"/>
-      <c r="E23" s="251"/>
-      <c r="F23" s="252"/>
+      <c r="E23" s="246"/>
+      <c r="F23" s="247"/>
       <c r="G23" s="108"/>
       <c r="H23" s="109"/>
       <c r="I23" s="110" t="s">
@@ -3295,8 +3316,8 @@
       <c r="B24" s="105"/>
       <c r="C24" s="106"/>
       <c r="D24" s="107"/>
-      <c r="E24" s="251"/>
-      <c r="F24" s="252"/>
+      <c r="E24" s="246"/>
+      <c r="F24" s="247"/>
       <c r="G24" s="108"/>
       <c r="H24" s="109"/>
       <c r="I24" s="110" t="s">
@@ -3330,8 +3351,8 @@
       <c r="B25" s="105"/>
       <c r="C25" s="106"/>
       <c r="D25" s="107"/>
-      <c r="E25" s="251"/>
-      <c r="F25" s="252"/>
+      <c r="E25" s="246"/>
+      <c r="F25" s="247"/>
       <c r="G25" s="108" t="s">
         <v>4</v>
       </c>
@@ -3361,8 +3382,8 @@
       <c r="B26" s="105"/>
       <c r="C26" s="106"/>
       <c r="D26" s="107"/>
-      <c r="E26" s="251"/>
-      <c r="F26" s="252"/>
+      <c r="E26" s="246"/>
+      <c r="F26" s="247"/>
       <c r="G26" s="108"/>
       <c r="H26" s="109"/>
       <c r="I26" s="110"/>
@@ -3396,8 +3417,8 @@
       <c r="B27" s="105"/>
       <c r="C27" s="106"/>
       <c r="D27" s="107"/>
-      <c r="E27" s="251"/>
-      <c r="F27" s="252"/>
+      <c r="E27" s="246"/>
+      <c r="F27" s="247"/>
       <c r="G27" s="108" t="s">
         <v>4</v>
       </c>
@@ -3427,8 +3448,8 @@
       <c r="B28" s="105"/>
       <c r="C28" s="106"/>
       <c r="D28" s="107"/>
-      <c r="E28" s="251"/>
-      <c r="F28" s="252"/>
+      <c r="E28" s="246"/>
+      <c r="F28" s="247"/>
       <c r="G28" s="108"/>
       <c r="H28" s="109"/>
       <c r="I28" s="110"/>
@@ -3462,8 +3483,8 @@
       <c r="B29" s="105"/>
       <c r="C29" s="106"/>
       <c r="D29" s="107"/>
-      <c r="E29" s="251"/>
-      <c r="F29" s="252"/>
+      <c r="E29" s="246"/>
+      <c r="F29" s="247"/>
       <c r="G29" s="108" t="s">
         <v>4</v>
       </c>
@@ -3493,8 +3514,8 @@
       <c r="B30" s="105"/>
       <c r="C30" s="106"/>
       <c r="D30" s="107"/>
-      <c r="E30" s="251"/>
-      <c r="F30" s="252"/>
+      <c r="E30" s="246"/>
+      <c r="F30" s="247"/>
       <c r="G30" s="108"/>
       <c r="H30" s="109"/>
       <c r="I30" s="110"/>
@@ -3528,8 +3549,8 @@
       <c r="B31" s="105"/>
       <c r="C31" s="106"/>
       <c r="D31" s="107"/>
-      <c r="E31" s="251"/>
-      <c r="F31" s="252"/>
+      <c r="E31" s="246"/>
+      <c r="F31" s="247"/>
       <c r="G31" s="108" t="s">
         <v>4</v>
       </c>
@@ -3559,8 +3580,8 @@
       <c r="B32" s="105"/>
       <c r="C32" s="106"/>
       <c r="D32" s="107"/>
-      <c r="E32" s="251"/>
-      <c r="F32" s="252"/>
+      <c r="E32" s="246"/>
+      <c r="F32" s="247"/>
       <c r="G32" s="108"/>
       <c r="H32" s="109"/>
       <c r="I32" s="110"/>
@@ -3598,8 +3619,8 @@
       <c r="D33" s="107">
         <v>63</v>
       </c>
-      <c r="E33" s="251"/>
-      <c r="F33" s="252"/>
+      <c r="E33" s="246"/>
+      <c r="F33" s="247"/>
       <c r="G33" s="108"/>
       <c r="H33" s="109"/>
       <c r="I33" s="110"/>
@@ -3628,16 +3649,16 @@
     <row r="34" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B34" s="105"/>
       <c r="C34" s="106" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D34" s="107">
         <v>7</v>
       </c>
-      <c r="E34" s="251">
+      <c r="E34" s="246">
         <v>7</v>
       </c>
-      <c r="F34" s="252" t="s">
-        <v>89</v>
+      <c r="F34" s="247" t="s">
+        <v>88</v>
       </c>
       <c r="G34" s="108"/>
       <c r="H34" s="109"/>
@@ -3649,18 +3670,10 @@
       <c r="N34" s="115"/>
       <c r="O34" s="116"/>
       <c r="P34" s="117"/>
-      <c r="Q34" s="118" t="s">
-        <v>31</v>
-      </c>
-      <c r="R34" s="119">
-        <v>7</v>
-      </c>
-      <c r="S34" s="120" t="s">
-        <v>31</v>
-      </c>
-      <c r="T34" s="121">
-        <v>7</v>
-      </c>
+      <c r="Q34" s="118"/>
+      <c r="R34" s="119"/>
+      <c r="S34" s="120"/>
+      <c r="T34" s="121"/>
       <c r="U34" s="45"/>
       <c r="V34" s="122"/>
     </row>
@@ -3668,8 +3681,8 @@
       <c r="B35" s="47"/>
       <c r="C35" s="106"/>
       <c r="D35" s="107"/>
-      <c r="E35" s="251"/>
-      <c r="F35" s="252"/>
+      <c r="E35" s="246"/>
+      <c r="F35" s="247"/>
       <c r="G35" s="108" t="s">
         <v>12</v>
       </c>
@@ -3703,16 +3716,16 @@
         <v>0</v>
       </c>
       <c r="D36" s="68"/>
-      <c r="E36" s="247">
+      <c r="E36" s="242">
         <v>7</v>
       </c>
-      <c r="F36" s="248"/>
+      <c r="F36" s="243"/>
       <c r="G36" s="123">
         <v>15595.12</v>
       </c>
       <c r="H36" s="70"/>
       <c r="I36" s="124" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J36" s="72"/>
       <c r="K36" s="73" t="s">
@@ -3736,14 +3749,14 @@
       <c r="S36" s="81">
         <v>7000</v>
       </c>
-      <c r="T36" s="126">
-        <v>5946.1</v>
-      </c>
-      <c r="U36" s="127">
-        <v>16136.12</v>
-      </c>
-      <c r="V36" s="84" t="b">
-        <v>1</v>
+      <c r="T36" s="275">
+        <v>5939.1</v>
+      </c>
+      <c r="U36" s="276">
+        <v>16143.12</v>
+      </c>
+      <c r="V36" s="272" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="2:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3752,8 +3765,8 @@
       </c>
       <c r="C37" s="86"/>
       <c r="D37" s="87"/>
-      <c r="E37" s="249"/>
-      <c r="F37" s="250"/>
+      <c r="E37" s="244"/>
+      <c r="F37" s="245"/>
       <c r="G37" s="88"/>
       <c r="H37" s="89"/>
       <c r="I37" s="90"/>
@@ -3767,201 +3780,201 @@
       <c r="Q37" s="79">
         <v>0</v>
       </c>
-      <c r="R37" s="128">
+      <c r="R37" s="126">
         <v>3296.8</v>
       </c>
       <c r="S37" s="81">
         <v>7000</v>
       </c>
-      <c r="T37" s="129">
-        <v>6289.8</v>
-      </c>
-      <c r="U37" s="130"/>
-      <c r="V37" s="103"/>
+      <c r="T37" s="277">
+        <v>6282.8</v>
+      </c>
+      <c r="U37" s="278"/>
+      <c r="V37" s="273"/>
     </row>
     <row r="38" spans="2:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C38" s="4">
         <v>0</v>
       </c>
-      <c r="D38" s="131" t="b">
+      <c r="D38" s="127" t="b">
         <v>1</v>
       </c>
-      <c r="E38" s="253">
+      <c r="E38" s="248">
         <v>7</v>
       </c>
-      <c r="F38" s="254" t="b">
+      <c r="F38" s="249" t="b">
         <v>1</v>
       </c>
       <c r="G38" s="6">
         <v>15595.12</v>
       </c>
-      <c r="H38" s="132" t="b">
+      <c r="H38" s="128" t="b">
         <v>1</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J38" s="133" t="b">
+        <v>31</v>
+      </c>
+      <c r="J38" s="129" t="b">
         <v>1</v>
       </c>
       <c r="K38" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="L38" s="134" t="b">
+      <c r="L38" s="130" t="b">
         <v>1</v>
       </c>
       <c r="M38" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="N38" s="135" t="b">
+      <c r="N38" s="131" t="b">
         <v>1</v>
       </c>
       <c r="O38" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="P38" s="136" t="b">
+      <c r="P38" s="132" t="b">
         <v>1</v>
       </c>
       <c r="Q38" s="22"/>
       <c r="R38" s="23"/>
       <c r="S38" s="24"/>
-      <c r="T38" s="25"/>
-      <c r="U38" s="137">
-        <v>16136.12</v>
-      </c>
-      <c r="V38" s="27"/>
+      <c r="T38" s="279"/>
+      <c r="U38" s="280">
+        <v>16143.12</v>
+      </c>
+      <c r="V38" s="274"/>
     </row>
     <row r="39" spans="2:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="138"/>
-      <c r="C39" s="236" t="s">
+      <c r="B39" s="133"/>
+      <c r="C39" s="231" t="s">
+        <v>77</v>
+      </c>
+      <c r="D39" s="134"/>
+      <c r="E39" s="231" t="s">
+        <v>90</v>
+      </c>
+      <c r="F39" s="134"/>
+      <c r="G39" s="231" t="s">
         <v>78</v>
       </c>
-      <c r="D39" s="139"/>
-      <c r="E39" s="236" t="s">
-        <v>91</v>
-      </c>
-      <c r="F39" s="139"/>
-      <c r="G39" s="236" t="s">
+      <c r="H39" s="133"/>
+      <c r="I39" s="231" t="s">
         <v>79</v>
       </c>
-      <c r="H39" s="138"/>
-      <c r="I39" s="236" t="s">
+      <c r="J39" s="134"/>
+      <c r="K39" s="231" t="s">
         <v>80</v>
       </c>
-      <c r="J39" s="139"/>
-      <c r="K39" s="236" t="s">
+      <c r="L39" s="134"/>
+      <c r="M39" s="231" t="s">
         <v>81</v>
       </c>
-      <c r="L39" s="139"/>
-      <c r="M39" s="236" t="s">
+      <c r="N39" s="134"/>
+      <c r="O39" s="231" t="s">
         <v>82</v>
       </c>
-      <c r="N39" s="139"/>
-      <c r="O39" s="236" t="s">
+      <c r="P39" s="134"/>
+      <c r="Q39" s="231" t="s">
         <v>83</v>
       </c>
-      <c r="P39" s="139"/>
-      <c r="Q39" s="236" t="s">
+      <c r="R39" s="133"/>
+      <c r="S39" s="231" t="s">
         <v>84</v>
       </c>
-      <c r="R39" s="138"/>
-      <c r="S39" s="236" t="s">
+      <c r="T39" s="133"/>
+      <c r="U39" s="134"/>
+      <c r="V39" s="231" t="s">
         <v>85</v>
       </c>
-      <c r="T39" s="138"/>
-      <c r="U39" s="139"/>
-      <c r="V39" s="236" t="s">
-        <v>86</v>
-      </c>
     </row>
     <row r="40" spans="2:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="139"/>
-      <c r="C40" s="139"/>
-      <c r="D40" s="139"/>
-      <c r="E40" s="139"/>
-      <c r="F40" s="139"/>
-      <c r="G40" s="138"/>
-      <c r="H40" s="138"/>
-      <c r="I40" s="139"/>
-      <c r="J40" s="139"/>
-      <c r="K40" s="138"/>
-      <c r="L40" s="138"/>
-      <c r="M40" s="139"/>
-      <c r="N40" s="139"/>
-      <c r="O40" s="139"/>
-      <c r="P40" s="139"/>
-      <c r="Q40" s="139"/>
-      <c r="R40" s="139"/>
-      <c r="S40" s="139"/>
-      <c r="T40" s="139"/>
-      <c r="U40" s="139"/>
-      <c r="V40" s="139"/>
+      <c r="B40" s="134"/>
+      <c r="C40" s="134"/>
+      <c r="D40" s="134"/>
+      <c r="E40" s="134"/>
+      <c r="F40" s="134"/>
+      <c r="G40" s="133"/>
+      <c r="H40" s="133"/>
+      <c r="I40" s="134"/>
+      <c r="J40" s="134"/>
+      <c r="K40" s="133"/>
+      <c r="L40" s="133"/>
+      <c r="M40" s="134"/>
+      <c r="N40" s="134"/>
+      <c r="O40" s="134"/>
+      <c r="P40" s="134"/>
+      <c r="Q40" s="134"/>
+      <c r="R40" s="134"/>
+      <c r="S40" s="134"/>
+      <c r="T40" s="134"/>
+      <c r="U40" s="134"/>
+      <c r="V40" s="134"/>
     </row>
     <row r="41" spans="2:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="X41" s="143"/>
+      <c r="X41" s="138"/>
     </row>
     <row r="42" spans="2:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="43" spans="2:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="220"/>
-      <c r="C43" s="221"/>
-      <c r="D43" s="223"/>
-      <c r="E43" s="237"/>
-      <c r="F43" s="237"/>
-      <c r="G43" s="222"/>
+      <c r="B43" s="215"/>
+      <c r="C43" s="216"/>
+      <c r="D43" s="218"/>
+      <c r="E43" s="232"/>
+      <c r="F43" s="232"/>
+      <c r="G43" s="217"/>
     </row>
     <row r="44" spans="2:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="224"/>
-      <c r="C44" s="226"/>
-      <c r="D44" s="227"/>
-      <c r="E44" s="238"/>
-      <c r="F44" s="238"/>
-      <c r="G44" s="225"/>
+      <c r="B44" s="219"/>
+      <c r="C44" s="221"/>
+      <c r="D44" s="222"/>
+      <c r="E44" s="233"/>
+      <c r="F44" s="233"/>
+      <c r="G44" s="220"/>
     </row>
     <row r="45" spans="2:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="224"/>
-      <c r="C45" s="226"/>
-      <c r="D45" s="227"/>
-      <c r="E45" s="238"/>
-      <c r="F45" s="238"/>
-      <c r="G45" s="225"/>
+      <c r="B45" s="219"/>
+      <c r="C45" s="221"/>
+      <c r="D45" s="222"/>
+      <c r="E45" s="233"/>
+      <c r="F45" s="233"/>
+      <c r="G45" s="220"/>
     </row>
     <row r="46" spans="2:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="228"/>
-      <c r="C46" s="229"/>
-      <c r="D46" s="230"/>
-      <c r="E46" s="239"/>
-      <c r="F46" s="239"/>
-      <c r="G46" s="231"/>
+      <c r="B46" s="223"/>
+      <c r="C46" s="224"/>
+      <c r="D46" s="225"/>
+      <c r="E46" s="234"/>
+      <c r="F46" s="234"/>
+      <c r="G46" s="226"/>
     </row>
     <row r="47" spans="2:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="232"/>
-      <c r="C47" s="233"/>
-      <c r="D47" s="234"/>
-      <c r="E47" s="240"/>
-      <c r="F47" s="240"/>
-      <c r="G47" s="235"/>
+      <c r="B47" s="227"/>
+      <c r="C47" s="228"/>
+      <c r="D47" s="229"/>
+      <c r="E47" s="235"/>
+      <c r="F47" s="235"/>
+      <c r="G47" s="230"/>
     </row>
     <row r="48" spans="2:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="49" spans="2:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="256" t="s">
-        <v>92</v>
-      </c>
-      <c r="C49" s="143"/>
-      <c r="E49" s="143"/>
+      <c r="B49" s="251" t="s">
+        <v>91</v>
+      </c>
+      <c r="C49" s="138"/>
+      <c r="E49" s="138"/>
     </row>
     <row r="50" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="257" t="s">
-        <v>93</v>
+      <c r="B51" s="252" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="52" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="53" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="258" t="s">
-        <v>94</v>
+      <c r="B53" s="253" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3983,1959 +3996,1959 @@
     <row r="70" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="71" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="138"/>
-      <c r="C72" s="139"/>
-      <c r="D72" s="139"/>
-      <c r="E72" s="139"/>
-      <c r="F72" s="139"/>
-      <c r="G72" s="139"/>
-      <c r="H72" s="139"/>
-      <c r="I72" s="139"/>
-      <c r="J72" s="139"/>
-      <c r="K72" s="139"/>
-      <c r="L72" s="139"/>
-      <c r="M72" s="139"/>
-      <c r="N72" s="139"/>
-      <c r="O72" s="139"/>
-      <c r="P72" s="139"/>
-      <c r="Q72" s="138"/>
-      <c r="R72" s="138"/>
-      <c r="S72" s="138"/>
-      <c r="T72" s="138"/>
-      <c r="U72" s="138"/>
-      <c r="V72" s="139"/>
+      <c r="B72" s="133"/>
+      <c r="C72" s="134"/>
+      <c r="D72" s="134"/>
+      <c r="E72" s="134"/>
+      <c r="F72" s="134"/>
+      <c r="G72" s="134"/>
+      <c r="H72" s="134"/>
+      <c r="I72" s="134"/>
+      <c r="J72" s="134"/>
+      <c r="K72" s="134"/>
+      <c r="L72" s="134"/>
+      <c r="M72" s="134"/>
+      <c r="N72" s="134"/>
+      <c r="O72" s="134"/>
+      <c r="P72" s="134"/>
+      <c r="Q72" s="133"/>
+      <c r="R72" s="133"/>
+      <c r="S72" s="133"/>
+      <c r="T72" s="133"/>
+      <c r="U72" s="133"/>
+      <c r="V72" s="134"/>
     </row>
     <row r="73" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="138"/>
-      <c r="C73" s="139"/>
-      <c r="D73" s="139"/>
-      <c r="E73" s="139"/>
-      <c r="F73" s="139"/>
-      <c r="G73" s="139"/>
-      <c r="H73" s="139"/>
-      <c r="I73" s="138"/>
-      <c r="J73" s="138"/>
-      <c r="K73" s="139"/>
-      <c r="L73" s="139"/>
-      <c r="M73" s="139"/>
-      <c r="N73" s="139"/>
-      <c r="O73" s="139"/>
-      <c r="P73" s="139"/>
-      <c r="Q73" s="138"/>
-      <c r="R73" s="138"/>
-      <c r="S73" s="138"/>
-      <c r="T73" s="138"/>
-      <c r="U73" s="139"/>
-      <c r="V73" s="139"/>
+      <c r="B73" s="133"/>
+      <c r="C73" s="134"/>
+      <c r="D73" s="134"/>
+      <c r="E73" s="134"/>
+      <c r="F73" s="134"/>
+      <c r="G73" s="134"/>
+      <c r="H73" s="134"/>
+      <c r="I73" s="133"/>
+      <c r="J73" s="133"/>
+      <c r="K73" s="134"/>
+      <c r="L73" s="134"/>
+      <c r="M73" s="134"/>
+      <c r="N73" s="134"/>
+      <c r="O73" s="134"/>
+      <c r="P73" s="134"/>
+      <c r="Q73" s="133"/>
+      <c r="R73" s="133"/>
+      <c r="S73" s="133"/>
+      <c r="T73" s="133"/>
+      <c r="U73" s="134"/>
+      <c r="V73" s="134"/>
     </row>
     <row r="74" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="139"/>
-      <c r="C74" s="139"/>
-      <c r="D74" s="139"/>
-      <c r="E74" s="139"/>
-      <c r="F74" s="139"/>
-      <c r="G74" s="139"/>
-      <c r="H74" s="139"/>
-      <c r="I74" s="138"/>
-      <c r="J74" s="138"/>
-      <c r="K74" s="139"/>
-      <c r="L74" s="139"/>
-      <c r="M74" s="139"/>
-      <c r="N74" s="139"/>
-      <c r="O74" s="139"/>
-      <c r="P74" s="139"/>
-      <c r="Q74" s="138"/>
-      <c r="R74" s="138"/>
-      <c r="S74" s="138"/>
-      <c r="T74" s="138"/>
-      <c r="U74" s="139"/>
-      <c r="V74" s="139"/>
+      <c r="B74" s="134"/>
+      <c r="C74" s="134"/>
+      <c r="D74" s="134"/>
+      <c r="E74" s="134"/>
+      <c r="F74" s="134"/>
+      <c r="G74" s="134"/>
+      <c r="H74" s="134"/>
+      <c r="I74" s="133"/>
+      <c r="J74" s="133"/>
+      <c r="K74" s="134"/>
+      <c r="L74" s="134"/>
+      <c r="M74" s="134"/>
+      <c r="N74" s="134"/>
+      <c r="O74" s="134"/>
+      <c r="P74" s="134"/>
+      <c r="Q74" s="133"/>
+      <c r="R74" s="133"/>
+      <c r="S74" s="133"/>
+      <c r="T74" s="133"/>
+      <c r="U74" s="134"/>
+      <c r="V74" s="134"/>
     </row>
     <row r="75" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="139"/>
-      <c r="C75" s="139"/>
-      <c r="D75" s="139"/>
-      <c r="E75" s="139"/>
-      <c r="F75" s="139"/>
-      <c r="G75" s="138"/>
-      <c r="H75" s="138"/>
-      <c r="I75" s="139"/>
-      <c r="J75" s="139"/>
-      <c r="K75" s="138"/>
-      <c r="L75" s="138"/>
-      <c r="M75" s="139"/>
-      <c r="N75" s="139"/>
-      <c r="O75" s="139"/>
-      <c r="P75" s="139"/>
-      <c r="Q75" s="139"/>
-      <c r="R75" s="139"/>
-      <c r="S75" s="139"/>
-      <c r="T75" s="139"/>
-      <c r="U75" s="139"/>
-      <c r="V75" s="139"/>
+      <c r="B75" s="134"/>
+      <c r="C75" s="134"/>
+      <c r="D75" s="134"/>
+      <c r="E75" s="134"/>
+      <c r="F75" s="134"/>
+      <c r="G75" s="133"/>
+      <c r="H75" s="133"/>
+      <c r="I75" s="134"/>
+      <c r="J75" s="134"/>
+      <c r="K75" s="133"/>
+      <c r="L75" s="133"/>
+      <c r="M75" s="134"/>
+      <c r="N75" s="134"/>
+      <c r="O75" s="134"/>
+      <c r="P75" s="134"/>
+      <c r="Q75" s="134"/>
+      <c r="R75" s="134"/>
+      <c r="S75" s="134"/>
+      <c r="T75" s="134"/>
+      <c r="U75" s="134"/>
+      <c r="V75" s="134"/>
     </row>
     <row r="76" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="139"/>
-      <c r="C76" s="139"/>
-      <c r="D76" s="139"/>
-      <c r="E76" s="139"/>
-      <c r="F76" s="139"/>
-      <c r="G76" s="139"/>
-      <c r="H76" s="139"/>
-      <c r="I76" s="139"/>
-      <c r="J76" s="139"/>
-      <c r="K76" s="138"/>
-      <c r="L76" s="138"/>
-      <c r="M76" s="139"/>
-      <c r="N76" s="139"/>
-      <c r="O76" s="139"/>
-      <c r="P76" s="139"/>
-      <c r="Q76" s="138"/>
-      <c r="R76" s="138"/>
-      <c r="S76" s="138"/>
-      <c r="T76" s="138"/>
-      <c r="U76" s="139"/>
-      <c r="V76" s="139"/>
+      <c r="B76" s="134"/>
+      <c r="C76" s="134"/>
+      <c r="D76" s="134"/>
+      <c r="E76" s="134"/>
+      <c r="F76" s="134"/>
+      <c r="G76" s="134"/>
+      <c r="H76" s="134"/>
+      <c r="I76" s="134"/>
+      <c r="J76" s="134"/>
+      <c r="K76" s="133"/>
+      <c r="L76" s="133"/>
+      <c r="M76" s="134"/>
+      <c r="N76" s="134"/>
+      <c r="O76" s="134"/>
+      <c r="P76" s="134"/>
+      <c r="Q76" s="133"/>
+      <c r="R76" s="133"/>
+      <c r="S76" s="133"/>
+      <c r="T76" s="133"/>
+      <c r="U76" s="134"/>
+      <c r="V76" s="134"/>
     </row>
     <row r="77" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="139"/>
-      <c r="C77" s="139"/>
-      <c r="D77" s="139"/>
-      <c r="E77" s="139"/>
-      <c r="F77" s="139"/>
-      <c r="G77" s="139"/>
-      <c r="H77" s="139"/>
-      <c r="I77" s="138"/>
-      <c r="J77" s="138"/>
-      <c r="K77" s="139"/>
-      <c r="L77" s="139"/>
-      <c r="M77" s="139"/>
-      <c r="N77" s="139"/>
-      <c r="O77" s="139"/>
-      <c r="P77" s="139"/>
-      <c r="Q77" s="138"/>
-      <c r="R77" s="138"/>
-      <c r="S77" s="138"/>
-      <c r="T77" s="138"/>
-      <c r="U77" s="139"/>
-      <c r="V77" s="139"/>
+      <c r="B77" s="134"/>
+      <c r="C77" s="134"/>
+      <c r="D77" s="134"/>
+      <c r="E77" s="134"/>
+      <c r="F77" s="134"/>
+      <c r="G77" s="134"/>
+      <c r="H77" s="134"/>
+      <c r="I77" s="133"/>
+      <c r="J77" s="133"/>
+      <c r="K77" s="134"/>
+      <c r="L77" s="134"/>
+      <c r="M77" s="134"/>
+      <c r="N77" s="134"/>
+      <c r="O77" s="134"/>
+      <c r="P77" s="134"/>
+      <c r="Q77" s="133"/>
+      <c r="R77" s="133"/>
+      <c r="S77" s="133"/>
+      <c r="T77" s="133"/>
+      <c r="U77" s="134"/>
+      <c r="V77" s="134"/>
     </row>
     <row r="78" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="139"/>
-      <c r="C78" s="139"/>
-      <c r="D78" s="139"/>
-      <c r="E78" s="139"/>
-      <c r="F78" s="139"/>
-      <c r="G78" s="138"/>
-      <c r="H78" s="138"/>
-      <c r="I78" s="139"/>
-      <c r="J78" s="139"/>
-      <c r="K78" s="138"/>
-      <c r="L78" s="138"/>
-      <c r="M78" s="139"/>
-      <c r="N78" s="139"/>
-      <c r="O78" s="139"/>
-      <c r="P78" s="139"/>
-      <c r="Q78" s="139"/>
-      <c r="R78" s="139"/>
-      <c r="S78" s="139"/>
-      <c r="T78" s="139"/>
-      <c r="U78" s="139"/>
-      <c r="V78" s="139"/>
+      <c r="B78" s="134"/>
+      <c r="C78" s="134"/>
+      <c r="D78" s="134"/>
+      <c r="E78" s="134"/>
+      <c r="F78" s="134"/>
+      <c r="G78" s="133"/>
+      <c r="H78" s="133"/>
+      <c r="I78" s="134"/>
+      <c r="J78" s="134"/>
+      <c r="K78" s="133"/>
+      <c r="L78" s="133"/>
+      <c r="M78" s="134"/>
+      <c r="N78" s="134"/>
+      <c r="O78" s="134"/>
+      <c r="P78" s="134"/>
+      <c r="Q78" s="134"/>
+      <c r="R78" s="134"/>
+      <c r="S78" s="134"/>
+      <c r="T78" s="134"/>
+      <c r="U78" s="134"/>
+      <c r="V78" s="134"/>
     </row>
     <row r="79" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="139"/>
-      <c r="C79" s="139"/>
-      <c r="D79" s="139"/>
-      <c r="E79" s="139"/>
-      <c r="F79" s="139"/>
-      <c r="G79" s="139"/>
-      <c r="H79" s="139"/>
-      <c r="I79" s="139"/>
-      <c r="J79" s="139"/>
-      <c r="K79" s="138"/>
-      <c r="L79" s="138"/>
-      <c r="M79" s="139"/>
-      <c r="N79" s="139"/>
-      <c r="O79" s="139"/>
-      <c r="P79" s="139"/>
-      <c r="Q79" s="138"/>
-      <c r="R79" s="138"/>
-      <c r="S79" s="138"/>
-      <c r="T79" s="138"/>
-      <c r="U79" s="139"/>
-      <c r="V79" s="139"/>
+      <c r="B79" s="134"/>
+      <c r="C79" s="134"/>
+      <c r="D79" s="134"/>
+      <c r="E79" s="134"/>
+      <c r="F79" s="134"/>
+      <c r="G79" s="134"/>
+      <c r="H79" s="134"/>
+      <c r="I79" s="134"/>
+      <c r="J79" s="134"/>
+      <c r="K79" s="133"/>
+      <c r="L79" s="133"/>
+      <c r="M79" s="134"/>
+      <c r="N79" s="134"/>
+      <c r="O79" s="134"/>
+      <c r="P79" s="134"/>
+      <c r="Q79" s="133"/>
+      <c r="R79" s="133"/>
+      <c r="S79" s="133"/>
+      <c r="T79" s="133"/>
+      <c r="U79" s="134"/>
+      <c r="V79" s="134"/>
     </row>
     <row r="80" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="138"/>
-      <c r="C80" s="138"/>
-      <c r="D80" s="139"/>
-      <c r="E80" s="139"/>
-      <c r="F80" s="139"/>
-      <c r="G80" s="138"/>
-      <c r="H80" s="139"/>
-      <c r="I80" s="138"/>
-      <c r="J80" s="139"/>
-      <c r="K80" s="138"/>
-      <c r="L80" s="139"/>
-      <c r="M80" s="138"/>
-      <c r="N80" s="139"/>
-      <c r="O80" s="138"/>
-      <c r="P80" s="139"/>
-      <c r="Q80" s="138"/>
-      <c r="R80" s="138"/>
-      <c r="S80" s="138"/>
-      <c r="T80" s="138"/>
-      <c r="U80" s="138"/>
-      <c r="V80" s="138"/>
+      <c r="B80" s="133"/>
+      <c r="C80" s="133"/>
+      <c r="D80" s="134"/>
+      <c r="E80" s="134"/>
+      <c r="F80" s="134"/>
+      <c r="G80" s="133"/>
+      <c r="H80" s="134"/>
+      <c r="I80" s="133"/>
+      <c r="J80" s="134"/>
+      <c r="K80" s="133"/>
+      <c r="L80" s="134"/>
+      <c r="M80" s="133"/>
+      <c r="N80" s="134"/>
+      <c r="O80" s="133"/>
+      <c r="P80" s="134"/>
+      <c r="Q80" s="133"/>
+      <c r="R80" s="133"/>
+      <c r="S80" s="133"/>
+      <c r="T80" s="133"/>
+      <c r="U80" s="133"/>
+      <c r="V80" s="133"/>
     </row>
     <row r="81" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="138"/>
-      <c r="C81" s="139"/>
-      <c r="D81" s="139"/>
-      <c r="E81" s="139"/>
-      <c r="F81" s="139"/>
-      <c r="G81" s="139"/>
-      <c r="H81" s="139"/>
-      <c r="I81" s="139"/>
-      <c r="J81" s="139"/>
-      <c r="K81" s="139"/>
-      <c r="L81" s="139"/>
-      <c r="M81" s="139"/>
-      <c r="N81" s="139"/>
-      <c r="O81" s="139"/>
-      <c r="P81" s="139"/>
-      <c r="Q81" s="138"/>
-      <c r="R81" s="138"/>
-      <c r="S81" s="138"/>
-      <c r="T81" s="138"/>
-      <c r="U81" s="138"/>
-      <c r="V81" s="139"/>
+      <c r="B81" s="133"/>
+      <c r="C81" s="134"/>
+      <c r="D81" s="134"/>
+      <c r="E81" s="134"/>
+      <c r="F81" s="134"/>
+      <c r="G81" s="134"/>
+      <c r="H81" s="134"/>
+      <c r="I81" s="134"/>
+      <c r="J81" s="134"/>
+      <c r="K81" s="134"/>
+      <c r="L81" s="134"/>
+      <c r="M81" s="134"/>
+      <c r="N81" s="134"/>
+      <c r="O81" s="134"/>
+      <c r="P81" s="134"/>
+      <c r="Q81" s="133"/>
+      <c r="R81" s="133"/>
+      <c r="S81" s="133"/>
+      <c r="T81" s="133"/>
+      <c r="U81" s="133"/>
+      <c r="V81" s="134"/>
     </row>
     <row r="82" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="138"/>
-      <c r="C82" s="138"/>
-      <c r="D82" s="138"/>
-      <c r="E82" s="138"/>
-      <c r="F82" s="138"/>
-      <c r="G82" s="138"/>
-      <c r="H82" s="138"/>
-      <c r="I82" s="138"/>
-      <c r="J82" s="138"/>
-      <c r="K82" s="138"/>
-      <c r="L82" s="138"/>
-      <c r="M82" s="138"/>
-      <c r="N82" s="138"/>
-      <c r="O82" s="138"/>
-      <c r="P82" s="138"/>
-      <c r="Q82" s="139"/>
-      <c r="R82" s="139"/>
-      <c r="S82" s="139"/>
-      <c r="T82" s="139"/>
-      <c r="U82" s="138"/>
-      <c r="V82" s="139"/>
+      <c r="B82" s="133"/>
+      <c r="C82" s="133"/>
+      <c r="D82" s="133"/>
+      <c r="E82" s="133"/>
+      <c r="F82" s="133"/>
+      <c r="G82" s="133"/>
+      <c r="H82" s="133"/>
+      <c r="I82" s="133"/>
+      <c r="J82" s="133"/>
+      <c r="K82" s="133"/>
+      <c r="L82" s="133"/>
+      <c r="M82" s="133"/>
+      <c r="N82" s="133"/>
+      <c r="O82" s="133"/>
+      <c r="P82" s="133"/>
+      <c r="Q82" s="134"/>
+      <c r="R82" s="134"/>
+      <c r="S82" s="134"/>
+      <c r="T82" s="134"/>
+      <c r="U82" s="133"/>
+      <c r="V82" s="134"/>
     </row>
     <row r="83" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="138"/>
-      <c r="C83" s="139"/>
-      <c r="D83" s="139"/>
-      <c r="E83" s="139"/>
-      <c r="F83" s="139"/>
-      <c r="G83" s="138"/>
-      <c r="H83" s="138"/>
-      <c r="I83" s="139"/>
-      <c r="J83" s="139"/>
-      <c r="K83" s="139"/>
-      <c r="L83" s="139"/>
-      <c r="M83" s="139"/>
-      <c r="N83" s="139"/>
-      <c r="O83" s="139"/>
-      <c r="P83" s="139"/>
-      <c r="Q83" s="138"/>
-      <c r="R83" s="138"/>
-      <c r="S83" s="138"/>
-      <c r="T83" s="138"/>
-      <c r="U83" s="139"/>
-      <c r="V83" s="139"/>
+      <c r="B83" s="133"/>
+      <c r="C83" s="134"/>
+      <c r="D83" s="134"/>
+      <c r="E83" s="134"/>
+      <c r="F83" s="134"/>
+      <c r="G83" s="133"/>
+      <c r="H83" s="133"/>
+      <c r="I83" s="134"/>
+      <c r="J83" s="134"/>
+      <c r="K83" s="134"/>
+      <c r="L83" s="134"/>
+      <c r="M83" s="134"/>
+      <c r="N83" s="134"/>
+      <c r="O83" s="134"/>
+      <c r="P83" s="134"/>
+      <c r="Q83" s="133"/>
+      <c r="R83" s="133"/>
+      <c r="S83" s="133"/>
+      <c r="T83" s="133"/>
+      <c r="U83" s="134"/>
+      <c r="V83" s="134"/>
     </row>
     <row r="84" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="139"/>
-      <c r="C84" s="139"/>
-      <c r="D84" s="139"/>
-      <c r="E84" s="139"/>
-      <c r="F84" s="139"/>
-      <c r="G84" s="139"/>
-      <c r="H84" s="139"/>
-      <c r="I84" s="138"/>
-      <c r="J84" s="138"/>
-      <c r="K84" s="139"/>
-      <c r="L84" s="139"/>
-      <c r="M84" s="139"/>
-      <c r="N84" s="139"/>
-      <c r="O84" s="139"/>
-      <c r="P84" s="139"/>
-      <c r="Q84" s="138"/>
-      <c r="R84" s="138"/>
-      <c r="S84" s="138"/>
-      <c r="T84" s="138"/>
-      <c r="U84" s="139"/>
-      <c r="V84" s="139"/>
+      <c r="B84" s="134"/>
+      <c r="C84" s="134"/>
+      <c r="D84" s="134"/>
+      <c r="E84" s="134"/>
+      <c r="F84" s="134"/>
+      <c r="G84" s="134"/>
+      <c r="H84" s="134"/>
+      <c r="I84" s="133"/>
+      <c r="J84" s="133"/>
+      <c r="K84" s="134"/>
+      <c r="L84" s="134"/>
+      <c r="M84" s="134"/>
+      <c r="N84" s="134"/>
+      <c r="O84" s="134"/>
+      <c r="P84" s="134"/>
+      <c r="Q84" s="133"/>
+      <c r="R84" s="133"/>
+      <c r="S84" s="133"/>
+      <c r="T84" s="133"/>
+      <c r="U84" s="134"/>
+      <c r="V84" s="134"/>
     </row>
     <row r="85" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="139"/>
-      <c r="C85" s="139"/>
-      <c r="D85" s="139"/>
-      <c r="E85" s="139"/>
-      <c r="F85" s="139"/>
-      <c r="G85" s="138"/>
-      <c r="H85" s="138"/>
-      <c r="I85" s="139"/>
-      <c r="J85" s="139"/>
-      <c r="K85" s="138"/>
-      <c r="L85" s="138"/>
-      <c r="M85" s="139"/>
-      <c r="N85" s="139"/>
-      <c r="O85" s="139"/>
-      <c r="P85" s="139"/>
-      <c r="Q85" s="139"/>
-      <c r="R85" s="139"/>
-      <c r="S85" s="139"/>
-      <c r="T85" s="139"/>
-      <c r="U85" s="139"/>
-      <c r="V85" s="139"/>
+      <c r="B85" s="134"/>
+      <c r="C85" s="134"/>
+      <c r="D85" s="134"/>
+      <c r="E85" s="134"/>
+      <c r="F85" s="134"/>
+      <c r="G85" s="133"/>
+      <c r="H85" s="133"/>
+      <c r="I85" s="134"/>
+      <c r="J85" s="134"/>
+      <c r="K85" s="133"/>
+      <c r="L85" s="133"/>
+      <c r="M85" s="134"/>
+      <c r="N85" s="134"/>
+      <c r="O85" s="134"/>
+      <c r="P85" s="134"/>
+      <c r="Q85" s="134"/>
+      <c r="R85" s="134"/>
+      <c r="S85" s="134"/>
+      <c r="T85" s="134"/>
+      <c r="U85" s="134"/>
+      <c r="V85" s="134"/>
     </row>
     <row r="86" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="139"/>
-      <c r="C86" s="139"/>
-      <c r="D86" s="139"/>
-      <c r="E86" s="139"/>
-      <c r="F86" s="139"/>
-      <c r="G86" s="139"/>
-      <c r="H86" s="139"/>
-      <c r="I86" s="139"/>
-      <c r="J86" s="139"/>
-      <c r="K86" s="138"/>
-      <c r="L86" s="138"/>
-      <c r="M86" s="139"/>
-      <c r="N86" s="139"/>
-      <c r="O86" s="139"/>
-      <c r="P86" s="139"/>
-      <c r="Q86" s="138"/>
-      <c r="R86" s="138"/>
-      <c r="S86" s="138"/>
-      <c r="T86" s="138"/>
-      <c r="U86" s="139"/>
-      <c r="V86" s="139"/>
+      <c r="B86" s="134"/>
+      <c r="C86" s="134"/>
+      <c r="D86" s="134"/>
+      <c r="E86" s="134"/>
+      <c r="F86" s="134"/>
+      <c r="G86" s="134"/>
+      <c r="H86" s="134"/>
+      <c r="I86" s="134"/>
+      <c r="J86" s="134"/>
+      <c r="K86" s="133"/>
+      <c r="L86" s="133"/>
+      <c r="M86" s="134"/>
+      <c r="N86" s="134"/>
+      <c r="O86" s="134"/>
+      <c r="P86" s="134"/>
+      <c r="Q86" s="133"/>
+      <c r="R86" s="133"/>
+      <c r="S86" s="133"/>
+      <c r="T86" s="133"/>
+      <c r="U86" s="134"/>
+      <c r="V86" s="134"/>
     </row>
     <row r="87" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="139"/>
-      <c r="C87" s="139"/>
-      <c r="D87" s="139"/>
-      <c r="E87" s="139"/>
-      <c r="F87" s="139"/>
-      <c r="G87" s="138"/>
-      <c r="H87" s="138"/>
-      <c r="I87" s="139"/>
-      <c r="J87" s="139"/>
-      <c r="K87" s="138"/>
-      <c r="L87" s="138"/>
-      <c r="M87" s="139"/>
-      <c r="N87" s="139"/>
-      <c r="O87" s="139"/>
-      <c r="P87" s="139"/>
-      <c r="Q87" s="139"/>
-      <c r="R87" s="139"/>
-      <c r="S87" s="139"/>
-      <c r="T87" s="139"/>
-      <c r="U87" s="139"/>
-      <c r="V87" s="139"/>
+      <c r="B87" s="134"/>
+      <c r="C87" s="134"/>
+      <c r="D87" s="134"/>
+      <c r="E87" s="134"/>
+      <c r="F87" s="134"/>
+      <c r="G87" s="133"/>
+      <c r="H87" s="133"/>
+      <c r="I87" s="134"/>
+      <c r="J87" s="134"/>
+      <c r="K87" s="133"/>
+      <c r="L87" s="133"/>
+      <c r="M87" s="134"/>
+      <c r="N87" s="134"/>
+      <c r="O87" s="134"/>
+      <c r="P87" s="134"/>
+      <c r="Q87" s="134"/>
+      <c r="R87" s="134"/>
+      <c r="S87" s="134"/>
+      <c r="T87" s="134"/>
+      <c r="U87" s="134"/>
+      <c r="V87" s="134"/>
     </row>
     <row r="88" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="139"/>
-      <c r="C88" s="139"/>
-      <c r="D88" s="139"/>
-      <c r="E88" s="139"/>
-      <c r="F88" s="139"/>
-      <c r="G88" s="139"/>
-      <c r="H88" s="139"/>
-      <c r="I88" s="139"/>
-      <c r="J88" s="139"/>
-      <c r="K88" s="138"/>
-      <c r="L88" s="138"/>
-      <c r="M88" s="139"/>
-      <c r="N88" s="139"/>
-      <c r="O88" s="139"/>
-      <c r="P88" s="139"/>
-      <c r="Q88" s="138"/>
-      <c r="R88" s="138"/>
-      <c r="S88" s="138"/>
-      <c r="T88" s="138"/>
-      <c r="U88" s="139"/>
-      <c r="V88" s="139"/>
+      <c r="B88" s="134"/>
+      <c r="C88" s="134"/>
+      <c r="D88" s="134"/>
+      <c r="E88" s="134"/>
+      <c r="F88" s="134"/>
+      <c r="G88" s="134"/>
+      <c r="H88" s="134"/>
+      <c r="I88" s="134"/>
+      <c r="J88" s="134"/>
+      <c r="K88" s="133"/>
+      <c r="L88" s="133"/>
+      <c r="M88" s="134"/>
+      <c r="N88" s="134"/>
+      <c r="O88" s="134"/>
+      <c r="P88" s="134"/>
+      <c r="Q88" s="133"/>
+      <c r="R88" s="133"/>
+      <c r="S88" s="133"/>
+      <c r="T88" s="133"/>
+      <c r="U88" s="134"/>
+      <c r="V88" s="134"/>
     </row>
     <row r="89" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="139"/>
-      <c r="C89" s="139"/>
-      <c r="D89" s="139"/>
-      <c r="E89" s="139"/>
-      <c r="F89" s="139"/>
-      <c r="G89" s="139"/>
-      <c r="H89" s="139"/>
-      <c r="I89" s="138"/>
-      <c r="J89" s="138"/>
-      <c r="K89" s="139"/>
-      <c r="L89" s="139"/>
-      <c r="M89" s="139"/>
-      <c r="N89" s="139"/>
-      <c r="O89" s="139"/>
-      <c r="P89" s="139"/>
-      <c r="Q89" s="138"/>
-      <c r="R89" s="138"/>
-      <c r="S89" s="138"/>
-      <c r="T89" s="138"/>
-      <c r="U89" s="139"/>
-      <c r="V89" s="139"/>
+      <c r="B89" s="134"/>
+      <c r="C89" s="134"/>
+      <c r="D89" s="134"/>
+      <c r="E89" s="134"/>
+      <c r="F89" s="134"/>
+      <c r="G89" s="134"/>
+      <c r="H89" s="134"/>
+      <c r="I89" s="133"/>
+      <c r="J89" s="133"/>
+      <c r="K89" s="134"/>
+      <c r="L89" s="134"/>
+      <c r="M89" s="134"/>
+      <c r="N89" s="134"/>
+      <c r="O89" s="134"/>
+      <c r="P89" s="134"/>
+      <c r="Q89" s="133"/>
+      <c r="R89" s="133"/>
+      <c r="S89" s="133"/>
+      <c r="T89" s="133"/>
+      <c r="U89" s="134"/>
+      <c r="V89" s="134"/>
     </row>
     <row r="90" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="139"/>
-      <c r="C90" s="139"/>
-      <c r="D90" s="139"/>
-      <c r="E90" s="139"/>
-      <c r="F90" s="139"/>
-      <c r="G90" s="139"/>
-      <c r="H90" s="139"/>
-      <c r="I90" s="138"/>
-      <c r="J90" s="138"/>
-      <c r="K90" s="139"/>
-      <c r="L90" s="139"/>
-      <c r="M90" s="139"/>
-      <c r="N90" s="139"/>
-      <c r="O90" s="139"/>
-      <c r="P90" s="139"/>
-      <c r="Q90" s="138"/>
-      <c r="R90" s="138"/>
-      <c r="S90" s="138"/>
-      <c r="T90" s="138"/>
-      <c r="U90" s="139"/>
-      <c r="V90" s="139"/>
+      <c r="B90" s="134"/>
+      <c r="C90" s="134"/>
+      <c r="D90" s="134"/>
+      <c r="E90" s="134"/>
+      <c r="F90" s="134"/>
+      <c r="G90" s="134"/>
+      <c r="H90" s="134"/>
+      <c r="I90" s="133"/>
+      <c r="J90" s="133"/>
+      <c r="K90" s="134"/>
+      <c r="L90" s="134"/>
+      <c r="M90" s="134"/>
+      <c r="N90" s="134"/>
+      <c r="O90" s="134"/>
+      <c r="P90" s="134"/>
+      <c r="Q90" s="133"/>
+      <c r="R90" s="133"/>
+      <c r="S90" s="133"/>
+      <c r="T90" s="133"/>
+      <c r="U90" s="134"/>
+      <c r="V90" s="134"/>
     </row>
     <row r="91" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="139"/>
-      <c r="C91" s="139"/>
-      <c r="D91" s="139"/>
-      <c r="E91" s="139"/>
-      <c r="F91" s="139"/>
-      <c r="G91" s="139"/>
-      <c r="H91" s="139"/>
-      <c r="I91" s="138"/>
-      <c r="J91" s="138"/>
-      <c r="K91" s="139"/>
-      <c r="L91" s="139"/>
-      <c r="M91" s="139"/>
-      <c r="N91" s="139"/>
-      <c r="O91" s="139"/>
-      <c r="P91" s="139"/>
-      <c r="Q91" s="138"/>
-      <c r="R91" s="138"/>
-      <c r="S91" s="138"/>
-      <c r="T91" s="138"/>
-      <c r="U91" s="139"/>
-      <c r="V91" s="139"/>
+      <c r="B91" s="134"/>
+      <c r="C91" s="134"/>
+      <c r="D91" s="134"/>
+      <c r="E91" s="134"/>
+      <c r="F91" s="134"/>
+      <c r="G91" s="134"/>
+      <c r="H91" s="134"/>
+      <c r="I91" s="133"/>
+      <c r="J91" s="133"/>
+      <c r="K91" s="134"/>
+      <c r="L91" s="134"/>
+      <c r="M91" s="134"/>
+      <c r="N91" s="134"/>
+      <c r="O91" s="134"/>
+      <c r="P91" s="134"/>
+      <c r="Q91" s="133"/>
+      <c r="R91" s="133"/>
+      <c r="S91" s="133"/>
+      <c r="T91" s="133"/>
+      <c r="U91" s="134"/>
+      <c r="V91" s="134"/>
     </row>
     <row r="92" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="139"/>
-      <c r="C92" s="139"/>
-      <c r="D92" s="139"/>
-      <c r="E92" s="139"/>
-      <c r="F92" s="139"/>
-      <c r="G92" s="139"/>
-      <c r="H92" s="139"/>
-      <c r="I92" s="138"/>
-      <c r="J92" s="138"/>
-      <c r="K92" s="139"/>
-      <c r="L92" s="139"/>
-      <c r="M92" s="139"/>
-      <c r="N92" s="139"/>
-      <c r="O92" s="139"/>
-      <c r="P92" s="139"/>
-      <c r="Q92" s="138"/>
-      <c r="R92" s="138"/>
-      <c r="S92" s="138"/>
-      <c r="T92" s="138"/>
-      <c r="U92" s="139"/>
-      <c r="V92" s="139"/>
+      <c r="B92" s="134"/>
+      <c r="C92" s="134"/>
+      <c r="D92" s="134"/>
+      <c r="E92" s="134"/>
+      <c r="F92" s="134"/>
+      <c r="G92" s="134"/>
+      <c r="H92" s="134"/>
+      <c r="I92" s="133"/>
+      <c r="J92" s="133"/>
+      <c r="K92" s="134"/>
+      <c r="L92" s="134"/>
+      <c r="M92" s="134"/>
+      <c r="N92" s="134"/>
+      <c r="O92" s="134"/>
+      <c r="P92" s="134"/>
+      <c r="Q92" s="133"/>
+      <c r="R92" s="133"/>
+      <c r="S92" s="133"/>
+      <c r="T92" s="133"/>
+      <c r="U92" s="134"/>
+      <c r="V92" s="134"/>
     </row>
     <row r="93" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="139"/>
-      <c r="C93" s="139"/>
-      <c r="D93" s="139"/>
-      <c r="E93" s="139"/>
-      <c r="F93" s="139"/>
-      <c r="G93" s="138"/>
-      <c r="H93" s="138"/>
-      <c r="I93" s="139"/>
-      <c r="J93" s="139"/>
-      <c r="K93" s="139"/>
-      <c r="L93" s="139"/>
-      <c r="M93" s="139"/>
-      <c r="N93" s="139"/>
-      <c r="O93" s="139"/>
-      <c r="P93" s="139"/>
-      <c r="Q93" s="138"/>
-      <c r="R93" s="138"/>
-      <c r="S93" s="138"/>
-      <c r="T93" s="138"/>
-      <c r="U93" s="139"/>
-      <c r="V93" s="139"/>
+      <c r="B93" s="134"/>
+      <c r="C93" s="134"/>
+      <c r="D93" s="134"/>
+      <c r="E93" s="134"/>
+      <c r="F93" s="134"/>
+      <c r="G93" s="133"/>
+      <c r="H93" s="133"/>
+      <c r="I93" s="134"/>
+      <c r="J93" s="134"/>
+      <c r="K93" s="134"/>
+      <c r="L93" s="134"/>
+      <c r="M93" s="134"/>
+      <c r="N93" s="134"/>
+      <c r="O93" s="134"/>
+      <c r="P93" s="134"/>
+      <c r="Q93" s="133"/>
+      <c r="R93" s="133"/>
+      <c r="S93" s="133"/>
+      <c r="T93" s="133"/>
+      <c r="U93" s="134"/>
+      <c r="V93" s="134"/>
     </row>
     <row r="94" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="138"/>
-      <c r="C94" s="138"/>
-      <c r="D94" s="139"/>
-      <c r="E94" s="139"/>
-      <c r="F94" s="139"/>
-      <c r="G94" s="138"/>
-      <c r="H94" s="139"/>
-      <c r="I94" s="138"/>
-      <c r="J94" s="139"/>
-      <c r="K94" s="138"/>
-      <c r="L94" s="139"/>
-      <c r="M94" s="138"/>
-      <c r="N94" s="139"/>
-      <c r="O94" s="138"/>
-      <c r="P94" s="139"/>
-      <c r="Q94" s="138"/>
-      <c r="R94" s="138"/>
-      <c r="S94" s="138"/>
-      <c r="T94" s="138"/>
-      <c r="U94" s="138"/>
-      <c r="V94" s="138"/>
+      <c r="B94" s="133"/>
+      <c r="C94" s="133"/>
+      <c r="D94" s="134"/>
+      <c r="E94" s="134"/>
+      <c r="F94" s="134"/>
+      <c r="G94" s="133"/>
+      <c r="H94" s="134"/>
+      <c r="I94" s="133"/>
+      <c r="J94" s="134"/>
+      <c r="K94" s="133"/>
+      <c r="L94" s="134"/>
+      <c r="M94" s="133"/>
+      <c r="N94" s="134"/>
+      <c r="O94" s="133"/>
+      <c r="P94" s="134"/>
+      <c r="Q94" s="133"/>
+      <c r="R94" s="133"/>
+      <c r="S94" s="133"/>
+      <c r="T94" s="133"/>
+      <c r="U94" s="133"/>
+      <c r="V94" s="133"/>
     </row>
     <row r="95" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="138"/>
-      <c r="C95" s="139"/>
-      <c r="D95" s="139"/>
-      <c r="E95" s="139"/>
-      <c r="F95" s="139"/>
-      <c r="G95" s="139"/>
-      <c r="H95" s="139"/>
-      <c r="I95" s="139"/>
-      <c r="J95" s="139"/>
-      <c r="K95" s="139"/>
-      <c r="L95" s="139"/>
-      <c r="M95" s="139"/>
-      <c r="N95" s="139"/>
-      <c r="O95" s="139"/>
-      <c r="P95" s="139"/>
-      <c r="Q95" s="138"/>
-      <c r="R95" s="138"/>
-      <c r="S95" s="138"/>
-      <c r="T95" s="138"/>
-      <c r="U95" s="138"/>
-      <c r="V95" s="139"/>
+      <c r="B95" s="133"/>
+      <c r="C95" s="134"/>
+      <c r="D95" s="134"/>
+      <c r="E95" s="134"/>
+      <c r="F95" s="134"/>
+      <c r="G95" s="134"/>
+      <c r="H95" s="134"/>
+      <c r="I95" s="134"/>
+      <c r="J95" s="134"/>
+      <c r="K95" s="134"/>
+      <c r="L95" s="134"/>
+      <c r="M95" s="134"/>
+      <c r="N95" s="134"/>
+      <c r="O95" s="134"/>
+      <c r="P95" s="134"/>
+      <c r="Q95" s="133"/>
+      <c r="R95" s="133"/>
+      <c r="S95" s="133"/>
+      <c r="T95" s="133"/>
+      <c r="U95" s="133"/>
+      <c r="V95" s="134"/>
     </row>
     <row r="96" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B96" s="138"/>
-      <c r="C96" s="138"/>
-      <c r="D96" s="138"/>
-      <c r="E96" s="138"/>
-      <c r="F96" s="138"/>
-      <c r="G96" s="138"/>
-      <c r="H96" s="138"/>
-      <c r="I96" s="138"/>
-      <c r="J96" s="138"/>
-      <c r="K96" s="138"/>
-      <c r="L96" s="138"/>
-      <c r="M96" s="138"/>
-      <c r="N96" s="138"/>
-      <c r="O96" s="138"/>
-      <c r="P96" s="138"/>
-      <c r="Q96" s="139"/>
-      <c r="R96" s="139"/>
-      <c r="S96" s="139"/>
-      <c r="T96" s="139"/>
-      <c r="U96" s="138"/>
-      <c r="V96" s="139"/>
+      <c r="B96" s="133"/>
+      <c r="C96" s="133"/>
+      <c r="D96" s="133"/>
+      <c r="E96" s="133"/>
+      <c r="F96" s="133"/>
+      <c r="G96" s="133"/>
+      <c r="H96" s="133"/>
+      <c r="I96" s="133"/>
+      <c r="J96" s="133"/>
+      <c r="K96" s="133"/>
+      <c r="L96" s="133"/>
+      <c r="M96" s="133"/>
+      <c r="N96" s="133"/>
+      <c r="O96" s="133"/>
+      <c r="P96" s="133"/>
+      <c r="Q96" s="134"/>
+      <c r="R96" s="134"/>
+      <c r="S96" s="134"/>
+      <c r="T96" s="134"/>
+      <c r="U96" s="133"/>
+      <c r="V96" s="134"/>
     </row>
     <row r="97" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B97" s="138"/>
-      <c r="C97" s="139"/>
-      <c r="D97" s="139"/>
-      <c r="E97" s="139"/>
-      <c r="F97" s="139"/>
-      <c r="G97" s="138"/>
-      <c r="H97" s="138"/>
-      <c r="I97" s="139"/>
-      <c r="J97" s="139"/>
-      <c r="K97" s="138"/>
-      <c r="L97" s="138"/>
-      <c r="M97" s="139"/>
-      <c r="N97" s="139"/>
-      <c r="O97" s="139"/>
-      <c r="P97" s="139"/>
-      <c r="Q97" s="139"/>
-      <c r="R97" s="139"/>
-      <c r="S97" s="139"/>
-      <c r="T97" s="139"/>
-      <c r="U97" s="139"/>
-      <c r="V97" s="139"/>
+      <c r="B97" s="133"/>
+      <c r="C97" s="134"/>
+      <c r="D97" s="134"/>
+      <c r="E97" s="134"/>
+      <c r="F97" s="134"/>
+      <c r="G97" s="133"/>
+      <c r="H97" s="133"/>
+      <c r="I97" s="134"/>
+      <c r="J97" s="134"/>
+      <c r="K97" s="133"/>
+      <c r="L97" s="133"/>
+      <c r="M97" s="134"/>
+      <c r="N97" s="134"/>
+      <c r="O97" s="134"/>
+      <c r="P97" s="134"/>
+      <c r="Q97" s="134"/>
+      <c r="R97" s="134"/>
+      <c r="S97" s="134"/>
+      <c r="T97" s="134"/>
+      <c r="U97" s="134"/>
+      <c r="V97" s="134"/>
     </row>
     <row r="98" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B98" s="139"/>
-      <c r="C98" s="139"/>
-      <c r="D98" s="139"/>
-      <c r="E98" s="139"/>
-      <c r="F98" s="139"/>
-      <c r="G98" s="139"/>
-      <c r="H98" s="139"/>
-      <c r="I98" s="139"/>
-      <c r="J98" s="139"/>
-      <c r="K98" s="138"/>
-      <c r="L98" s="138"/>
-      <c r="M98" s="139"/>
-      <c r="N98" s="139"/>
-      <c r="O98" s="139"/>
-      <c r="P98" s="139"/>
-      <c r="Q98" s="138"/>
-      <c r="R98" s="138"/>
-      <c r="S98" s="138"/>
-      <c r="T98" s="138"/>
-      <c r="U98" s="139"/>
-      <c r="V98" s="139"/>
+      <c r="B98" s="134"/>
+      <c r="C98" s="134"/>
+      <c r="D98" s="134"/>
+      <c r="E98" s="134"/>
+      <c r="F98" s="134"/>
+      <c r="G98" s="134"/>
+      <c r="H98" s="134"/>
+      <c r="I98" s="134"/>
+      <c r="J98" s="134"/>
+      <c r="K98" s="133"/>
+      <c r="L98" s="133"/>
+      <c r="M98" s="134"/>
+      <c r="N98" s="134"/>
+      <c r="O98" s="134"/>
+      <c r="P98" s="134"/>
+      <c r="Q98" s="133"/>
+      <c r="R98" s="133"/>
+      <c r="S98" s="133"/>
+      <c r="T98" s="133"/>
+      <c r="U98" s="134"/>
+      <c r="V98" s="134"/>
     </row>
     <row r="99" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="139"/>
-      <c r="C99" s="139"/>
-      <c r="D99" s="139"/>
-      <c r="E99" s="139"/>
-      <c r="F99" s="139"/>
-      <c r="G99" s="138"/>
-      <c r="H99" s="138"/>
-      <c r="I99" s="139"/>
-      <c r="J99" s="139"/>
-      <c r="K99" s="139"/>
-      <c r="L99" s="139"/>
-      <c r="M99" s="139"/>
-      <c r="N99" s="139"/>
-      <c r="O99" s="139"/>
-      <c r="P99" s="139"/>
-      <c r="Q99" s="138"/>
-      <c r="R99" s="138"/>
-      <c r="S99" s="138"/>
-      <c r="T99" s="138"/>
-      <c r="U99" s="139"/>
-      <c r="V99" s="139"/>
+      <c r="B99" s="134"/>
+      <c r="C99" s="134"/>
+      <c r="D99" s="134"/>
+      <c r="E99" s="134"/>
+      <c r="F99" s="134"/>
+      <c r="G99" s="133"/>
+      <c r="H99" s="133"/>
+      <c r="I99" s="134"/>
+      <c r="J99" s="134"/>
+      <c r="K99" s="134"/>
+      <c r="L99" s="134"/>
+      <c r="M99" s="134"/>
+      <c r="N99" s="134"/>
+      <c r="O99" s="134"/>
+      <c r="P99" s="134"/>
+      <c r="Q99" s="133"/>
+      <c r="R99" s="133"/>
+      <c r="S99" s="133"/>
+      <c r="T99" s="133"/>
+      <c r="U99" s="134"/>
+      <c r="V99" s="134"/>
     </row>
     <row r="100" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B100" s="139"/>
-      <c r="C100" s="139"/>
-      <c r="D100" s="139"/>
-      <c r="E100" s="139"/>
-      <c r="F100" s="139"/>
-      <c r="G100" s="138"/>
-      <c r="H100" s="138"/>
-      <c r="I100" s="139"/>
-      <c r="J100" s="139"/>
-      <c r="K100" s="138"/>
-      <c r="L100" s="138"/>
-      <c r="M100" s="139"/>
-      <c r="N100" s="139"/>
-      <c r="O100" s="139"/>
-      <c r="P100" s="139"/>
-      <c r="Q100" s="139"/>
-      <c r="R100" s="139"/>
-      <c r="S100" s="139"/>
-      <c r="T100" s="139"/>
-      <c r="U100" s="139"/>
-      <c r="V100" s="139"/>
+      <c r="B100" s="134"/>
+      <c r="C100" s="134"/>
+      <c r="D100" s="134"/>
+      <c r="E100" s="134"/>
+      <c r="F100" s="134"/>
+      <c r="G100" s="133"/>
+      <c r="H100" s="133"/>
+      <c r="I100" s="134"/>
+      <c r="J100" s="134"/>
+      <c r="K100" s="133"/>
+      <c r="L100" s="133"/>
+      <c r="M100" s="134"/>
+      <c r="N100" s="134"/>
+      <c r="O100" s="134"/>
+      <c r="P100" s="134"/>
+      <c r="Q100" s="134"/>
+      <c r="R100" s="134"/>
+      <c r="S100" s="134"/>
+      <c r="T100" s="134"/>
+      <c r="U100" s="134"/>
+      <c r="V100" s="134"/>
     </row>
     <row r="101" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="139"/>
-      <c r="C101" s="139"/>
-      <c r="D101" s="139"/>
-      <c r="E101" s="139"/>
-      <c r="F101" s="139"/>
-      <c r="G101" s="139"/>
-      <c r="H101" s="139"/>
-      <c r="I101" s="139"/>
-      <c r="J101" s="139"/>
-      <c r="K101" s="138"/>
-      <c r="L101" s="138"/>
-      <c r="M101" s="139"/>
-      <c r="N101" s="139"/>
-      <c r="O101" s="139"/>
-      <c r="P101" s="139"/>
-      <c r="Q101" s="138"/>
-      <c r="R101" s="138"/>
-      <c r="S101" s="138"/>
-      <c r="T101" s="138"/>
-      <c r="U101" s="139"/>
-      <c r="V101" s="139"/>
+      <c r="B101" s="134"/>
+      <c r="C101" s="134"/>
+      <c r="D101" s="134"/>
+      <c r="E101" s="134"/>
+      <c r="F101" s="134"/>
+      <c r="G101" s="134"/>
+      <c r="H101" s="134"/>
+      <c r="I101" s="134"/>
+      <c r="J101" s="134"/>
+      <c r="K101" s="133"/>
+      <c r="L101" s="133"/>
+      <c r="M101" s="134"/>
+      <c r="N101" s="134"/>
+      <c r="O101" s="134"/>
+      <c r="P101" s="134"/>
+      <c r="Q101" s="133"/>
+      <c r="R101" s="133"/>
+      <c r="S101" s="133"/>
+      <c r="T101" s="133"/>
+      <c r="U101" s="134"/>
+      <c r="V101" s="134"/>
     </row>
     <row r="102" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B102" s="138"/>
-      <c r="C102" s="138"/>
-      <c r="D102" s="139"/>
-      <c r="E102" s="139"/>
-      <c r="F102" s="139"/>
-      <c r="G102" s="138"/>
-      <c r="H102" s="139"/>
-      <c r="I102" s="138"/>
-      <c r="J102" s="139"/>
-      <c r="K102" s="138"/>
-      <c r="L102" s="139"/>
-      <c r="M102" s="138"/>
-      <c r="N102" s="139"/>
-      <c r="O102" s="138"/>
-      <c r="P102" s="139"/>
-      <c r="Q102" s="138"/>
-      <c r="R102" s="138"/>
-      <c r="S102" s="138"/>
-      <c r="T102" s="138"/>
-      <c r="U102" s="138"/>
-      <c r="V102" s="138"/>
+      <c r="B102" s="133"/>
+      <c r="C102" s="133"/>
+      <c r="D102" s="134"/>
+      <c r="E102" s="134"/>
+      <c r="F102" s="134"/>
+      <c r="G102" s="133"/>
+      <c r="H102" s="134"/>
+      <c r="I102" s="133"/>
+      <c r="J102" s="134"/>
+      <c r="K102" s="133"/>
+      <c r="L102" s="134"/>
+      <c r="M102" s="133"/>
+      <c r="N102" s="134"/>
+      <c r="O102" s="133"/>
+      <c r="P102" s="134"/>
+      <c r="Q102" s="133"/>
+      <c r="R102" s="133"/>
+      <c r="S102" s="133"/>
+      <c r="T102" s="133"/>
+      <c r="U102" s="133"/>
+      <c r="V102" s="133"/>
     </row>
     <row r="103" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B103" s="138"/>
-      <c r="C103" s="139"/>
-      <c r="D103" s="139"/>
-      <c r="E103" s="139"/>
-      <c r="F103" s="139"/>
-      <c r="G103" s="139"/>
-      <c r="H103" s="139"/>
-      <c r="I103" s="139"/>
-      <c r="J103" s="139"/>
-      <c r="K103" s="139"/>
-      <c r="L103" s="139"/>
-      <c r="M103" s="139"/>
-      <c r="N103" s="139"/>
-      <c r="O103" s="139"/>
-      <c r="P103" s="139"/>
-      <c r="Q103" s="138"/>
-      <c r="R103" s="138"/>
-      <c r="S103" s="138"/>
-      <c r="T103" s="138"/>
-      <c r="U103" s="138"/>
-      <c r="V103" s="139"/>
+      <c r="B103" s="133"/>
+      <c r="C103" s="134"/>
+      <c r="D103" s="134"/>
+      <c r="E103" s="134"/>
+      <c r="F103" s="134"/>
+      <c r="G103" s="134"/>
+      <c r="H103" s="134"/>
+      <c r="I103" s="134"/>
+      <c r="J103" s="134"/>
+      <c r="K103" s="134"/>
+      <c r="L103" s="134"/>
+      <c r="M103" s="134"/>
+      <c r="N103" s="134"/>
+      <c r="O103" s="134"/>
+      <c r="P103" s="134"/>
+      <c r="Q103" s="133"/>
+      <c r="R103" s="133"/>
+      <c r="S103" s="133"/>
+      <c r="T103" s="133"/>
+      <c r="U103" s="133"/>
+      <c r="V103" s="134"/>
     </row>
     <row r="104" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="138"/>
-      <c r="C104" s="139"/>
-      <c r="D104" s="139"/>
-      <c r="E104" s="139"/>
-      <c r="F104" s="139"/>
-      <c r="G104" s="139"/>
-      <c r="H104" s="139"/>
-      <c r="I104" s="138"/>
-      <c r="J104" s="138"/>
-      <c r="K104" s="139"/>
-      <c r="L104" s="139"/>
-      <c r="M104" s="139"/>
-      <c r="N104" s="139"/>
-      <c r="O104" s="139"/>
-      <c r="P104" s="139"/>
-      <c r="Q104" s="138"/>
-      <c r="R104" s="138"/>
-      <c r="S104" s="138"/>
-      <c r="T104" s="138"/>
-      <c r="U104" s="139"/>
-      <c r="V104" s="139"/>
+      <c r="B104" s="133"/>
+      <c r="C104" s="134"/>
+      <c r="D104" s="134"/>
+      <c r="E104" s="134"/>
+      <c r="F104" s="134"/>
+      <c r="G104" s="134"/>
+      <c r="H104" s="134"/>
+      <c r="I104" s="133"/>
+      <c r="J104" s="133"/>
+      <c r="K104" s="134"/>
+      <c r="L104" s="134"/>
+      <c r="M104" s="134"/>
+      <c r="N104" s="134"/>
+      <c r="O104" s="134"/>
+      <c r="P104" s="134"/>
+      <c r="Q104" s="133"/>
+      <c r="R104" s="133"/>
+      <c r="S104" s="133"/>
+      <c r="T104" s="133"/>
+      <c r="U104" s="134"/>
+      <c r="V104" s="134"/>
     </row>
     <row r="105" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="139"/>
-      <c r="C105" s="139"/>
-      <c r="D105" s="139"/>
-      <c r="E105" s="139"/>
-      <c r="F105" s="139"/>
-      <c r="G105" s="139"/>
-      <c r="H105" s="139"/>
-      <c r="I105" s="138"/>
-      <c r="J105" s="138"/>
-      <c r="K105" s="139"/>
-      <c r="L105" s="139"/>
-      <c r="M105" s="139"/>
-      <c r="N105" s="139"/>
-      <c r="O105" s="139"/>
-      <c r="P105" s="139"/>
-      <c r="Q105" s="138"/>
-      <c r="R105" s="138"/>
-      <c r="S105" s="138"/>
-      <c r="T105" s="138"/>
-      <c r="U105" s="139"/>
-      <c r="V105" s="139"/>
+      <c r="B105" s="134"/>
+      <c r="C105" s="134"/>
+      <c r="D105" s="134"/>
+      <c r="E105" s="134"/>
+      <c r="F105" s="134"/>
+      <c r="G105" s="134"/>
+      <c r="H105" s="134"/>
+      <c r="I105" s="133"/>
+      <c r="J105" s="133"/>
+      <c r="K105" s="134"/>
+      <c r="L105" s="134"/>
+      <c r="M105" s="134"/>
+      <c r="N105" s="134"/>
+      <c r="O105" s="134"/>
+      <c r="P105" s="134"/>
+      <c r="Q105" s="133"/>
+      <c r="R105" s="133"/>
+      <c r="S105" s="133"/>
+      <c r="T105" s="133"/>
+      <c r="U105" s="134"/>
+      <c r="V105" s="134"/>
     </row>
     <row r="106" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="139"/>
-      <c r="C106" s="139"/>
-      <c r="D106" s="139"/>
-      <c r="E106" s="139"/>
-      <c r="F106" s="139"/>
-      <c r="G106" s="138"/>
-      <c r="H106" s="138"/>
-      <c r="I106" s="139"/>
-      <c r="J106" s="139"/>
-      <c r="K106" s="138"/>
-      <c r="L106" s="138"/>
-      <c r="M106" s="139"/>
-      <c r="N106" s="139"/>
-      <c r="O106" s="139"/>
-      <c r="P106" s="139"/>
-      <c r="Q106" s="139"/>
-      <c r="R106" s="139"/>
-      <c r="S106" s="139"/>
-      <c r="T106" s="139"/>
-      <c r="U106" s="139"/>
-      <c r="V106" s="139"/>
+      <c r="B106" s="134"/>
+      <c r="C106" s="134"/>
+      <c r="D106" s="134"/>
+      <c r="E106" s="134"/>
+      <c r="F106" s="134"/>
+      <c r="G106" s="133"/>
+      <c r="H106" s="133"/>
+      <c r="I106" s="134"/>
+      <c r="J106" s="134"/>
+      <c r="K106" s="133"/>
+      <c r="L106" s="133"/>
+      <c r="M106" s="134"/>
+      <c r="N106" s="134"/>
+      <c r="O106" s="134"/>
+      <c r="P106" s="134"/>
+      <c r="Q106" s="134"/>
+      <c r="R106" s="134"/>
+      <c r="S106" s="134"/>
+      <c r="T106" s="134"/>
+      <c r="U106" s="134"/>
+      <c r="V106" s="134"/>
     </row>
     <row r="107" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="139"/>
-      <c r="C107" s="139"/>
-      <c r="D107" s="139"/>
-      <c r="E107" s="139"/>
-      <c r="F107" s="139"/>
-      <c r="G107" s="139"/>
-      <c r="H107" s="139"/>
-      <c r="I107" s="139"/>
-      <c r="J107" s="139"/>
-      <c r="K107" s="138"/>
-      <c r="L107" s="138"/>
-      <c r="M107" s="139"/>
-      <c r="N107" s="139"/>
-      <c r="O107" s="139"/>
-      <c r="P107" s="139"/>
-      <c r="Q107" s="138"/>
-      <c r="R107" s="138"/>
-      <c r="S107" s="138"/>
-      <c r="T107" s="138"/>
-      <c r="U107" s="139"/>
-      <c r="V107" s="139"/>
+      <c r="B107" s="134"/>
+      <c r="C107" s="134"/>
+      <c r="D107" s="134"/>
+      <c r="E107" s="134"/>
+      <c r="F107" s="134"/>
+      <c r="G107" s="134"/>
+      <c r="H107" s="134"/>
+      <c r="I107" s="134"/>
+      <c r="J107" s="134"/>
+      <c r="K107" s="133"/>
+      <c r="L107" s="133"/>
+      <c r="M107" s="134"/>
+      <c r="N107" s="134"/>
+      <c r="O107" s="134"/>
+      <c r="P107" s="134"/>
+      <c r="Q107" s="133"/>
+      <c r="R107" s="133"/>
+      <c r="S107" s="133"/>
+      <c r="T107" s="133"/>
+      <c r="U107" s="134"/>
+      <c r="V107" s="134"/>
     </row>
     <row r="108" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="139"/>
-      <c r="C108" s="139"/>
-      <c r="D108" s="139"/>
-      <c r="E108" s="139"/>
-      <c r="F108" s="139"/>
-      <c r="G108" s="138"/>
-      <c r="H108" s="138"/>
-      <c r="I108" s="139"/>
-      <c r="J108" s="139"/>
-      <c r="K108" s="139"/>
-      <c r="L108" s="139"/>
-      <c r="M108" s="138"/>
-      <c r="N108" s="138"/>
-      <c r="O108" s="139"/>
-      <c r="P108" s="139"/>
-      <c r="Q108" s="139"/>
-      <c r="R108" s="139"/>
-      <c r="S108" s="139"/>
-      <c r="T108" s="139"/>
-      <c r="U108" s="139"/>
-      <c r="V108" s="139"/>
+      <c r="B108" s="134"/>
+      <c r="C108" s="134"/>
+      <c r="D108" s="134"/>
+      <c r="E108" s="134"/>
+      <c r="F108" s="134"/>
+      <c r="G108" s="133"/>
+      <c r="H108" s="133"/>
+      <c r="I108" s="134"/>
+      <c r="J108" s="134"/>
+      <c r="K108" s="134"/>
+      <c r="L108" s="134"/>
+      <c r="M108" s="133"/>
+      <c r="N108" s="133"/>
+      <c r="O108" s="134"/>
+      <c r="P108" s="134"/>
+      <c r="Q108" s="134"/>
+      <c r="R108" s="134"/>
+      <c r="S108" s="134"/>
+      <c r="T108" s="134"/>
+      <c r="U108" s="134"/>
+      <c r="V108" s="134"/>
     </row>
     <row r="109" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="139"/>
-      <c r="C109" s="139"/>
-      <c r="D109" s="139"/>
-      <c r="E109" s="139"/>
-      <c r="F109" s="139"/>
-      <c r="G109" s="138"/>
-      <c r="H109" s="138"/>
-      <c r="I109" s="139"/>
-      <c r="J109" s="139"/>
-      <c r="K109" s="138"/>
-      <c r="L109" s="138"/>
-      <c r="M109" s="139"/>
-      <c r="N109" s="139"/>
-      <c r="O109" s="139"/>
-      <c r="P109" s="139"/>
-      <c r="Q109" s="139"/>
-      <c r="R109" s="139"/>
-      <c r="S109" s="139"/>
-      <c r="T109" s="139"/>
-      <c r="U109" s="139"/>
-      <c r="V109" s="139"/>
+      <c r="B109" s="134"/>
+      <c r="C109" s="134"/>
+      <c r="D109" s="134"/>
+      <c r="E109" s="134"/>
+      <c r="F109" s="134"/>
+      <c r="G109" s="133"/>
+      <c r="H109" s="133"/>
+      <c r="I109" s="134"/>
+      <c r="J109" s="134"/>
+      <c r="K109" s="133"/>
+      <c r="L109" s="133"/>
+      <c r="M109" s="134"/>
+      <c r="N109" s="134"/>
+      <c r="O109" s="134"/>
+      <c r="P109" s="134"/>
+      <c r="Q109" s="134"/>
+      <c r="R109" s="134"/>
+      <c r="S109" s="134"/>
+      <c r="T109" s="134"/>
+      <c r="U109" s="134"/>
+      <c r="V109" s="134"/>
     </row>
     <row r="110" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B110" s="139"/>
-      <c r="C110" s="139"/>
-      <c r="D110" s="139"/>
-      <c r="E110" s="139"/>
-      <c r="F110" s="139"/>
-      <c r="G110" s="139"/>
-      <c r="H110" s="139"/>
-      <c r="I110" s="139"/>
-      <c r="J110" s="139"/>
-      <c r="K110" s="138"/>
-      <c r="L110" s="138"/>
-      <c r="M110" s="139"/>
-      <c r="N110" s="139"/>
-      <c r="O110" s="139"/>
-      <c r="P110" s="139"/>
-      <c r="Q110" s="138"/>
-      <c r="R110" s="138"/>
-      <c r="S110" s="138"/>
-      <c r="T110" s="138"/>
-      <c r="U110" s="139"/>
-      <c r="V110" s="139"/>
+      <c r="B110" s="134"/>
+      <c r="C110" s="134"/>
+      <c r="D110" s="134"/>
+      <c r="E110" s="134"/>
+      <c r="F110" s="134"/>
+      <c r="G110" s="134"/>
+      <c r="H110" s="134"/>
+      <c r="I110" s="134"/>
+      <c r="J110" s="134"/>
+      <c r="K110" s="133"/>
+      <c r="L110" s="133"/>
+      <c r="M110" s="134"/>
+      <c r="N110" s="134"/>
+      <c r="O110" s="134"/>
+      <c r="P110" s="134"/>
+      <c r="Q110" s="133"/>
+      <c r="R110" s="133"/>
+      <c r="S110" s="133"/>
+      <c r="T110" s="133"/>
+      <c r="U110" s="134"/>
+      <c r="V110" s="134"/>
     </row>
     <row r="111" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="139"/>
-      <c r="C111" s="139"/>
-      <c r="D111" s="139"/>
-      <c r="E111" s="139"/>
-      <c r="F111" s="139"/>
-      <c r="G111" s="139"/>
-      <c r="H111" s="139"/>
-      <c r="I111" s="138"/>
-      <c r="J111" s="138"/>
-      <c r="K111" s="139"/>
-      <c r="L111" s="139"/>
-      <c r="M111" s="139"/>
-      <c r="N111" s="139"/>
-      <c r="O111" s="139"/>
-      <c r="P111" s="139"/>
-      <c r="Q111" s="138"/>
-      <c r="R111" s="138"/>
-      <c r="S111" s="138"/>
-      <c r="T111" s="138"/>
-      <c r="U111" s="139"/>
-      <c r="V111" s="139"/>
+      <c r="B111" s="134"/>
+      <c r="C111" s="134"/>
+      <c r="D111" s="134"/>
+      <c r="E111" s="134"/>
+      <c r="F111" s="134"/>
+      <c r="G111" s="134"/>
+      <c r="H111" s="134"/>
+      <c r="I111" s="133"/>
+      <c r="J111" s="133"/>
+      <c r="K111" s="134"/>
+      <c r="L111" s="134"/>
+      <c r="M111" s="134"/>
+      <c r="N111" s="134"/>
+      <c r="O111" s="134"/>
+      <c r="P111" s="134"/>
+      <c r="Q111" s="133"/>
+      <c r="R111" s="133"/>
+      <c r="S111" s="133"/>
+      <c r="T111" s="133"/>
+      <c r="U111" s="134"/>
+      <c r="V111" s="134"/>
     </row>
     <row r="112" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B112" s="138"/>
-      <c r="C112" s="138"/>
-      <c r="D112" s="139"/>
-      <c r="E112" s="139"/>
-      <c r="F112" s="139"/>
-      <c r="G112" s="138"/>
-      <c r="H112" s="139"/>
-      <c r="I112" s="138"/>
-      <c r="J112" s="139"/>
-      <c r="K112" s="138"/>
-      <c r="L112" s="139"/>
-      <c r="M112" s="138"/>
-      <c r="N112" s="139"/>
-      <c r="O112" s="138"/>
-      <c r="P112" s="139"/>
-      <c r="Q112" s="138"/>
-      <c r="R112" s="138"/>
-      <c r="S112" s="138"/>
-      <c r="T112" s="138"/>
-      <c r="U112" s="138"/>
-      <c r="V112" s="138"/>
+      <c r="B112" s="133"/>
+      <c r="C112" s="133"/>
+      <c r="D112" s="134"/>
+      <c r="E112" s="134"/>
+      <c r="F112" s="134"/>
+      <c r="G112" s="133"/>
+      <c r="H112" s="134"/>
+      <c r="I112" s="133"/>
+      <c r="J112" s="134"/>
+      <c r="K112" s="133"/>
+      <c r="L112" s="134"/>
+      <c r="M112" s="133"/>
+      <c r="N112" s="134"/>
+      <c r="O112" s="133"/>
+      <c r="P112" s="134"/>
+      <c r="Q112" s="133"/>
+      <c r="R112" s="133"/>
+      <c r="S112" s="133"/>
+      <c r="T112" s="133"/>
+      <c r="U112" s="133"/>
+      <c r="V112" s="133"/>
     </row>
     <row r="113" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B113" s="138"/>
-      <c r="C113" s="139"/>
-      <c r="D113" s="139"/>
-      <c r="E113" s="139"/>
-      <c r="F113" s="139"/>
-      <c r="G113" s="139"/>
-      <c r="H113" s="139"/>
-      <c r="I113" s="139"/>
-      <c r="J113" s="139"/>
-      <c r="K113" s="139"/>
-      <c r="L113" s="139"/>
-      <c r="M113" s="139"/>
-      <c r="N113" s="139"/>
-      <c r="O113" s="139"/>
-      <c r="P113" s="139"/>
-      <c r="Q113" s="138"/>
-      <c r="R113" s="138"/>
-      <c r="S113" s="138"/>
-      <c r="T113" s="138"/>
-      <c r="U113" s="138"/>
-      <c r="V113" s="139"/>
+      <c r="B113" s="133"/>
+      <c r="C113" s="134"/>
+      <c r="D113" s="134"/>
+      <c r="E113" s="134"/>
+      <c r="F113" s="134"/>
+      <c r="G113" s="134"/>
+      <c r="H113" s="134"/>
+      <c r="I113" s="134"/>
+      <c r="J113" s="134"/>
+      <c r="K113" s="134"/>
+      <c r="L113" s="134"/>
+      <c r="M113" s="134"/>
+      <c r="N113" s="134"/>
+      <c r="O113" s="134"/>
+      <c r="P113" s="134"/>
+      <c r="Q113" s="133"/>
+      <c r="R113" s="133"/>
+      <c r="S113" s="133"/>
+      <c r="T113" s="133"/>
+      <c r="U113" s="133"/>
+      <c r="V113" s="134"/>
     </row>
     <row r="114" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="138"/>
-      <c r="C114" s="138"/>
-      <c r="D114" s="138"/>
-      <c r="E114" s="138"/>
-      <c r="F114" s="138"/>
-      <c r="G114" s="138"/>
-      <c r="H114" s="138"/>
-      <c r="I114" s="138"/>
-      <c r="J114" s="138"/>
-      <c r="K114" s="138"/>
-      <c r="L114" s="138"/>
-      <c r="M114" s="138"/>
-      <c r="N114" s="138"/>
-      <c r="O114" s="138"/>
-      <c r="P114" s="138"/>
-      <c r="Q114" s="139"/>
-      <c r="R114" s="139"/>
-      <c r="S114" s="139"/>
-      <c r="T114" s="139"/>
-      <c r="U114" s="138"/>
-      <c r="V114" s="139"/>
+      <c r="B114" s="133"/>
+      <c r="C114" s="133"/>
+      <c r="D114" s="133"/>
+      <c r="E114" s="133"/>
+      <c r="F114" s="133"/>
+      <c r="G114" s="133"/>
+      <c r="H114" s="133"/>
+      <c r="I114" s="133"/>
+      <c r="J114" s="133"/>
+      <c r="K114" s="133"/>
+      <c r="L114" s="133"/>
+      <c r="M114" s="133"/>
+      <c r="N114" s="133"/>
+      <c r="O114" s="133"/>
+      <c r="P114" s="133"/>
+      <c r="Q114" s="134"/>
+      <c r="R114" s="134"/>
+      <c r="S114" s="134"/>
+      <c r="T114" s="134"/>
+      <c r="U114" s="133"/>
+      <c r="V114" s="134"/>
     </row>
     <row r="115" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B115" s="138"/>
-      <c r="C115" s="139"/>
-      <c r="D115" s="139"/>
-      <c r="E115" s="139"/>
-      <c r="F115" s="139"/>
-      <c r="G115" s="139"/>
-      <c r="H115" s="139"/>
-      <c r="I115" s="139"/>
-      <c r="J115" s="139"/>
-      <c r="K115" s="139"/>
-      <c r="L115" s="139"/>
-      <c r="M115" s="138"/>
-      <c r="N115" s="138"/>
-      <c r="O115" s="139"/>
-      <c r="P115" s="139"/>
-      <c r="Q115" s="138"/>
-      <c r="R115" s="138"/>
-      <c r="S115" s="138"/>
-      <c r="T115" s="138"/>
-      <c r="U115" s="139"/>
-      <c r="V115" s="139"/>
+      <c r="B115" s="133"/>
+      <c r="C115" s="134"/>
+      <c r="D115" s="134"/>
+      <c r="E115" s="134"/>
+      <c r="F115" s="134"/>
+      <c r="G115" s="134"/>
+      <c r="H115" s="134"/>
+      <c r="I115" s="134"/>
+      <c r="J115" s="134"/>
+      <c r="K115" s="134"/>
+      <c r="L115" s="134"/>
+      <c r="M115" s="133"/>
+      <c r="N115" s="133"/>
+      <c r="O115" s="134"/>
+      <c r="P115" s="134"/>
+      <c r="Q115" s="133"/>
+      <c r="R115" s="133"/>
+      <c r="S115" s="133"/>
+      <c r="T115" s="133"/>
+      <c r="U115" s="134"/>
+      <c r="V115" s="134"/>
     </row>
     <row r="116" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B116" s="139"/>
-      <c r="C116" s="139"/>
-      <c r="D116" s="139"/>
-      <c r="E116" s="139"/>
-      <c r="F116" s="139"/>
-      <c r="G116" s="139"/>
-      <c r="H116" s="139"/>
-      <c r="I116" s="138"/>
-      <c r="J116" s="138"/>
-      <c r="K116" s="139"/>
-      <c r="L116" s="139"/>
-      <c r="M116" s="139"/>
-      <c r="N116" s="139"/>
-      <c r="O116" s="139"/>
-      <c r="P116" s="139"/>
-      <c r="Q116" s="138"/>
-      <c r="R116" s="138"/>
-      <c r="S116" s="138"/>
-      <c r="T116" s="138"/>
-      <c r="U116" s="139"/>
-      <c r="V116" s="139"/>
+      <c r="B116" s="134"/>
+      <c r="C116" s="134"/>
+      <c r="D116" s="134"/>
+      <c r="E116" s="134"/>
+      <c r="F116" s="134"/>
+      <c r="G116" s="134"/>
+      <c r="H116" s="134"/>
+      <c r="I116" s="133"/>
+      <c r="J116" s="133"/>
+      <c r="K116" s="134"/>
+      <c r="L116" s="134"/>
+      <c r="M116" s="134"/>
+      <c r="N116" s="134"/>
+      <c r="O116" s="134"/>
+      <c r="P116" s="134"/>
+      <c r="Q116" s="133"/>
+      <c r="R116" s="133"/>
+      <c r="S116" s="133"/>
+      <c r="T116" s="133"/>
+      <c r="U116" s="134"/>
+      <c r="V116" s="134"/>
     </row>
     <row r="117" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B117" s="139"/>
-      <c r="C117" s="139"/>
-      <c r="D117" s="139"/>
-      <c r="E117" s="139"/>
-      <c r="F117" s="139"/>
-      <c r="G117" s="139"/>
-      <c r="H117" s="139"/>
-      <c r="I117" s="138"/>
-      <c r="J117" s="138"/>
-      <c r="K117" s="139"/>
-      <c r="L117" s="139"/>
-      <c r="M117" s="139"/>
-      <c r="N117" s="139"/>
-      <c r="O117" s="139"/>
-      <c r="P117" s="139"/>
-      <c r="Q117" s="138"/>
-      <c r="R117" s="138"/>
-      <c r="S117" s="138"/>
-      <c r="T117" s="138"/>
-      <c r="U117" s="139"/>
-      <c r="V117" s="139"/>
+      <c r="B117" s="134"/>
+      <c r="C117" s="134"/>
+      <c r="D117" s="134"/>
+      <c r="E117" s="134"/>
+      <c r="F117" s="134"/>
+      <c r="G117" s="134"/>
+      <c r="H117" s="134"/>
+      <c r="I117" s="133"/>
+      <c r="J117" s="133"/>
+      <c r="K117" s="134"/>
+      <c r="L117" s="134"/>
+      <c r="M117" s="134"/>
+      <c r="N117" s="134"/>
+      <c r="O117" s="134"/>
+      <c r="P117" s="134"/>
+      <c r="Q117" s="133"/>
+      <c r="R117" s="133"/>
+      <c r="S117" s="133"/>
+      <c r="T117" s="133"/>
+      <c r="U117" s="134"/>
+      <c r="V117" s="134"/>
     </row>
     <row r="118" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B118" s="139"/>
-      <c r="C118" s="139"/>
-      <c r="D118" s="139"/>
-      <c r="E118" s="139"/>
-      <c r="F118" s="139"/>
-      <c r="G118" s="138"/>
-      <c r="H118" s="138"/>
-      <c r="I118" s="139"/>
-      <c r="J118" s="139"/>
-      <c r="K118" s="138"/>
-      <c r="L118" s="138"/>
-      <c r="M118" s="139"/>
-      <c r="N118" s="139"/>
-      <c r="O118" s="139"/>
-      <c r="P118" s="139"/>
-      <c r="Q118" s="139"/>
-      <c r="R118" s="139"/>
-      <c r="S118" s="139"/>
-      <c r="T118" s="139"/>
-      <c r="U118" s="139"/>
-      <c r="V118" s="139"/>
+      <c r="B118" s="134"/>
+      <c r="C118" s="134"/>
+      <c r="D118" s="134"/>
+      <c r="E118" s="134"/>
+      <c r="F118" s="134"/>
+      <c r="G118" s="133"/>
+      <c r="H118" s="133"/>
+      <c r="I118" s="134"/>
+      <c r="J118" s="134"/>
+      <c r="K118" s="133"/>
+      <c r="L118" s="133"/>
+      <c r="M118" s="134"/>
+      <c r="N118" s="134"/>
+      <c r="O118" s="134"/>
+      <c r="P118" s="134"/>
+      <c r="Q118" s="134"/>
+      <c r="R118" s="134"/>
+      <c r="S118" s="134"/>
+      <c r="T118" s="134"/>
+      <c r="U118" s="134"/>
+      <c r="V118" s="134"/>
     </row>
     <row r="119" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B119" s="139"/>
-      <c r="C119" s="139"/>
-      <c r="D119" s="139"/>
-      <c r="E119" s="139"/>
-      <c r="F119" s="139"/>
-      <c r="G119" s="139"/>
-      <c r="H119" s="139"/>
-      <c r="I119" s="139"/>
-      <c r="J119" s="139"/>
-      <c r="K119" s="138"/>
-      <c r="L119" s="138"/>
-      <c r="M119" s="139"/>
-      <c r="N119" s="139"/>
-      <c r="O119" s="139"/>
-      <c r="P119" s="139"/>
-      <c r="Q119" s="138"/>
-      <c r="R119" s="138"/>
-      <c r="S119" s="138"/>
-      <c r="T119" s="138"/>
-      <c r="U119" s="139"/>
-      <c r="V119" s="139"/>
+      <c r="B119" s="134"/>
+      <c r="C119" s="134"/>
+      <c r="D119" s="134"/>
+      <c r="E119" s="134"/>
+      <c r="F119" s="134"/>
+      <c r="G119" s="134"/>
+      <c r="H119" s="134"/>
+      <c r="I119" s="134"/>
+      <c r="J119" s="134"/>
+      <c r="K119" s="133"/>
+      <c r="L119" s="133"/>
+      <c r="M119" s="134"/>
+      <c r="N119" s="134"/>
+      <c r="O119" s="134"/>
+      <c r="P119" s="134"/>
+      <c r="Q119" s="133"/>
+      <c r="R119" s="133"/>
+      <c r="S119" s="133"/>
+      <c r="T119" s="133"/>
+      <c r="U119" s="134"/>
+      <c r="V119" s="134"/>
     </row>
     <row r="120" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B120" s="139"/>
-      <c r="C120" s="139"/>
-      <c r="D120" s="139"/>
-      <c r="E120" s="139"/>
-      <c r="F120" s="139"/>
-      <c r="G120" s="138"/>
-      <c r="H120" s="138"/>
-      <c r="I120" s="139"/>
-      <c r="J120" s="139"/>
-      <c r="K120" s="138"/>
-      <c r="L120" s="138"/>
-      <c r="M120" s="139"/>
-      <c r="N120" s="139"/>
-      <c r="O120" s="139"/>
-      <c r="P120" s="139"/>
-      <c r="Q120" s="139"/>
-      <c r="R120" s="139"/>
-      <c r="S120" s="139"/>
-      <c r="T120" s="139"/>
-      <c r="U120" s="139"/>
-      <c r="V120" s="139"/>
+      <c r="B120" s="134"/>
+      <c r="C120" s="134"/>
+      <c r="D120" s="134"/>
+      <c r="E120" s="134"/>
+      <c r="F120" s="134"/>
+      <c r="G120" s="133"/>
+      <c r="H120" s="133"/>
+      <c r="I120" s="134"/>
+      <c r="J120" s="134"/>
+      <c r="K120" s="133"/>
+      <c r="L120" s="133"/>
+      <c r="M120" s="134"/>
+      <c r="N120" s="134"/>
+      <c r="O120" s="134"/>
+      <c r="P120" s="134"/>
+      <c r="Q120" s="134"/>
+      <c r="R120" s="134"/>
+      <c r="S120" s="134"/>
+      <c r="T120" s="134"/>
+      <c r="U120" s="134"/>
+      <c r="V120" s="134"/>
     </row>
     <row r="121" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B121" s="139"/>
-      <c r="C121" s="139"/>
-      <c r="D121" s="139"/>
-      <c r="E121" s="139"/>
-      <c r="F121" s="139"/>
-      <c r="G121" s="139"/>
-      <c r="H121" s="139"/>
-      <c r="I121" s="139"/>
-      <c r="J121" s="139"/>
-      <c r="K121" s="138"/>
-      <c r="L121" s="138"/>
-      <c r="M121" s="139"/>
-      <c r="N121" s="139"/>
-      <c r="O121" s="139"/>
-      <c r="P121" s="139"/>
-      <c r="Q121" s="138"/>
-      <c r="R121" s="138"/>
-      <c r="S121" s="138"/>
-      <c r="T121" s="138"/>
-      <c r="U121" s="139"/>
-      <c r="V121" s="139"/>
+      <c r="B121" s="134"/>
+      <c r="C121" s="134"/>
+      <c r="D121" s="134"/>
+      <c r="E121" s="134"/>
+      <c r="F121" s="134"/>
+      <c r="G121" s="134"/>
+      <c r="H121" s="134"/>
+      <c r="I121" s="134"/>
+      <c r="J121" s="134"/>
+      <c r="K121" s="133"/>
+      <c r="L121" s="133"/>
+      <c r="M121" s="134"/>
+      <c r="N121" s="134"/>
+      <c r="O121" s="134"/>
+      <c r="P121" s="134"/>
+      <c r="Q121" s="133"/>
+      <c r="R121" s="133"/>
+      <c r="S121" s="133"/>
+      <c r="T121" s="133"/>
+      <c r="U121" s="134"/>
+      <c r="V121" s="134"/>
     </row>
     <row r="122" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B122" s="139"/>
-      <c r="C122" s="139"/>
-      <c r="D122" s="139"/>
-      <c r="E122" s="139"/>
-      <c r="F122" s="139"/>
-      <c r="G122" s="139"/>
-      <c r="H122" s="139"/>
-      <c r="I122" s="138"/>
-      <c r="J122" s="138"/>
-      <c r="K122" s="139"/>
-      <c r="L122" s="139"/>
-      <c r="M122" s="139"/>
-      <c r="N122" s="139"/>
-      <c r="O122" s="139"/>
-      <c r="P122" s="139"/>
-      <c r="Q122" s="138"/>
-      <c r="R122" s="138"/>
-      <c r="S122" s="138"/>
-      <c r="T122" s="138"/>
-      <c r="U122" s="139"/>
-      <c r="V122" s="139"/>
+      <c r="B122" s="134"/>
+      <c r="C122" s="134"/>
+      <c r="D122" s="134"/>
+      <c r="E122" s="134"/>
+      <c r="F122" s="134"/>
+      <c r="G122" s="134"/>
+      <c r="H122" s="134"/>
+      <c r="I122" s="133"/>
+      <c r="J122" s="133"/>
+      <c r="K122" s="134"/>
+      <c r="L122" s="134"/>
+      <c r="M122" s="134"/>
+      <c r="N122" s="134"/>
+      <c r="O122" s="134"/>
+      <c r="P122" s="134"/>
+      <c r="Q122" s="133"/>
+      <c r="R122" s="133"/>
+      <c r="S122" s="133"/>
+      <c r="T122" s="133"/>
+      <c r="U122" s="134"/>
+      <c r="V122" s="134"/>
     </row>
     <row r="123" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B123" s="139"/>
-      <c r="C123" s="139"/>
-      <c r="D123" s="139"/>
-      <c r="E123" s="139"/>
-      <c r="F123" s="139"/>
-      <c r="G123" s="139"/>
-      <c r="H123" s="139"/>
-      <c r="I123" s="138"/>
-      <c r="J123" s="138"/>
-      <c r="K123" s="139"/>
-      <c r="L123" s="139"/>
-      <c r="M123" s="139"/>
-      <c r="N123" s="139"/>
-      <c r="O123" s="139"/>
-      <c r="P123" s="139"/>
-      <c r="Q123" s="138"/>
-      <c r="R123" s="138"/>
-      <c r="S123" s="138"/>
-      <c r="T123" s="138"/>
-      <c r="U123" s="139"/>
-      <c r="V123" s="139"/>
+      <c r="B123" s="134"/>
+      <c r="C123" s="134"/>
+      <c r="D123" s="134"/>
+      <c r="E123" s="134"/>
+      <c r="F123" s="134"/>
+      <c r="G123" s="134"/>
+      <c r="H123" s="134"/>
+      <c r="I123" s="133"/>
+      <c r="J123" s="133"/>
+      <c r="K123" s="134"/>
+      <c r="L123" s="134"/>
+      <c r="M123" s="134"/>
+      <c r="N123" s="134"/>
+      <c r="O123" s="134"/>
+      <c r="P123" s="134"/>
+      <c r="Q123" s="133"/>
+      <c r="R123" s="133"/>
+      <c r="S123" s="133"/>
+      <c r="T123" s="133"/>
+      <c r="U123" s="134"/>
+      <c r="V123" s="134"/>
     </row>
     <row r="124" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B124" s="139"/>
-      <c r="C124" s="139"/>
-      <c r="D124" s="139"/>
-      <c r="E124" s="139"/>
-      <c r="F124" s="139"/>
-      <c r="G124" s="138"/>
-      <c r="H124" s="138"/>
-      <c r="I124" s="139"/>
-      <c r="J124" s="139"/>
-      <c r="K124" s="139"/>
-      <c r="L124" s="139"/>
-      <c r="M124" s="139"/>
-      <c r="N124" s="139"/>
-      <c r="O124" s="139"/>
-      <c r="P124" s="139"/>
-      <c r="Q124" s="138"/>
-      <c r="R124" s="138"/>
-      <c r="S124" s="138"/>
-      <c r="T124" s="138"/>
-      <c r="U124" s="139"/>
-      <c r="V124" s="139"/>
+      <c r="B124" s="134"/>
+      <c r="C124" s="134"/>
+      <c r="D124" s="134"/>
+      <c r="E124" s="134"/>
+      <c r="F124" s="134"/>
+      <c r="G124" s="133"/>
+      <c r="H124" s="133"/>
+      <c r="I124" s="134"/>
+      <c r="J124" s="134"/>
+      <c r="K124" s="134"/>
+      <c r="L124" s="134"/>
+      <c r="M124" s="134"/>
+      <c r="N124" s="134"/>
+      <c r="O124" s="134"/>
+      <c r="P124" s="134"/>
+      <c r="Q124" s="133"/>
+      <c r="R124" s="133"/>
+      <c r="S124" s="133"/>
+      <c r="T124" s="133"/>
+      <c r="U124" s="134"/>
+      <c r="V124" s="134"/>
     </row>
     <row r="125" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B125" s="139"/>
-      <c r="C125" s="139"/>
-      <c r="D125" s="139"/>
-      <c r="E125" s="139"/>
-      <c r="F125" s="139"/>
-      <c r="G125" s="138"/>
-      <c r="H125" s="138"/>
-      <c r="I125" s="139"/>
-      <c r="J125" s="139"/>
-      <c r="K125" s="138"/>
-      <c r="L125" s="138"/>
-      <c r="M125" s="139"/>
-      <c r="N125" s="139"/>
-      <c r="O125" s="139"/>
-      <c r="P125" s="139"/>
-      <c r="Q125" s="139"/>
-      <c r="R125" s="139"/>
-      <c r="S125" s="139"/>
-      <c r="T125" s="139"/>
-      <c r="U125" s="139"/>
-      <c r="V125" s="139"/>
+      <c r="B125" s="134"/>
+      <c r="C125" s="134"/>
+      <c r="D125" s="134"/>
+      <c r="E125" s="134"/>
+      <c r="F125" s="134"/>
+      <c r="G125" s="133"/>
+      <c r="H125" s="133"/>
+      <c r="I125" s="134"/>
+      <c r="J125" s="134"/>
+      <c r="K125" s="133"/>
+      <c r="L125" s="133"/>
+      <c r="M125" s="134"/>
+      <c r="N125" s="134"/>
+      <c r="O125" s="134"/>
+      <c r="P125" s="134"/>
+      <c r="Q125" s="134"/>
+      <c r="R125" s="134"/>
+      <c r="S125" s="134"/>
+      <c r="T125" s="134"/>
+      <c r="U125" s="134"/>
+      <c r="V125" s="134"/>
     </row>
     <row r="126" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B126" s="139"/>
-      <c r="C126" s="139"/>
-      <c r="D126" s="139"/>
-      <c r="E126" s="139"/>
-      <c r="F126" s="139"/>
-      <c r="G126" s="139"/>
-      <c r="H126" s="139"/>
-      <c r="I126" s="139"/>
-      <c r="J126" s="139"/>
-      <c r="K126" s="138"/>
-      <c r="L126" s="138"/>
-      <c r="M126" s="139"/>
-      <c r="N126" s="139"/>
-      <c r="O126" s="139"/>
-      <c r="P126" s="139"/>
-      <c r="Q126" s="138"/>
-      <c r="R126" s="138"/>
-      <c r="S126" s="138"/>
-      <c r="T126" s="138"/>
-      <c r="U126" s="139"/>
-      <c r="V126" s="139"/>
+      <c r="B126" s="134"/>
+      <c r="C126" s="134"/>
+      <c r="D126" s="134"/>
+      <c r="E126" s="134"/>
+      <c r="F126" s="134"/>
+      <c r="G126" s="134"/>
+      <c r="H126" s="134"/>
+      <c r="I126" s="134"/>
+      <c r="J126" s="134"/>
+      <c r="K126" s="133"/>
+      <c r="L126" s="133"/>
+      <c r="M126" s="134"/>
+      <c r="N126" s="134"/>
+      <c r="O126" s="134"/>
+      <c r="P126" s="134"/>
+      <c r="Q126" s="133"/>
+      <c r="R126" s="133"/>
+      <c r="S126" s="133"/>
+      <c r="T126" s="133"/>
+      <c r="U126" s="134"/>
+      <c r="V126" s="134"/>
     </row>
     <row r="127" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B127" s="138"/>
-      <c r="C127" s="138"/>
-      <c r="D127" s="139"/>
-      <c r="E127" s="139"/>
-      <c r="F127" s="139"/>
-      <c r="G127" s="138"/>
-      <c r="H127" s="139"/>
-      <c r="I127" s="138"/>
-      <c r="J127" s="139"/>
-      <c r="K127" s="138"/>
-      <c r="L127" s="139"/>
-      <c r="M127" s="138"/>
-      <c r="N127" s="139"/>
-      <c r="O127" s="138"/>
-      <c r="P127" s="139"/>
-      <c r="Q127" s="138"/>
-      <c r="R127" s="138"/>
-      <c r="S127" s="138"/>
-      <c r="T127" s="138"/>
-      <c r="U127" s="138"/>
-      <c r="V127" s="138"/>
+      <c r="B127" s="133"/>
+      <c r="C127" s="133"/>
+      <c r="D127" s="134"/>
+      <c r="E127" s="134"/>
+      <c r="F127" s="134"/>
+      <c r="G127" s="133"/>
+      <c r="H127" s="134"/>
+      <c r="I127" s="133"/>
+      <c r="J127" s="134"/>
+      <c r="K127" s="133"/>
+      <c r="L127" s="134"/>
+      <c r="M127" s="133"/>
+      <c r="N127" s="134"/>
+      <c r="O127" s="133"/>
+      <c r="P127" s="134"/>
+      <c r="Q127" s="133"/>
+      <c r="R127" s="133"/>
+      <c r="S127" s="133"/>
+      <c r="T127" s="133"/>
+      <c r="U127" s="133"/>
+      <c r="V127" s="133"/>
     </row>
     <row r="128" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B128" s="138"/>
-      <c r="C128" s="139"/>
-      <c r="D128" s="139"/>
-      <c r="E128" s="139"/>
-      <c r="F128" s="139"/>
-      <c r="G128" s="139"/>
-      <c r="H128" s="139"/>
-      <c r="I128" s="139"/>
-      <c r="J128" s="139"/>
-      <c r="K128" s="139"/>
-      <c r="L128" s="139"/>
-      <c r="M128" s="139"/>
-      <c r="N128" s="139"/>
-      <c r="O128" s="139"/>
-      <c r="P128" s="139"/>
-      <c r="Q128" s="138"/>
-      <c r="R128" s="138"/>
-      <c r="S128" s="138"/>
-      <c r="T128" s="138"/>
-      <c r="U128" s="138"/>
-      <c r="V128" s="139"/>
+      <c r="B128" s="133"/>
+      <c r="C128" s="134"/>
+      <c r="D128" s="134"/>
+      <c r="E128" s="134"/>
+      <c r="F128" s="134"/>
+      <c r="G128" s="134"/>
+      <c r="H128" s="134"/>
+      <c r="I128" s="134"/>
+      <c r="J128" s="134"/>
+      <c r="K128" s="134"/>
+      <c r="L128" s="134"/>
+      <c r="M128" s="134"/>
+      <c r="N128" s="134"/>
+      <c r="O128" s="134"/>
+      <c r="P128" s="134"/>
+      <c r="Q128" s="133"/>
+      <c r="R128" s="133"/>
+      <c r="S128" s="133"/>
+      <c r="T128" s="133"/>
+      <c r="U128" s="133"/>
+      <c r="V128" s="134"/>
     </row>
     <row r="129" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B129" s="138"/>
-      <c r="C129" s="139"/>
-      <c r="D129" s="139"/>
-      <c r="E129" s="139"/>
-      <c r="F129" s="139"/>
-      <c r="G129" s="139"/>
-      <c r="H129" s="139"/>
-      <c r="I129" s="138"/>
-      <c r="J129" s="138"/>
-      <c r="K129" s="139"/>
-      <c r="L129" s="139"/>
-      <c r="M129" s="139"/>
-      <c r="N129" s="139"/>
-      <c r="O129" s="139"/>
-      <c r="P129" s="139"/>
-      <c r="Q129" s="138"/>
-      <c r="R129" s="138"/>
-      <c r="S129" s="138"/>
-      <c r="T129" s="138"/>
-      <c r="U129" s="139"/>
-      <c r="V129" s="139"/>
+      <c r="B129" s="133"/>
+      <c r="C129" s="134"/>
+      <c r="D129" s="134"/>
+      <c r="E129" s="134"/>
+      <c r="F129" s="134"/>
+      <c r="G129" s="134"/>
+      <c r="H129" s="134"/>
+      <c r="I129" s="133"/>
+      <c r="J129" s="133"/>
+      <c r="K129" s="134"/>
+      <c r="L129" s="134"/>
+      <c r="M129" s="134"/>
+      <c r="N129" s="134"/>
+      <c r="O129" s="134"/>
+      <c r="P129" s="134"/>
+      <c r="Q129" s="133"/>
+      <c r="R129" s="133"/>
+      <c r="S129" s="133"/>
+      <c r="T129" s="133"/>
+      <c r="U129" s="134"/>
+      <c r="V129" s="134"/>
     </row>
     <row r="130" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B130" s="139"/>
-      <c r="C130" s="139"/>
-      <c r="D130" s="139"/>
-      <c r="E130" s="139"/>
-      <c r="F130" s="139"/>
-      <c r="G130" s="138"/>
-      <c r="H130" s="138"/>
-      <c r="I130" s="139"/>
-      <c r="J130" s="139"/>
-      <c r="K130" s="138"/>
-      <c r="L130" s="138"/>
-      <c r="M130" s="139"/>
-      <c r="N130" s="139"/>
-      <c r="O130" s="139"/>
-      <c r="P130" s="139"/>
-      <c r="Q130" s="139"/>
-      <c r="R130" s="139"/>
-      <c r="S130" s="139"/>
-      <c r="T130" s="139"/>
-      <c r="U130" s="139"/>
-      <c r="V130" s="139"/>
+      <c r="B130" s="134"/>
+      <c r="C130" s="134"/>
+      <c r="D130" s="134"/>
+      <c r="E130" s="134"/>
+      <c r="F130" s="134"/>
+      <c r="G130" s="133"/>
+      <c r="H130" s="133"/>
+      <c r="I130" s="134"/>
+      <c r="J130" s="134"/>
+      <c r="K130" s="133"/>
+      <c r="L130" s="133"/>
+      <c r="M130" s="134"/>
+      <c r="N130" s="134"/>
+      <c r="O130" s="134"/>
+      <c r="P130" s="134"/>
+      <c r="Q130" s="134"/>
+      <c r="R130" s="134"/>
+      <c r="S130" s="134"/>
+      <c r="T130" s="134"/>
+      <c r="U130" s="134"/>
+      <c r="V130" s="134"/>
     </row>
     <row r="131" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B131" s="139"/>
-      <c r="C131" s="139"/>
-      <c r="D131" s="139"/>
-      <c r="E131" s="139"/>
-      <c r="F131" s="139"/>
-      <c r="G131" s="139"/>
-      <c r="H131" s="139"/>
-      <c r="I131" s="139"/>
-      <c r="J131" s="139"/>
-      <c r="K131" s="138"/>
-      <c r="L131" s="138"/>
-      <c r="M131" s="139"/>
-      <c r="N131" s="139"/>
-      <c r="O131" s="139"/>
-      <c r="P131" s="139"/>
-      <c r="Q131" s="138"/>
-      <c r="R131" s="138"/>
-      <c r="S131" s="138"/>
-      <c r="T131" s="138"/>
-      <c r="U131" s="139"/>
-      <c r="V131" s="139"/>
+      <c r="B131" s="134"/>
+      <c r="C131" s="134"/>
+      <c r="D131" s="134"/>
+      <c r="E131" s="134"/>
+      <c r="F131" s="134"/>
+      <c r="G131" s="134"/>
+      <c r="H131" s="134"/>
+      <c r="I131" s="134"/>
+      <c r="J131" s="134"/>
+      <c r="K131" s="133"/>
+      <c r="L131" s="133"/>
+      <c r="M131" s="134"/>
+      <c r="N131" s="134"/>
+      <c r="O131" s="134"/>
+      <c r="P131" s="134"/>
+      <c r="Q131" s="133"/>
+      <c r="R131" s="133"/>
+      <c r="S131" s="133"/>
+      <c r="T131" s="133"/>
+      <c r="U131" s="134"/>
+      <c r="V131" s="134"/>
     </row>
     <row r="132" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B132" s="139"/>
-      <c r="C132" s="139"/>
-      <c r="D132" s="139"/>
-      <c r="E132" s="139"/>
-      <c r="F132" s="139"/>
-      <c r="G132" s="139"/>
-      <c r="H132" s="139"/>
-      <c r="I132" s="138"/>
-      <c r="J132" s="138"/>
-      <c r="K132" s="139"/>
-      <c r="L132" s="139"/>
-      <c r="M132" s="139"/>
-      <c r="N132" s="139"/>
-      <c r="O132" s="139"/>
-      <c r="P132" s="139"/>
-      <c r="Q132" s="138"/>
-      <c r="R132" s="138"/>
-      <c r="S132" s="138"/>
-      <c r="T132" s="138"/>
-      <c r="U132" s="139"/>
-      <c r="V132" s="139"/>
+      <c r="B132" s="134"/>
+      <c r="C132" s="134"/>
+      <c r="D132" s="134"/>
+      <c r="E132" s="134"/>
+      <c r="F132" s="134"/>
+      <c r="G132" s="134"/>
+      <c r="H132" s="134"/>
+      <c r="I132" s="133"/>
+      <c r="J132" s="133"/>
+      <c r="K132" s="134"/>
+      <c r="L132" s="134"/>
+      <c r="M132" s="134"/>
+      <c r="N132" s="134"/>
+      <c r="O132" s="134"/>
+      <c r="P132" s="134"/>
+      <c r="Q132" s="133"/>
+      <c r="R132" s="133"/>
+      <c r="S132" s="133"/>
+      <c r="T132" s="133"/>
+      <c r="U132" s="134"/>
+      <c r="V132" s="134"/>
     </row>
     <row r="133" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B133" s="139"/>
-      <c r="C133" s="139"/>
-      <c r="D133" s="139"/>
-      <c r="E133" s="139"/>
-      <c r="F133" s="139"/>
-      <c r="G133" s="139"/>
-      <c r="H133" s="139"/>
-      <c r="I133" s="138"/>
-      <c r="J133" s="138"/>
-      <c r="K133" s="139"/>
-      <c r="L133" s="139"/>
-      <c r="M133" s="139"/>
-      <c r="N133" s="139"/>
-      <c r="O133" s="139"/>
-      <c r="P133" s="139"/>
-      <c r="Q133" s="138"/>
-      <c r="R133" s="138"/>
-      <c r="S133" s="138"/>
-      <c r="T133" s="138"/>
-      <c r="U133" s="139"/>
-      <c r="V133" s="139"/>
+      <c r="B133" s="134"/>
+      <c r="C133" s="134"/>
+      <c r="D133" s="134"/>
+      <c r="E133" s="134"/>
+      <c r="F133" s="134"/>
+      <c r="G133" s="134"/>
+      <c r="H133" s="134"/>
+      <c r="I133" s="133"/>
+      <c r="J133" s="133"/>
+      <c r="K133" s="134"/>
+      <c r="L133" s="134"/>
+      <c r="M133" s="134"/>
+      <c r="N133" s="134"/>
+      <c r="O133" s="134"/>
+      <c r="P133" s="134"/>
+      <c r="Q133" s="133"/>
+      <c r="R133" s="133"/>
+      <c r="S133" s="133"/>
+      <c r="T133" s="133"/>
+      <c r="U133" s="134"/>
+      <c r="V133" s="134"/>
     </row>
     <row r="134" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B134" s="139"/>
-      <c r="C134" s="139"/>
-      <c r="D134" s="139"/>
-      <c r="E134" s="139"/>
-      <c r="F134" s="139"/>
-      <c r="G134" s="139"/>
-      <c r="H134" s="139"/>
-      <c r="I134" s="138"/>
-      <c r="J134" s="138"/>
-      <c r="K134" s="139"/>
-      <c r="L134" s="139"/>
-      <c r="M134" s="139"/>
-      <c r="N134" s="139"/>
-      <c r="O134" s="139"/>
-      <c r="P134" s="139"/>
-      <c r="Q134" s="138"/>
-      <c r="R134" s="138"/>
-      <c r="S134" s="138"/>
-      <c r="T134" s="138"/>
-      <c r="U134" s="139"/>
-      <c r="V134" s="139"/>
+      <c r="B134" s="134"/>
+      <c r="C134" s="134"/>
+      <c r="D134" s="134"/>
+      <c r="E134" s="134"/>
+      <c r="F134" s="134"/>
+      <c r="G134" s="134"/>
+      <c r="H134" s="134"/>
+      <c r="I134" s="133"/>
+      <c r="J134" s="133"/>
+      <c r="K134" s="134"/>
+      <c r="L134" s="134"/>
+      <c r="M134" s="134"/>
+      <c r="N134" s="134"/>
+      <c r="O134" s="134"/>
+      <c r="P134" s="134"/>
+      <c r="Q134" s="133"/>
+      <c r="R134" s="133"/>
+      <c r="S134" s="133"/>
+      <c r="T134" s="133"/>
+      <c r="U134" s="134"/>
+      <c r="V134" s="134"/>
     </row>
     <row r="135" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B135" s="139"/>
-      <c r="C135" s="139"/>
-      <c r="D135" s="139"/>
-      <c r="E135" s="139"/>
-      <c r="F135" s="139"/>
-      <c r="G135" s="139"/>
-      <c r="H135" s="139"/>
-      <c r="I135" s="138"/>
-      <c r="J135" s="138"/>
-      <c r="K135" s="139"/>
-      <c r="L135" s="139"/>
-      <c r="M135" s="139"/>
-      <c r="N135" s="139"/>
-      <c r="O135" s="139"/>
-      <c r="P135" s="139"/>
-      <c r="Q135" s="138"/>
-      <c r="R135" s="138"/>
-      <c r="S135" s="138"/>
-      <c r="T135" s="138"/>
-      <c r="U135" s="139"/>
-      <c r="V135" s="139"/>
+      <c r="B135" s="134"/>
+      <c r="C135" s="134"/>
+      <c r="D135" s="134"/>
+      <c r="E135" s="134"/>
+      <c r="F135" s="134"/>
+      <c r="G135" s="134"/>
+      <c r="H135" s="134"/>
+      <c r="I135" s="133"/>
+      <c r="J135" s="133"/>
+      <c r="K135" s="134"/>
+      <c r="L135" s="134"/>
+      <c r="M135" s="134"/>
+      <c r="N135" s="134"/>
+      <c r="O135" s="134"/>
+      <c r="P135" s="134"/>
+      <c r="Q135" s="133"/>
+      <c r="R135" s="133"/>
+      <c r="S135" s="133"/>
+      <c r="T135" s="133"/>
+      <c r="U135" s="134"/>
+      <c r="V135" s="134"/>
     </row>
     <row r="136" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B136" s="139"/>
-      <c r="C136" s="139"/>
-      <c r="D136" s="139"/>
-      <c r="E136" s="139"/>
-      <c r="F136" s="139"/>
-      <c r="G136" s="139"/>
-      <c r="H136" s="139"/>
-      <c r="I136" s="138"/>
-      <c r="J136" s="138"/>
-      <c r="K136" s="139"/>
-      <c r="L136" s="139"/>
-      <c r="M136" s="139"/>
-      <c r="N136" s="139"/>
-      <c r="O136" s="139"/>
-      <c r="P136" s="139"/>
-      <c r="Q136" s="138"/>
-      <c r="R136" s="138"/>
-      <c r="S136" s="138"/>
-      <c r="T136" s="138"/>
-      <c r="U136" s="139"/>
-      <c r="V136" s="139"/>
+      <c r="B136" s="134"/>
+      <c r="C136" s="134"/>
+      <c r="D136" s="134"/>
+      <c r="E136" s="134"/>
+      <c r="F136" s="134"/>
+      <c r="G136" s="134"/>
+      <c r="H136" s="134"/>
+      <c r="I136" s="133"/>
+      <c r="J136" s="133"/>
+      <c r="K136" s="134"/>
+      <c r="L136" s="134"/>
+      <c r="M136" s="134"/>
+      <c r="N136" s="134"/>
+      <c r="O136" s="134"/>
+      <c r="P136" s="134"/>
+      <c r="Q136" s="133"/>
+      <c r="R136" s="133"/>
+      <c r="S136" s="133"/>
+      <c r="T136" s="133"/>
+      <c r="U136" s="134"/>
+      <c r="V136" s="134"/>
     </row>
     <row r="137" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B137" s="138"/>
-      <c r="C137" s="138"/>
-      <c r="D137" s="139"/>
-      <c r="E137" s="139"/>
-      <c r="F137" s="139"/>
-      <c r="G137" s="138"/>
-      <c r="H137" s="139"/>
-      <c r="I137" s="138"/>
-      <c r="J137" s="139"/>
-      <c r="K137" s="138"/>
-      <c r="L137" s="139"/>
-      <c r="M137" s="138"/>
-      <c r="N137" s="139"/>
-      <c r="O137" s="138"/>
-      <c r="P137" s="139"/>
-      <c r="Q137" s="138"/>
-      <c r="R137" s="138"/>
-      <c r="S137" s="138"/>
-      <c r="T137" s="138"/>
-      <c r="U137" s="138"/>
-      <c r="V137" s="138"/>
+      <c r="B137" s="133"/>
+      <c r="C137" s="133"/>
+      <c r="D137" s="134"/>
+      <c r="E137" s="134"/>
+      <c r="F137" s="134"/>
+      <c r="G137" s="133"/>
+      <c r="H137" s="134"/>
+      <c r="I137" s="133"/>
+      <c r="J137" s="134"/>
+      <c r="K137" s="133"/>
+      <c r="L137" s="134"/>
+      <c r="M137" s="133"/>
+      <c r="N137" s="134"/>
+      <c r="O137" s="133"/>
+      <c r="P137" s="134"/>
+      <c r="Q137" s="133"/>
+      <c r="R137" s="133"/>
+      <c r="S137" s="133"/>
+      <c r="T137" s="133"/>
+      <c r="U137" s="133"/>
+      <c r="V137" s="133"/>
     </row>
     <row r="138" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B138" s="138"/>
-      <c r="C138" s="139"/>
-      <c r="D138" s="139"/>
-      <c r="E138" s="139"/>
-      <c r="F138" s="139"/>
-      <c r="G138" s="139"/>
-      <c r="H138" s="139"/>
-      <c r="I138" s="139"/>
-      <c r="J138" s="139"/>
-      <c r="K138" s="139"/>
-      <c r="L138" s="139"/>
-      <c r="M138" s="139"/>
-      <c r="N138" s="139"/>
-      <c r="O138" s="139"/>
-      <c r="P138" s="139"/>
-      <c r="Q138" s="138"/>
-      <c r="R138" s="138"/>
-      <c r="S138" s="138"/>
-      <c r="T138" s="138"/>
-      <c r="U138" s="138"/>
-      <c r="V138" s="139"/>
+      <c r="B138" s="133"/>
+      <c r="C138" s="134"/>
+      <c r="D138" s="134"/>
+      <c r="E138" s="134"/>
+      <c r="F138" s="134"/>
+      <c r="G138" s="134"/>
+      <c r="H138" s="134"/>
+      <c r="I138" s="134"/>
+      <c r="J138" s="134"/>
+      <c r="K138" s="134"/>
+      <c r="L138" s="134"/>
+      <c r="M138" s="134"/>
+      <c r="N138" s="134"/>
+      <c r="O138" s="134"/>
+      <c r="P138" s="134"/>
+      <c r="Q138" s="133"/>
+      <c r="R138" s="133"/>
+      <c r="S138" s="133"/>
+      <c r="T138" s="133"/>
+      <c r="U138" s="133"/>
+      <c r="V138" s="134"/>
     </row>
     <row r="139" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B139" s="138"/>
-      <c r="C139" s="139"/>
-      <c r="D139" s="139"/>
-      <c r="E139" s="139"/>
-      <c r="F139" s="139"/>
-      <c r="G139" s="139"/>
-      <c r="H139" s="139"/>
-      <c r="I139" s="138"/>
-      <c r="J139" s="138"/>
-      <c r="K139" s="139"/>
-      <c r="L139" s="139"/>
-      <c r="M139" s="139"/>
-      <c r="N139" s="139"/>
-      <c r="O139" s="139"/>
-      <c r="P139" s="139"/>
-      <c r="Q139" s="138"/>
-      <c r="R139" s="138"/>
-      <c r="S139" s="138"/>
-      <c r="T139" s="138"/>
-      <c r="U139" s="139"/>
-      <c r="V139" s="139"/>
+      <c r="B139" s="133"/>
+      <c r="C139" s="134"/>
+      <c r="D139" s="134"/>
+      <c r="E139" s="134"/>
+      <c r="F139" s="134"/>
+      <c r="G139" s="134"/>
+      <c r="H139" s="134"/>
+      <c r="I139" s="133"/>
+      <c r="J139" s="133"/>
+      <c r="K139" s="134"/>
+      <c r="L139" s="134"/>
+      <c r="M139" s="134"/>
+      <c r="N139" s="134"/>
+      <c r="O139" s="134"/>
+      <c r="P139" s="134"/>
+      <c r="Q139" s="133"/>
+      <c r="R139" s="133"/>
+      <c r="S139" s="133"/>
+      <c r="T139" s="133"/>
+      <c r="U139" s="134"/>
+      <c r="V139" s="134"/>
     </row>
     <row r="140" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B140" s="139"/>
-      <c r="C140" s="139"/>
-      <c r="D140" s="139"/>
-      <c r="E140" s="139"/>
-      <c r="F140" s="139"/>
-      <c r="G140" s="138"/>
-      <c r="H140" s="138"/>
-      <c r="I140" s="139"/>
-      <c r="J140" s="139"/>
-      <c r="K140" s="138"/>
-      <c r="L140" s="138"/>
-      <c r="M140" s="139"/>
-      <c r="N140" s="139"/>
-      <c r="O140" s="139"/>
-      <c r="P140" s="139"/>
-      <c r="Q140" s="139"/>
-      <c r="R140" s="139"/>
-      <c r="S140" s="139"/>
-      <c r="T140" s="139"/>
-      <c r="U140" s="139"/>
-      <c r="V140" s="139"/>
+      <c r="B140" s="134"/>
+      <c r="C140" s="134"/>
+      <c r="D140" s="134"/>
+      <c r="E140" s="134"/>
+      <c r="F140" s="134"/>
+      <c r="G140" s="133"/>
+      <c r="H140" s="133"/>
+      <c r="I140" s="134"/>
+      <c r="J140" s="134"/>
+      <c r="K140" s="133"/>
+      <c r="L140" s="133"/>
+      <c r="M140" s="134"/>
+      <c r="N140" s="134"/>
+      <c r="O140" s="134"/>
+      <c r="P140" s="134"/>
+      <c r="Q140" s="134"/>
+      <c r="R140" s="134"/>
+      <c r="S140" s="134"/>
+      <c r="T140" s="134"/>
+      <c r="U140" s="134"/>
+      <c r="V140" s="134"/>
     </row>
     <row r="141" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B141" s="139"/>
-      <c r="C141" s="139"/>
-      <c r="D141" s="139"/>
-      <c r="E141" s="139"/>
-      <c r="F141" s="139"/>
-      <c r="G141" s="139"/>
-      <c r="H141" s="139"/>
-      <c r="I141" s="139"/>
-      <c r="J141" s="139"/>
-      <c r="K141" s="138"/>
-      <c r="L141" s="138"/>
-      <c r="M141" s="139"/>
-      <c r="N141" s="139"/>
-      <c r="O141" s="139"/>
-      <c r="P141" s="139"/>
-      <c r="Q141" s="138"/>
-      <c r="R141" s="138"/>
-      <c r="S141" s="138"/>
-      <c r="T141" s="138"/>
-      <c r="U141" s="139"/>
-      <c r="V141" s="139"/>
+      <c r="B141" s="134"/>
+      <c r="C141" s="134"/>
+      <c r="D141" s="134"/>
+      <c r="E141" s="134"/>
+      <c r="F141" s="134"/>
+      <c r="G141" s="134"/>
+      <c r="H141" s="134"/>
+      <c r="I141" s="134"/>
+      <c r="J141" s="134"/>
+      <c r="K141" s="133"/>
+      <c r="L141" s="133"/>
+      <c r="M141" s="134"/>
+      <c r="N141" s="134"/>
+      <c r="O141" s="134"/>
+      <c r="P141" s="134"/>
+      <c r="Q141" s="133"/>
+      <c r="R141" s="133"/>
+      <c r="S141" s="133"/>
+      <c r="T141" s="133"/>
+      <c r="U141" s="134"/>
+      <c r="V141" s="134"/>
     </row>
     <row r="142" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B142" s="139"/>
-      <c r="C142" s="139"/>
-      <c r="D142" s="139"/>
-      <c r="E142" s="139"/>
-      <c r="F142" s="139"/>
-      <c r="G142" s="138"/>
-      <c r="H142" s="138"/>
-      <c r="I142" s="139"/>
-      <c r="J142" s="139"/>
-      <c r="K142" s="139"/>
-      <c r="L142" s="139"/>
-      <c r="M142" s="139"/>
-      <c r="N142" s="139"/>
-      <c r="O142" s="139"/>
-      <c r="P142" s="139"/>
-      <c r="Q142" s="138"/>
-      <c r="R142" s="138"/>
-      <c r="S142" s="138"/>
-      <c r="T142" s="138"/>
-      <c r="U142" s="139"/>
-      <c r="V142" s="139"/>
+      <c r="B142" s="134"/>
+      <c r="C142" s="134"/>
+      <c r="D142" s="134"/>
+      <c r="E142" s="134"/>
+      <c r="F142" s="134"/>
+      <c r="G142" s="133"/>
+      <c r="H142" s="133"/>
+      <c r="I142" s="134"/>
+      <c r="J142" s="134"/>
+      <c r="K142" s="134"/>
+      <c r="L142" s="134"/>
+      <c r="M142" s="134"/>
+      <c r="N142" s="134"/>
+      <c r="O142" s="134"/>
+      <c r="P142" s="134"/>
+      <c r="Q142" s="133"/>
+      <c r="R142" s="133"/>
+      <c r="S142" s="133"/>
+      <c r="T142" s="133"/>
+      <c r="U142" s="134"/>
+      <c r="V142" s="134"/>
     </row>
     <row r="143" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B143" s="139"/>
-      <c r="C143" s="139"/>
-      <c r="D143" s="139"/>
-      <c r="E143" s="139"/>
-      <c r="F143" s="139"/>
-      <c r="G143" s="138"/>
-      <c r="H143" s="138"/>
-      <c r="I143" s="139"/>
-      <c r="J143" s="139"/>
-      <c r="K143" s="138"/>
-      <c r="L143" s="138"/>
-      <c r="M143" s="139"/>
-      <c r="N143" s="139"/>
-      <c r="O143" s="139"/>
-      <c r="P143" s="139"/>
-      <c r="Q143" s="139"/>
-      <c r="R143" s="139"/>
-      <c r="S143" s="139"/>
-      <c r="T143" s="139"/>
-      <c r="U143" s="139"/>
-      <c r="V143" s="139"/>
+      <c r="B143" s="134"/>
+      <c r="C143" s="134"/>
+      <c r="D143" s="134"/>
+      <c r="E143" s="134"/>
+      <c r="F143" s="134"/>
+      <c r="G143" s="133"/>
+      <c r="H143" s="133"/>
+      <c r="I143" s="134"/>
+      <c r="J143" s="134"/>
+      <c r="K143" s="133"/>
+      <c r="L143" s="133"/>
+      <c r="M143" s="134"/>
+      <c r="N143" s="134"/>
+      <c r="O143" s="134"/>
+      <c r="P143" s="134"/>
+      <c r="Q143" s="134"/>
+      <c r="R143" s="134"/>
+      <c r="S143" s="134"/>
+      <c r="T143" s="134"/>
+      <c r="U143" s="134"/>
+      <c r="V143" s="134"/>
     </row>
     <row r="144" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B144" s="139"/>
-      <c r="C144" s="139"/>
-      <c r="D144" s="139"/>
-      <c r="E144" s="139"/>
-      <c r="F144" s="139"/>
-      <c r="G144" s="139"/>
-      <c r="H144" s="139"/>
-      <c r="I144" s="139"/>
-      <c r="J144" s="139"/>
-      <c r="K144" s="138"/>
-      <c r="L144" s="138"/>
-      <c r="M144" s="139"/>
-      <c r="N144" s="139"/>
-      <c r="O144" s="139"/>
-      <c r="P144" s="139"/>
-      <c r="Q144" s="138"/>
-      <c r="R144" s="138"/>
-      <c r="S144" s="138"/>
-      <c r="T144" s="138"/>
-      <c r="U144" s="139"/>
-      <c r="V144" s="139"/>
+      <c r="B144" s="134"/>
+      <c r="C144" s="134"/>
+      <c r="D144" s="134"/>
+      <c r="E144" s="134"/>
+      <c r="F144" s="134"/>
+      <c r="G144" s="134"/>
+      <c r="H144" s="134"/>
+      <c r="I144" s="134"/>
+      <c r="J144" s="134"/>
+      <c r="K144" s="133"/>
+      <c r="L144" s="133"/>
+      <c r="M144" s="134"/>
+      <c r="N144" s="134"/>
+      <c r="O144" s="134"/>
+      <c r="P144" s="134"/>
+      <c r="Q144" s="133"/>
+      <c r="R144" s="133"/>
+      <c r="S144" s="133"/>
+      <c r="T144" s="133"/>
+      <c r="U144" s="134"/>
+      <c r="V144" s="134"/>
     </row>
     <row r="145" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B145" s="139"/>
-      <c r="C145" s="139"/>
-      <c r="D145" s="139"/>
-      <c r="E145" s="139"/>
-      <c r="F145" s="139"/>
-      <c r="G145" s="139"/>
-      <c r="H145" s="139"/>
-      <c r="I145" s="138"/>
-      <c r="J145" s="138"/>
-      <c r="K145" s="139"/>
-      <c r="L145" s="139"/>
-      <c r="M145" s="139"/>
-      <c r="N145" s="139"/>
-      <c r="O145" s="139"/>
-      <c r="P145" s="139"/>
-      <c r="Q145" s="138"/>
-      <c r="R145" s="138"/>
-      <c r="S145" s="138"/>
-      <c r="T145" s="138"/>
-      <c r="U145" s="139"/>
-      <c r="V145" s="139"/>
+      <c r="B145" s="134"/>
+      <c r="C145" s="134"/>
+      <c r="D145" s="134"/>
+      <c r="E145" s="134"/>
+      <c r="F145" s="134"/>
+      <c r="G145" s="134"/>
+      <c r="H145" s="134"/>
+      <c r="I145" s="133"/>
+      <c r="J145" s="133"/>
+      <c r="K145" s="134"/>
+      <c r="L145" s="134"/>
+      <c r="M145" s="134"/>
+      <c r="N145" s="134"/>
+      <c r="O145" s="134"/>
+      <c r="P145" s="134"/>
+      <c r="Q145" s="133"/>
+      <c r="R145" s="133"/>
+      <c r="S145" s="133"/>
+      <c r="T145" s="133"/>
+      <c r="U145" s="134"/>
+      <c r="V145" s="134"/>
     </row>
     <row r="146" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B146" s="139"/>
-      <c r="C146" s="139"/>
-      <c r="D146" s="139"/>
-      <c r="E146" s="139"/>
-      <c r="F146" s="139"/>
-      <c r="G146" s="138"/>
-      <c r="H146" s="138"/>
-      <c r="I146" s="139"/>
-      <c r="J146" s="139"/>
-      <c r="K146" s="139"/>
-      <c r="L146" s="139"/>
-      <c r="M146" s="139"/>
-      <c r="N146" s="139"/>
-      <c r="O146" s="139"/>
-      <c r="P146" s="139"/>
-      <c r="Q146" s="138"/>
-      <c r="R146" s="138"/>
-      <c r="S146" s="138"/>
-      <c r="T146" s="138"/>
-      <c r="U146" s="139"/>
-      <c r="V146" s="139"/>
+      <c r="B146" s="134"/>
+      <c r="C146" s="134"/>
+      <c r="D146" s="134"/>
+      <c r="E146" s="134"/>
+      <c r="F146" s="134"/>
+      <c r="G146" s="133"/>
+      <c r="H146" s="133"/>
+      <c r="I146" s="134"/>
+      <c r="J146" s="134"/>
+      <c r="K146" s="134"/>
+      <c r="L146" s="134"/>
+      <c r="M146" s="134"/>
+      <c r="N146" s="134"/>
+      <c r="O146" s="134"/>
+      <c r="P146" s="134"/>
+      <c r="Q146" s="133"/>
+      <c r="R146" s="133"/>
+      <c r="S146" s="133"/>
+      <c r="T146" s="133"/>
+      <c r="U146" s="134"/>
+      <c r="V146" s="134"/>
     </row>
     <row r="147" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B147" s="139"/>
-      <c r="C147" s="139"/>
-      <c r="D147" s="139"/>
-      <c r="E147" s="139"/>
-      <c r="F147" s="139"/>
-      <c r="G147" s="138"/>
-      <c r="H147" s="138"/>
-      <c r="I147" s="139"/>
-      <c r="J147" s="139"/>
-      <c r="K147" s="138"/>
-      <c r="L147" s="138"/>
-      <c r="M147" s="139"/>
-      <c r="N147" s="139"/>
-      <c r="O147" s="139"/>
-      <c r="P147" s="139"/>
-      <c r="Q147" s="139"/>
-      <c r="R147" s="139"/>
-      <c r="S147" s="139"/>
-      <c r="T147" s="139"/>
-      <c r="U147" s="139"/>
-      <c r="V147" s="139"/>
+      <c r="B147" s="134"/>
+      <c r="C147" s="134"/>
+      <c r="D147" s="134"/>
+      <c r="E147" s="134"/>
+      <c r="F147" s="134"/>
+      <c r="G147" s="133"/>
+      <c r="H147" s="133"/>
+      <c r="I147" s="134"/>
+      <c r="J147" s="134"/>
+      <c r="K147" s="133"/>
+      <c r="L147" s="133"/>
+      <c r="M147" s="134"/>
+      <c r="N147" s="134"/>
+      <c r="O147" s="134"/>
+      <c r="P147" s="134"/>
+      <c r="Q147" s="134"/>
+      <c r="R147" s="134"/>
+      <c r="S147" s="134"/>
+      <c r="T147" s="134"/>
+      <c r="U147" s="134"/>
+      <c r="V147" s="134"/>
     </row>
     <row r="148" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B148" s="139"/>
-      <c r="C148" s="139"/>
-      <c r="D148" s="139"/>
-      <c r="E148" s="139"/>
-      <c r="F148" s="139"/>
-      <c r="G148" s="139"/>
-      <c r="H148" s="139"/>
-      <c r="I148" s="139"/>
-      <c r="J148" s="139"/>
-      <c r="K148" s="138"/>
-      <c r="L148" s="138"/>
-      <c r="M148" s="139"/>
-      <c r="N148" s="139"/>
-      <c r="O148" s="139"/>
-      <c r="P148" s="139"/>
-      <c r="Q148" s="138"/>
-      <c r="R148" s="138"/>
-      <c r="S148" s="138"/>
-      <c r="T148" s="138"/>
-      <c r="U148" s="139"/>
-      <c r="V148" s="139"/>
+      <c r="B148" s="134"/>
+      <c r="C148" s="134"/>
+      <c r="D148" s="134"/>
+      <c r="E148" s="134"/>
+      <c r="F148" s="134"/>
+      <c r="G148" s="134"/>
+      <c r="H148" s="134"/>
+      <c r="I148" s="134"/>
+      <c r="J148" s="134"/>
+      <c r="K148" s="133"/>
+      <c r="L148" s="133"/>
+      <c r="M148" s="134"/>
+      <c r="N148" s="134"/>
+      <c r="O148" s="134"/>
+      <c r="P148" s="134"/>
+      <c r="Q148" s="133"/>
+      <c r="R148" s="133"/>
+      <c r="S148" s="133"/>
+      <c r="T148" s="133"/>
+      <c r="U148" s="134"/>
+      <c r="V148" s="134"/>
     </row>
     <row r="149" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B149" s="139"/>
-      <c r="C149" s="139"/>
-      <c r="D149" s="139"/>
-      <c r="E149" s="139"/>
-      <c r="F149" s="139"/>
-      <c r="G149" s="138"/>
-      <c r="H149" s="138"/>
-      <c r="I149" s="139"/>
-      <c r="J149" s="139"/>
-      <c r="K149" s="139"/>
-      <c r="L149" s="139"/>
-      <c r="M149" s="139"/>
-      <c r="N149" s="139"/>
-      <c r="O149" s="139"/>
-      <c r="P149" s="139"/>
-      <c r="Q149" s="138"/>
-      <c r="R149" s="138"/>
-      <c r="S149" s="138"/>
-      <c r="T149" s="138"/>
-      <c r="U149" s="139"/>
-      <c r="V149" s="139"/>
+      <c r="B149" s="134"/>
+      <c r="C149" s="134"/>
+      <c r="D149" s="134"/>
+      <c r="E149" s="134"/>
+      <c r="F149" s="134"/>
+      <c r="G149" s="133"/>
+      <c r="H149" s="133"/>
+      <c r="I149" s="134"/>
+      <c r="J149" s="134"/>
+      <c r="K149" s="134"/>
+      <c r="L149" s="134"/>
+      <c r="M149" s="134"/>
+      <c r="N149" s="134"/>
+      <c r="O149" s="134"/>
+      <c r="P149" s="134"/>
+      <c r="Q149" s="133"/>
+      <c r="R149" s="133"/>
+      <c r="S149" s="133"/>
+      <c r="T149" s="133"/>
+      <c r="U149" s="134"/>
+      <c r="V149" s="134"/>
     </row>
     <row r="150" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B150" s="139"/>
-      <c r="C150" s="139"/>
-      <c r="D150" s="139"/>
-      <c r="E150" s="139"/>
-      <c r="F150" s="139"/>
-      <c r="G150" s="138"/>
-      <c r="H150" s="138"/>
-      <c r="I150" s="139"/>
-      <c r="J150" s="139"/>
-      <c r="K150" s="139"/>
-      <c r="L150" s="139"/>
-      <c r="M150" s="139"/>
-      <c r="N150" s="139"/>
-      <c r="O150" s="139"/>
-      <c r="P150" s="139"/>
-      <c r="Q150" s="138"/>
-      <c r="R150" s="138"/>
-      <c r="S150" s="138"/>
-      <c r="T150" s="138"/>
-      <c r="U150" s="139"/>
-      <c r="V150" s="139"/>
+      <c r="B150" s="134"/>
+      <c r="C150" s="134"/>
+      <c r="D150" s="134"/>
+      <c r="E150" s="134"/>
+      <c r="F150" s="134"/>
+      <c r="G150" s="133"/>
+      <c r="H150" s="133"/>
+      <c r="I150" s="134"/>
+      <c r="J150" s="134"/>
+      <c r="K150" s="134"/>
+      <c r="L150" s="134"/>
+      <c r="M150" s="134"/>
+      <c r="N150" s="134"/>
+      <c r="O150" s="134"/>
+      <c r="P150" s="134"/>
+      <c r="Q150" s="133"/>
+      <c r="R150" s="133"/>
+      <c r="S150" s="133"/>
+      <c r="T150" s="133"/>
+      <c r="U150" s="134"/>
+      <c r="V150" s="134"/>
     </row>
     <row r="151" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B151" s="139"/>
-      <c r="C151" s="139"/>
-      <c r="D151" s="139"/>
-      <c r="E151" s="139"/>
-      <c r="F151" s="139"/>
-      <c r="G151" s="138"/>
-      <c r="H151" s="138"/>
-      <c r="I151" s="139"/>
-      <c r="J151" s="139"/>
-      <c r="K151" s="139"/>
-      <c r="L151" s="139"/>
-      <c r="M151" s="139"/>
-      <c r="N151" s="139"/>
-      <c r="O151" s="139"/>
-      <c r="P151" s="139"/>
-      <c r="Q151" s="138"/>
-      <c r="R151" s="138"/>
-      <c r="S151" s="138"/>
-      <c r="T151" s="138"/>
-      <c r="U151" s="139"/>
-      <c r="V151" s="139"/>
+      <c r="B151" s="134"/>
+      <c r="C151" s="134"/>
+      <c r="D151" s="134"/>
+      <c r="E151" s="134"/>
+      <c r="F151" s="134"/>
+      <c r="G151" s="133"/>
+      <c r="H151" s="133"/>
+      <c r="I151" s="134"/>
+      <c r="J151" s="134"/>
+      <c r="K151" s="134"/>
+      <c r="L151" s="134"/>
+      <c r="M151" s="134"/>
+      <c r="N151" s="134"/>
+      <c r="O151" s="134"/>
+      <c r="P151" s="134"/>
+      <c r="Q151" s="133"/>
+      <c r="R151" s="133"/>
+      <c r="S151" s="133"/>
+      <c r="T151" s="133"/>
+      <c r="U151" s="134"/>
+      <c r="V151" s="134"/>
     </row>
     <row r="152" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B152" s="138"/>
-      <c r="C152" s="138"/>
-      <c r="D152" s="139"/>
-      <c r="E152" s="139"/>
-      <c r="F152" s="139"/>
-      <c r="G152" s="138"/>
-      <c r="H152" s="139"/>
-      <c r="I152" s="138"/>
-      <c r="J152" s="139"/>
-      <c r="K152" s="138"/>
-      <c r="L152" s="139"/>
-      <c r="M152" s="138"/>
-      <c r="N152" s="139"/>
-      <c r="O152" s="138"/>
-      <c r="P152" s="139"/>
-      <c r="Q152" s="138"/>
-      <c r="R152" s="138"/>
-      <c r="S152" s="138"/>
-      <c r="T152" s="138"/>
-      <c r="U152" s="138"/>
-      <c r="V152" s="138"/>
+      <c r="B152" s="133"/>
+      <c r="C152" s="133"/>
+      <c r="D152" s="134"/>
+      <c r="E152" s="134"/>
+      <c r="F152" s="134"/>
+      <c r="G152" s="133"/>
+      <c r="H152" s="134"/>
+      <c r="I152" s="133"/>
+      <c r="J152" s="134"/>
+      <c r="K152" s="133"/>
+      <c r="L152" s="134"/>
+      <c r="M152" s="133"/>
+      <c r="N152" s="134"/>
+      <c r="O152" s="133"/>
+      <c r="P152" s="134"/>
+      <c r="Q152" s="133"/>
+      <c r="R152" s="133"/>
+      <c r="S152" s="133"/>
+      <c r="T152" s="133"/>
+      <c r="U152" s="133"/>
+      <c r="V152" s="133"/>
     </row>
     <row r="153" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B153" s="138"/>
-      <c r="C153" s="139"/>
-      <c r="D153" s="139"/>
-      <c r="E153" s="139"/>
-      <c r="F153" s="139"/>
-      <c r="G153" s="139"/>
-      <c r="H153" s="139"/>
-      <c r="I153" s="139"/>
-      <c r="J153" s="139"/>
-      <c r="K153" s="139"/>
-      <c r="L153" s="139"/>
-      <c r="M153" s="139"/>
-      <c r="N153" s="139"/>
-      <c r="O153" s="139"/>
-      <c r="P153" s="139"/>
-      <c r="Q153" s="138"/>
-      <c r="R153" s="138"/>
-      <c r="S153" s="138"/>
-      <c r="T153" s="138"/>
-      <c r="U153" s="138"/>
-      <c r="V153" s="139"/>
+      <c r="B153" s="133"/>
+      <c r="C153" s="134"/>
+      <c r="D153" s="134"/>
+      <c r="E153" s="134"/>
+      <c r="F153" s="134"/>
+      <c r="G153" s="134"/>
+      <c r="H153" s="134"/>
+      <c r="I153" s="134"/>
+      <c r="J153" s="134"/>
+      <c r="K153" s="134"/>
+      <c r="L153" s="134"/>
+      <c r="M153" s="134"/>
+      <c r="N153" s="134"/>
+      <c r="O153" s="134"/>
+      <c r="P153" s="134"/>
+      <c r="Q153" s="133"/>
+      <c r="R153" s="133"/>
+      <c r="S153" s="133"/>
+      <c r="T153" s="133"/>
+      <c r="U153" s="133"/>
+      <c r="V153" s="134"/>
     </row>
     <row r="154" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B154" s="138"/>
-      <c r="C154" s="138"/>
-      <c r="D154" s="138"/>
-      <c r="E154" s="138"/>
-      <c r="F154" s="138"/>
-      <c r="G154" s="138"/>
-      <c r="H154" s="138"/>
-      <c r="I154" s="138"/>
-      <c r="J154" s="138"/>
-      <c r="K154" s="138"/>
-      <c r="L154" s="138"/>
-      <c r="M154" s="138"/>
-      <c r="N154" s="138"/>
-      <c r="O154" s="138"/>
-      <c r="P154" s="138"/>
-      <c r="Q154" s="139"/>
-      <c r="R154" s="139"/>
-      <c r="S154" s="139"/>
-      <c r="T154" s="139"/>
-      <c r="U154" s="138"/>
-      <c r="V154" s="139"/>
+      <c r="B154" s="133"/>
+      <c r="C154" s="133"/>
+      <c r="D154" s="133"/>
+      <c r="E154" s="133"/>
+      <c r="F154" s="133"/>
+      <c r="G154" s="133"/>
+      <c r="H154" s="133"/>
+      <c r="I154" s="133"/>
+      <c r="J154" s="133"/>
+      <c r="K154" s="133"/>
+      <c r="L154" s="133"/>
+      <c r="M154" s="133"/>
+      <c r="N154" s="133"/>
+      <c r="O154" s="133"/>
+      <c r="P154" s="133"/>
+      <c r="Q154" s="134"/>
+      <c r="R154" s="134"/>
+      <c r="S154" s="134"/>
+      <c r="T154" s="134"/>
+      <c r="U154" s="133"/>
+      <c r="V154" s="134"/>
     </row>
     <row r="155" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B155" s="144"/>
-      <c r="C155" s="144"/>
-      <c r="D155" s="144"/>
-      <c r="E155" s="144"/>
-      <c r="F155" s="144"/>
-      <c r="G155" s="144"/>
-      <c r="H155" s="144"/>
-      <c r="I155" s="144"/>
-      <c r="J155" s="144"/>
-      <c r="K155" s="144"/>
-      <c r="L155" s="144"/>
-      <c r="M155" s="144"/>
-      <c r="N155" s="144"/>
-      <c r="O155" s="144"/>
-      <c r="P155" s="144"/>
-      <c r="Q155" s="144"/>
-      <c r="R155" s="144"/>
-      <c r="S155" s="144"/>
-      <c r="T155" s="144"/>
-      <c r="U155" s="144"/>
-      <c r="V155" s="144"/>
+      <c r="B155" s="139"/>
+      <c r="C155" s="139"/>
+      <c r="D155" s="139"/>
+      <c r="E155" s="139"/>
+      <c r="F155" s="139"/>
+      <c r="G155" s="139"/>
+      <c r="H155" s="139"/>
+      <c r="I155" s="139"/>
+      <c r="J155" s="139"/>
+      <c r="K155" s="139"/>
+      <c r="L155" s="139"/>
+      <c r="M155" s="139"/>
+      <c r="N155" s="139"/>
+      <c r="O155" s="139"/>
+      <c r="P155" s="139"/>
+      <c r="Q155" s="139"/>
+      <c r="R155" s="139"/>
+      <c r="S155" s="139"/>
+      <c r="T155" s="139"/>
+      <c r="U155" s="139"/>
+      <c r="V155" s="139"/>
     </row>
     <row r="156" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B156" s="144"/>
-      <c r="C156" s="144"/>
-      <c r="D156" s="144"/>
-      <c r="E156" s="144"/>
-      <c r="F156" s="144"/>
-      <c r="G156" s="144"/>
-      <c r="H156" s="144"/>
-      <c r="I156" s="144"/>
-      <c r="J156" s="144"/>
-      <c r="K156" s="144"/>
-      <c r="L156" s="144"/>
-      <c r="M156" s="144"/>
-      <c r="N156" s="144"/>
-      <c r="O156" s="144"/>
-      <c r="P156" s="144"/>
-      <c r="Q156" s="144"/>
-      <c r="R156" s="144"/>
-      <c r="S156" s="144"/>
-      <c r="T156" s="144"/>
-      <c r="U156" s="144"/>
-      <c r="V156" s="144"/>
+      <c r="B156" s="139"/>
+      <c r="C156" s="139"/>
+      <c r="D156" s="139"/>
+      <c r="E156" s="139"/>
+      <c r="F156" s="139"/>
+      <c r="G156" s="139"/>
+      <c r="H156" s="139"/>
+      <c r="I156" s="139"/>
+      <c r="J156" s="139"/>
+      <c r="K156" s="139"/>
+      <c r="L156" s="139"/>
+      <c r="M156" s="139"/>
+      <c r="N156" s="139"/>
+      <c r="O156" s="139"/>
+      <c r="P156" s="139"/>
+      <c r="Q156" s="139"/>
+      <c r="R156" s="139"/>
+      <c r="S156" s="139"/>
+      <c r="T156" s="139"/>
+      <c r="U156" s="139"/>
+      <c r="V156" s="139"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -5969,29 +5982,29 @@
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="140" t="s">
+      <c r="C2" s="135" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="140">
+        <v>46023</v>
+      </c>
+      <c r="C3" s="141" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="145">
-        <v>46023</v>
-      </c>
-      <c r="C3" s="146" t="s">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="140">
+        <v>46024</v>
+      </c>
+      <c r="C4" s="141" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="145">
-        <v>46024</v>
-      </c>
-      <c r="C4" s="146" t="s">
-        <v>36</v>
-      </c>
-    </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="145"/>
-      <c r="C5" s="147"/>
+      <c r="B5" s="140"/>
+      <c r="C5" s="142"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -6014,108 +6027,108 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="2:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="148" t="s">
+      <c r="B2" s="143" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="149" t="s">
+      <c r="C2" s="144" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="145" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="150" t="s">
+      <c r="E2" s="136" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="141" t="s">
+      <c r="F2" s="137" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="142" t="s">
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="146">
+        <v>46023</v>
+      </c>
+      <c r="C3" s="147" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="151">
-        <v>46023</v>
-      </c>
-      <c r="C3" s="152" t="s">
+      <c r="D3" s="148">
+        <v>950</v>
+      </c>
+      <c r="E3" s="149"/>
+      <c r="F3" s="150"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="151"/>
+      <c r="C4" s="152" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="153">
+        <v>950</v>
+      </c>
+      <c r="E4" s="154"/>
+      <c r="F4" s="155"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="156"/>
+      <c r="C5" s="157" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="153">
-        <v>950</v>
-      </c>
-      <c r="E3" s="154"/>
-      <c r="F3" s="155"/>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="156"/>
-      <c r="C4" s="157" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="158">
-        <v>950</v>
-      </c>
-      <c r="E4" s="159"/>
-      <c r="F4" s="160"/>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="161"/>
-      <c r="C5" s="162" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="163">
+      <c r="D5" s="158">
         <v>1150</v>
       </c>
-      <c r="E5" s="164"/>
-      <c r="F5" s="165"/>
+      <c r="E5" s="159"/>
+      <c r="F5" s="160"/>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="85" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="86"/>
-      <c r="D6" s="166">
+      <c r="D6" s="161">
         <v>3050</v>
       </c>
-      <c r="E6" s="167">
+      <c r="E6" s="162">
         <v>3000</v>
       </c>
-      <c r="F6" s="168">
+      <c r="F6" s="163">
         <v>2850</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="151">
+      <c r="B7" s="146">
         <v>46024</v>
       </c>
-      <c r="C7" s="152" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="163">
+      <c r="C7" s="147" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="158">
         <v>1150</v>
       </c>
-      <c r="E7" s="169"/>
-      <c r="F7" s="170"/>
+      <c r="E7" s="164"/>
+      <c r="F7" s="165"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="156"/>
-      <c r="C8" s="157" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="163">
+      <c r="B8" s="151"/>
+      <c r="C8" s="152" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="158">
         <v>1150</v>
       </c>
-      <c r="E8" s="171"/>
-      <c r="F8" s="172"/>
+      <c r="E8" s="166"/>
+      <c r="F8" s="167"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="85" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="86"/>
-      <c r="D9" s="166">
+      <c r="D9" s="161">
         <v>2300</v>
       </c>
-      <c r="E9" s="173">
+      <c r="E9" s="168">
         <v>3000</v>
       </c>
-      <c r="F9" s="174">
+      <c r="F9" s="169">
         <v>4750</v>
       </c>
     </row>
@@ -6132,174 +6145,174 @@
   <dimension ref="A2:AMJ10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="175"/>
-    <col min="2" max="2" width="13.5" style="175" customWidth="1"/>
-    <col min="3" max="8" width="14" style="175" customWidth="1"/>
-    <col min="9" max="20" width="9.25" style="175" customWidth="1"/>
-    <col min="21" max="1024" width="9" style="175"/>
+    <col min="1" max="1" width="9" style="170"/>
+    <col min="2" max="2" width="13.5" style="170" customWidth="1"/>
+    <col min="3" max="8" width="14" style="170" customWidth="1"/>
+    <col min="9" max="20" width="9.25" style="170" customWidth="1"/>
+    <col min="21" max="1024" width="9" style="170"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="176" t="s">
+      <c r="B2" s="171" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="177" t="s">
+      <c r="C2" s="172" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="173" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="178" t="s">
+      <c r="E2" s="174" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="179" t="s">
+      <c r="F2" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="180" t="s">
+      <c r="G2" s="176" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="177" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="181" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" s="182" t="s">
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="178" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="183" t="s">
+      <c r="C3" s="179" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="184" t="s">
+      <c r="D3" s="180" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="185" t="s">
+      <c r="E3" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="186" t="s">
+      <c r="F3" s="182" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="187" t="s">
+      <c r="G3" s="183"/>
+      <c r="H3" s="184"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="185"/>
+      <c r="C4" s="186" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="187" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="188"/>
-      <c r="H3" s="189"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="190"/>
-      <c r="C4" s="191" t="s">
+      <c r="E4" s="188" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="189" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="190"/>
+      <c r="H4" s="191"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="192"/>
+      <c r="C5" s="193" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="194" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="195" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="196" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="197"/>
+      <c r="H5" s="198"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="199" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="200"/>
+      <c r="D6" s="201"/>
+      <c r="E6" s="202"/>
+      <c r="F6" s="203" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="204" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" s="205" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="178" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="179" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="180" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="193" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="194" t="s">
+      <c r="E7" s="181" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="182" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" s="183"/>
+      <c r="H7" s="206"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="185"/>
+      <c r="C8" s="186" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="187" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="188" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="189" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="207"/>
+      <c r="H8" s="208"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="192"/>
+      <c r="C9" s="193" t="s">
         <v>55</v>
       </c>
-      <c r="G4" s="195"/>
-      <c r="H4" s="196"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="197"/>
-      <c r="C5" s="198" t="s">
+      <c r="D9" s="194" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="199" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="200" t="s">
-        <v>58</v>
-      </c>
-      <c r="F5" s="201" t="s">
-        <v>59</v>
-      </c>
-      <c r="G5" s="202"/>
-      <c r="H5" s="203"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="204" t="s">
+      <c r="E9" s="195" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="196" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="209"/>
+      <c r="H9" s="198"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="199" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="205"/>
-      <c r="D6" s="206"/>
-      <c r="E6" s="207"/>
-      <c r="F6" s="208" t="s">
+      <c r="C10" s="200"/>
+      <c r="D10" s="201"/>
+      <c r="E10" s="202"/>
+      <c r="F10" s="203" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="210" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="209" t="s">
-        <v>61</v>
-      </c>
-      <c r="H6" s="210" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="183" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="184" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="185" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="186" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="187" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" s="188"/>
-      <c r="H7" s="211"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="190"/>
-      <c r="C8" s="191" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="192" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="193" t="s">
-        <v>63</v>
-      </c>
-      <c r="F8" s="194" t="s">
-        <v>64</v>
-      </c>
-      <c r="G8" s="212"/>
-      <c r="H8" s="213"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="197"/>
-      <c r="C9" s="198" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="199" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="200" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" s="201" t="s">
+      <c r="H10" s="205" t="s">
         <v>66</v>
-      </c>
-      <c r="G9" s="214"/>
-      <c r="H9" s="203"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="204" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="205"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="208" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" s="215" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" s="210" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -6314,90 +6327,90 @@
   <dimension ref="A2:AMJ6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="216"/>
-    <col min="2" max="2" width="13.5" style="216" customWidth="1"/>
-    <col min="3" max="3" width="13" style="216" customWidth="1"/>
-    <col min="4" max="4" width="21.125" style="216" customWidth="1"/>
-    <col min="5" max="6" width="13" style="216" customWidth="1"/>
-    <col min="7" max="19" width="9.25" style="216" customWidth="1"/>
-    <col min="20" max="1024" width="9" style="216"/>
+    <col min="1" max="1" width="9" style="211"/>
+    <col min="2" max="2" width="13.5" style="211" customWidth="1"/>
+    <col min="3" max="3" width="13" style="211" customWidth="1"/>
+    <col min="4" max="4" width="21.125" style="211" customWidth="1"/>
+    <col min="5" max="6" width="13" style="211" customWidth="1"/>
+    <col min="7" max="19" width="9.25" style="211" customWidth="1"/>
+    <col min="20" max="1024" width="9" style="211"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="176" t="s">
+      <c r="B2" s="171" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="177" t="s">
+      <c r="C2" s="172" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="173" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="178" t="s">
+      <c r="E2" s="174" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="179" t="s">
+      <c r="F2" s="175" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="178" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="179" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="180" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="184" t="s">
+      <c r="D3" s="180" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="185" t="s">
+      <c r="E3" s="181" t="s">
         <v>72</v>
       </c>
-      <c r="E3" s="186" t="s">
+      <c r="F3" s="212" t="s">
         <v>73</v>
       </c>
-      <c r="F3" s="217" t="s">
+      <c r="H3" s="211" t="s">
         <v>74</v>
       </c>
-      <c r="H3" s="216" t="s">
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="199" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="200"/>
+      <c r="D4" s="201"/>
+      <c r="E4" s="202" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="213"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="178" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="179" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="180" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="181" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="214" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="199" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="200"/>
+      <c r="D6" s="201"/>
+      <c r="E6" s="202" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="204" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="205"/>
-      <c r="D4" s="206"/>
-      <c r="E4" s="207" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" s="218"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="183" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="184" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="185" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="186" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" s="219" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="204" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="205"/>
-      <c r="D6" s="206"/>
-      <c r="E6" s="207" t="s">
-        <v>76</v>
-      </c>
-      <c r="F6" s="218"/>
+      <c r="F6" s="213"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -6419,39 +6432,39 @@
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="272" t="s">
+      <c r="C2" s="267" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="272"/>
-      <c r="E2" s="273" t="s">
+      <c r="D2" s="267"/>
+      <c r="E2" s="268" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="273"/>
-      <c r="G2" s="274" t="s">
+      <c r="F2" s="268"/>
+      <c r="G2" s="269" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="274"/>
-      <c r="I2" s="275" t="s">
+      <c r="H2" s="269"/>
+      <c r="I2" s="270" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="275"/>
-      <c r="K2" s="276" t="s">
+      <c r="J2" s="270"/>
+      <c r="K2" s="271" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="276"/>
-      <c r="M2" s="269" t="s">
+      <c r="L2" s="271"/>
+      <c r="M2" s="264" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="269"/>
-      <c r="O2" s="270" t="s">
+      <c r="N2" s="264"/>
+      <c r="O2" s="265" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="270"/>
-      <c r="Q2" s="271" t="s">
+      <c r="P2" s="265"/>
+      <c r="Q2" s="266" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="271"/>
-      <c r="S2" s="271"/>
+      <c r="R2" s="266"/>
+      <c r="S2" s="266"/>
       <c r="T2" s="3" t="s">
         <v>9</v>
       </c>

--- a/docs/excel_template.xlsx
+++ b/docs/excel_template.xlsx
@@ -9,14 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Money" sheetId="1" r:id="rId1"/>
-    <sheet name="feeling" sheetId="2" r:id="rId2"/>
-    <sheet name="water" sheetId="3" r:id="rId3"/>
-    <sheet name="work" sheetId="4" r:id="rId4"/>
-    <sheet name="sleep" sheetId="5" r:id="rId5"/>
+    <sheet name="water" sheetId="3" r:id="rId2"/>
+    <sheet name="work" sheetId="4" r:id="rId3"/>
+    <sheet name="sleep" sheetId="5" r:id="rId4"/>
+    <sheet name="feeling" sheetId="2" r:id="rId5"/>
     <sheet name="investment" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="152511"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="98">
   <si>
     <t>Date</t>
   </si>
@@ -327,6 +327,14 @@
   </si>
   <si>
     <t>True</t>
+  </si>
+  <si>
+    <t>SALMON_RED</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SPEARMINT_GREEN</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2001,60 +2009,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2075,6 +2029,60 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2151,6 +2159,7 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
+      <color rgb="FF1DFF78"/>
       <color rgb="FFC6E0B4"/>
     </mruColors>
   </colors>
@@ -2511,43 +2520,43 @@
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="257" t="s">
+      <c r="C2" s="266" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="257"/>
-      <c r="E2" s="262" t="s">
+      <c r="D2" s="266"/>
+      <c r="E2" s="271" t="s">
         <v>89</v>
       </c>
-      <c r="F2" s="263"/>
-      <c r="G2" s="258" t="s">
+      <c r="F2" s="272"/>
+      <c r="G2" s="267" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="258"/>
-      <c r="I2" s="259" t="s">
+      <c r="H2" s="267"/>
+      <c r="I2" s="268" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="259"/>
-      <c r="K2" s="260" t="s">
+      <c r="J2" s="268"/>
+      <c r="K2" s="269" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="260"/>
-      <c r="M2" s="261" t="s">
+      <c r="L2" s="269"/>
+      <c r="M2" s="270" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="261"/>
-      <c r="O2" s="254" t="s">
+      <c r="N2" s="270"/>
+      <c r="O2" s="263" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="254"/>
-      <c r="Q2" s="255" t="s">
+      <c r="P2" s="263"/>
+      <c r="Q2" s="264" t="s">
         <v>7</v>
       </c>
-      <c r="R2" s="255"/>
-      <c r="S2" s="256" t="s">
+      <c r="R2" s="264"/>
+      <c r="S2" s="265" t="s">
         <v>8</v>
       </c>
-      <c r="T2" s="256"/>
-      <c r="U2" s="256"/>
+      <c r="T2" s="265"/>
+      <c r="U2" s="265"/>
       <c r="V2" s="3" t="s">
         <v>9</v>
       </c>
@@ -3749,13 +3758,13 @@
       <c r="S36" s="81">
         <v>7000</v>
       </c>
-      <c r="T36" s="275">
+      <c r="T36" s="257">
         <v>5939.1</v>
       </c>
-      <c r="U36" s="276">
+      <c r="U36" s="258">
         <v>16143.12</v>
       </c>
-      <c r="V36" s="272" t="s">
+      <c r="V36" s="254" t="s">
         <v>95</v>
       </c>
     </row>
@@ -3786,11 +3795,11 @@
       <c r="S37" s="81">
         <v>7000</v>
       </c>
-      <c r="T37" s="277">
+      <c r="T37" s="259">
         <v>6282.8</v>
       </c>
-      <c r="U37" s="278"/>
-      <c r="V37" s="273"/>
+      <c r="U37" s="260"/>
+      <c r="V37" s="255"/>
     </row>
     <row r="38" spans="2:24" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="21" t="s">
@@ -3841,11 +3850,11 @@
       <c r="Q38" s="22"/>
       <c r="R38" s="23"/>
       <c r="S38" s="24"/>
-      <c r="T38" s="279"/>
-      <c r="U38" s="280">
+      <c r="T38" s="261"/>
+      <c r="U38" s="262">
         <v>16143.12</v>
       </c>
-      <c r="V38" s="274"/>
+      <c r="V38" s="256"/>
     </row>
     <row r="39" spans="2:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="133"/>
@@ -5970,51 +5979,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:C5"/>
-  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="13.5" customWidth="1"/>
-    <col min="3" max="3" width="13.375" customWidth="1"/>
-    <col min="4" max="20" width="9.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="135" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="140">
-        <v>46023</v>
-      </c>
-      <c r="C3" s="141" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="140">
-        <v>46024</v>
-      </c>
-      <c r="C4" s="141" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="140"/>
-      <c r="C5" s="142"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:F17"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6117,7 +6081,7 @@
       <c r="E8" s="166"/>
       <c r="F8" s="167"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="85" t="s">
         <v>24</v>
       </c>
@@ -6132,15 +6096,44 @@
         <v>4750</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C10" s="231" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="231" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="231" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="231" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E14" s="162">
+        <v>3000</v>
+      </c>
+      <c r="F14" s="231" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="5:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E17" s="168">
+        <v>3000</v>
+      </c>
+      <c r="F17" s="231" t="s">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:AMJ10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
@@ -6322,7 +6315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:AMJ6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
@@ -6411,6 +6404,51 @@
         <v>75</v>
       </c>
       <c r="F6" s="213"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:C5"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.5" customWidth="1"/>
+    <col min="3" max="3" width="13.375" customWidth="1"/>
+    <col min="4" max="20" width="9.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="135" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="140">
+        <v>46023</v>
+      </c>
+      <c r="C3" s="141" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="140">
+        <v>46024</v>
+      </c>
+      <c r="C4" s="141" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="140"/>
+      <c r="C5" s="142"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -6432,39 +6470,39 @@
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="267" t="s">
+      <c r="C2" s="276" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="267"/>
-      <c r="E2" s="268" t="s">
+      <c r="D2" s="276"/>
+      <c r="E2" s="277" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="268"/>
-      <c r="G2" s="269" t="s">
+      <c r="F2" s="277"/>
+      <c r="G2" s="278" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="269"/>
-      <c r="I2" s="270" t="s">
+      <c r="H2" s="278"/>
+      <c r="I2" s="279" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="270"/>
-      <c r="K2" s="271" t="s">
+      <c r="J2" s="279"/>
+      <c r="K2" s="280" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="271"/>
-      <c r="M2" s="264" t="s">
+      <c r="L2" s="280"/>
+      <c r="M2" s="273" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="264"/>
-      <c r="O2" s="265" t="s">
+      <c r="N2" s="273"/>
+      <c r="O2" s="274" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="265"/>
-      <c r="Q2" s="266" t="s">
+      <c r="P2" s="274"/>
+      <c r="Q2" s="275" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="266"/>
-      <c r="S2" s="266"/>
+      <c r="R2" s="275"/>
+      <c r="S2" s="275"/>
       <c r="T2" s="3" t="s">
         <v>9</v>
       </c>
